--- a/source data/BO_iteration.xlsx
+++ b/source data/BO_iteration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dangerlin/Documents/GitHub/SDL-for-low-temperature-ZIB-electrolyte-optimiztion/source data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BC552A-DB8F-A74F-98D5-D6CB924E2FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9124EF48-FFAD-F241-A4B4-1EF1FC84E697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="5" xr2:uid="{C0319422-2C05-7840-8738-65B20D86A76B}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="1" xr2:uid="{C0319422-2C05-7840-8738-65B20D86A76B}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Content" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Multi-obj opt_HE3'!$A$1:$AI$116</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/source data/BO_iteration.xlsx
+++ b/source data/BO_iteration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dangerlin/Documents/GitHub/SDL-for-low-temperature-ZIB-electrolyte-optimiztion/source data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9124EF48-FFAD-F241-A4B4-1EF1FC84E697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CAC691-58A4-7C4A-BF89-E71A17C8B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="1" xr2:uid="{C0319422-2C05-7840-8738-65B20D86A76B}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="232">
   <si>
     <t>Mode</t>
   </si>
@@ -125,136 +125,6 @@
   </si>
   <si>
     <t xml:space="preserve">Data of single objective optimization </t>
-  </si>
-  <si>
-    <r>
-      <t>Liquid_1: saturated ZnCl</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(31.698 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_2: saturated ZnBr</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(20.915 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_3: satureated ZnSO</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(3.575 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_4: saturated Zn(OAc)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve"> (1.913 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_5: saturated Zn(Gluconate)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve"> (0.219 m)</t>
-    </r>
   </si>
   <si>
     <t>Potential_Mean</t>
@@ -1139,6 +1009,9 @@
     <t>random_v_bo campaign</t>
   </si>
   <si>
+    <t>Comparison of random search and BO in ionic conductivity optimization campaign</t>
+  </si>
+  <si>
     <r>
       <t>Liquid_1: saturated ZnCl</t>
     </r>
@@ -1157,7 +1030,137 @@
         <color theme="1"/>
         <rFont val="ArialMT"/>
       </rPr>
-      <t>(31.698 m)</t>
+      <t>(15 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_2: saturated ZnBr</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(10 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_3: satureated ZnSO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(3.575 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_4: saturated Zn(OAc)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (1.913 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_5: saturated Zn(Gluconate)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (0.219 m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Liquid_1: saturated ZnCl</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(32.657 m)</t>
     </r>
     <r>
       <rPr>
@@ -1242,7 +1245,134 @@
     </r>
   </si>
   <si>
-    <t>Comparison of random search and BO in ionic conductivity optimization campaign</t>
+    <r>
+      <t>Liquid_1: saturated ZnCl</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(32.657 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_2: saturated ZnBr</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(20.915 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_3: satureated ZnSO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(3.575 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_4: saturated Zn(OAc)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (1.913 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_5: saturated Zn(Gluconate)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (0.219 m)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1666,13 +1796,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="95">
@@ -1686,7 +1816,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="95">
@@ -1694,13 +1824,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>27</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="95">
@@ -1708,13 +1838,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="76">
@@ -1722,13 +1852,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1802,7 +1932,7 @@
         <v>42.918450947499998</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2">
         <v>42.050275999999997</v>
@@ -1852,7 +1982,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3">
         <v>0.24782085045246899</v>
@@ -1885,19 +2015,19 @@
         <v>61</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N3">
         <v>0.65780000000000005</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P3">
         <v>5.9568000000000003E-2</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -1908,7 +2038,7 @@
         <v>39.517174095000001</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D4">
         <v>39.16172675</v>
@@ -1961,7 +2091,7 @@
         <v>74.083560152499999</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5">
         <v>73.497387380000006</v>
@@ -2003,7 +2133,7 @@
         <v>3.066E-2</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -2014,7 +2144,7 @@
         <v>52.898363297499998</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>52.881947140000001</v>
@@ -2044,10 +2174,10 @@
         <v>91</v>
       </c>
       <c r="M6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="O6">
         <v>0.26782</v>
@@ -2067,7 +2197,7 @@
         <v>39.953147244999997</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7">
         <v>38.174922680000002</v>
@@ -2097,7 +2227,7 @@
         <v>90</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N7">
         <v>0.3861</v>
@@ -2109,7 +2239,7 @@
         <v>9.6360000000000005E-3</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -2120,7 +2250,7 @@
         <v>57.21813925</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8">
         <v>56.76311862</v>
@@ -2162,7 +2292,7 @@
         <v>2.3651999999999999E-2</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -2170,10 +2300,10 @@
         <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="D9">
         <v>60.740653760000001</v>
@@ -2206,7 +2336,7 @@
         <v>3.6575839999999999</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O9">
         <v>9.9475999999999995E-2</v>
@@ -2215,7 +2345,7 @@
         <v>1.0512000000000001E-2</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -2223,7 +2353,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10">
         <v>0.526246489632614</v>
@@ -2279,7 +2409,7 @@
         <v>48.656278100000002</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11">
         <v>49.002003170000002</v>
@@ -2362,7 +2492,7 @@
         <v>102</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12">
         <v>0.20019999999999999</v>
@@ -2385,7 +2515,7 @@
         <v>52.933969677500002</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13">
         <v>52.706491149999998</v>
@@ -2438,7 +2568,7 @@
         <v>39.682550677499997</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D14">
         <v>38.268316319999997</v>
@@ -2524,7 +2654,7 @@
         <v>20.116712</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O15">
         <v>6.1216E-2</v>
@@ -2544,7 +2674,7 @@
         <v>54.45862511</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D16">
         <v>52.004763179999998</v>
@@ -2597,7 +2727,7 @@
         <v>45.916521227499999</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17">
         <v>46.545090799999997</v>
@@ -2627,16 +2757,16 @@
         <v>130</v>
       </c>
       <c r="M17" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="N17" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="O17">
         <v>0.160692</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q17">
         <v>1.8134159999999999</v>
@@ -2647,10 +2777,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="D18">
         <v>38.504118099999999</v>
@@ -2703,7 +2833,7 @@
         <v>39.98774126</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19">
         <v>44.528613980000003</v>
@@ -2756,7 +2886,7 @@
         <v>38.087868784999998</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D20">
         <v>37.051213250000004</v>
@@ -2806,10 +2936,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="D21">
         <v>44.894928849999999</v>
@@ -2851,7 +2981,7 @@
         <v>5.5188000000000001E-2</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2862,7 +2992,7 @@
         <v>59.166765507500003</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D22">
         <v>57.888635649999998</v>
@@ -2892,7 +3022,7 @@
         <v>89</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N22">
         <v>0.55769999999999997</v>
@@ -2915,7 +3045,7 @@
         <v>30.025825112500002</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D23">
         <v>30.91275641</v>
@@ -2957,7 +3087,7 @@
         <v>5.1684000000000001E-2</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -3021,7 +3151,7 @@
         <v>44.418483864999999</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D25">
         <v>43.953496659999999</v>
@@ -3074,7 +3204,7 @@
         <v>51.919963320000001</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D26">
         <v>51.646000600000001</v>
@@ -3127,7 +3257,7 @@
         <v>50.467251564999998</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D27">
         <v>49.303560660000002</v>
@@ -3160,7 +3290,7 @@
         <v>5.3557480000000002</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O27">
         <v>8.4171999999999997E-2</v>
@@ -3169,7 +3299,7 @@
         <v>1.5768000000000001E-2</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -3180,7 +3310,7 @@
         <v>47.054673972499998</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D28">
         <v>46.224606780000002</v>
@@ -3230,10 +3360,10 @@
         <v>19</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="D29">
         <v>28.79088243</v>
@@ -3286,7 +3416,7 @@
         <v>64.1891300825</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D30">
         <v>64.044459579999995</v>
@@ -3328,7 +3458,7 @@
         <v>7.1831999999999993E-2</v>
       </c>
       <c r="Q30" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -3339,7 +3469,7 @@
         <v>36.5237768</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D31">
         <v>35.710041259999997</v>
@@ -3392,7 +3522,7 @@
         <v>54.608795227500003</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D32">
         <v>55.335758200000001</v>
@@ -3434,7 +3564,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="Q32" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -3537,7 +3667,7 @@
         <v>6.8867999999999999E-2</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q34">
         <v>12.835632</v>
@@ -3593,7 +3723,7 @@
         <v>2.9784000000000001E-2</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -3601,10 +3731,10 @@
         <v>19</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="D36">
         <v>47.829798220000001</v>
@@ -3640,13 +3770,13 @@
         <v>8.5800000000000001E-2</v>
       </c>
       <c r="O36" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="P36" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="P36" s="5" t="s">
+      <c r="Q36" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -3654,10 +3784,10 @@
         <v>19</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="D37">
         <v>29.869636610000001</v>
@@ -3687,7 +3817,7 @@
         <v>19</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N37">
         <v>1.4014</v>
@@ -3696,10 +3826,10 @@
         <v>0.57389999999999997</v>
       </c>
       <c r="P37" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q37" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="Q37" s="5" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -3707,10 +3837,10 @@
         <v>19</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="D38">
         <v>48.302143129999997</v>
@@ -3749,7 +3879,7 @@
         <v>0.18364800000000001</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q38">
         <v>8.3422560000000008</v>
@@ -3763,7 +3893,7 @@
         <v>43.912943492499998</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D39">
         <v>43.807258959999999</v>
@@ -3813,10 +3943,10 @@
         <v>20</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="D40">
         <v>34.971083950000001</v>
@@ -3852,13 +3982,13 @@
         <v>1.2869999999999999</v>
       </c>
       <c r="O40" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P40">
         <v>5.5188000000000001E-2</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -3866,10 +3996,10 @@
         <v>20</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="D41">
         <v>17.629161109999998</v>
@@ -3899,7 +4029,7 @@
         <v>13</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N41">
         <v>0.84370000000000001</v>
@@ -3911,7 +4041,7 @@
         <v>7.0080000000000003E-3</v>
       </c>
       <c r="Q41" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -3922,7 +4052,7 @@
         <v>42.693942667500004</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D42">
         <v>41.585500430000003</v>
@@ -3955,7 +4085,7 @@
         <v>4.3107240000000004</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O42">
         <v>0.35964400000000002</v>
@@ -3975,7 +4105,7 @@
         <v>59.239201352499997</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D43">
         <v>59.21154035</v>
@@ -4017,7 +4147,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="Q43" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -4025,10 +4155,10 @@
         <v>20</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="D44">
         <v>37.165418899999999</v>
@@ -4081,7 +4211,7 @@
         <v>42.565158369999999</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D45">
         <v>43.152021740000002</v>
@@ -4134,7 +4264,7 @@
         <v>50.865378542499997</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D46">
         <v>49.076958099999999</v>
@@ -4176,7 +4306,7 @@
         <v>7.7964000000000006E-2</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -4187,7 +4317,7 @@
         <v>51.105464947500003</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D47">
         <v>49.192516959999999</v>
@@ -4217,7 +4347,7 @@
         <v>87</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N47">
         <v>0.2288</v>
@@ -4229,7 +4359,7 @@
         <v>3.3287999999999998E-2</v>
       </c>
       <c r="Q47" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -4237,10 +4367,10 @@
         <v>19</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="D48">
         <v>42.311381820000001</v>
@@ -4270,7 +4400,7 @@
         <v>67</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N48">
         <v>1.5301</v>
@@ -4279,10 +4409,10 @@
         <v>0.13008400000000001</v>
       </c>
       <c r="P48" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q48" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="Q48" s="5" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -4290,10 +4420,10 @@
         <v>19</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="D49">
         <v>39.021679239999997</v>
@@ -4332,10 +4462,10 @@
         <v>0.20660400000000001</v>
       </c>
       <c r="P49" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q49" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -4346,7 +4476,7 @@
         <v>42.947345802500003</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D50">
         <v>43.43559741</v>
@@ -4385,7 +4515,7 @@
         <v>5.3564000000000001E-2</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q50">
         <v>2.0983000000000001</v>
@@ -4399,7 +4529,7 @@
         <v>36.774583759999999</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D51">
         <v>36.427164300000001</v>
@@ -4432,7 +4562,7 @@
         <v>3.1350720000000001</v>
       </c>
       <c r="N51" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O51">
         <v>0.91058799999999995</v>
@@ -4502,10 +4632,10 @@
         <v>20</v>
       </c>
       <c r="B53" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="D53">
         <v>58.376072559999997</v>
@@ -4558,7 +4688,7 @@
         <v>60.302358515000002</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D54">
         <v>59.678462619999998</v>
@@ -4588,19 +4718,19 @@
         <v>133</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N54">
         <v>0.12870000000000001</v>
       </c>
       <c r="O54" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="P54" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="P54" s="5" t="s">
+      <c r="Q54" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="Q54" s="5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -4611,7 +4741,7 @@
         <v>61.182410417500002</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D55">
         <v>61.002644850000003</v>
@@ -4653,7 +4783,7 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="Q55" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -4664,7 +4794,7 @@
         <v>50.737554317499999</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D56">
         <v>50.460411039999997</v>
@@ -4697,7 +4827,7 @@
         <v>3.1350720000000001</v>
       </c>
       <c r="N56" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O56">
         <v>0.107128</v>
@@ -4706,7 +4836,7 @@
         <v>5.8692000000000001E-2</v>
       </c>
       <c r="Q56" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -4767,10 +4897,10 @@
         <v>19</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="D58">
         <v>49.31990132</v>
@@ -4812,7 +4942,7 @@
         <v>9.4607999999999998E-2</v>
       </c>
       <c r="Q58" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -4820,10 +4950,10 @@
         <v>19</v>
       </c>
       <c r="B59" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="D59">
         <v>42.700642500000001</v>
@@ -4906,7 +5036,7 @@
         <v>5</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N60">
         <v>1.573</v>
@@ -4918,7 +5048,7 @@
         <v>5.2560000000000003E-3</v>
       </c>
       <c r="Q60" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -4926,10 +5056,10 @@
         <v>19</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="D61">
         <v>25.110166209999999</v>
@@ -4959,7 +5089,7 @@
         <v>16</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N61">
         <v>1.1153999999999999</v>
@@ -4968,10 +5098,10 @@
         <v>0.90293599999999996</v>
       </c>
       <c r="P61" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q61" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="Q61" s="5" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -4979,10 +5109,10 @@
         <v>19</v>
       </c>
       <c r="B62" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="D62">
         <v>40.560747689999999</v>
@@ -5012,7 +5142,7 @@
         <v>93</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N62">
         <v>1.2298</v>
@@ -5035,7 +5165,7 @@
         <v>45.376144932499997</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D63">
         <v>45.720019999999998</v>
@@ -5077,7 +5207,7 @@
         <v>8.4972000000000006E-2</v>
       </c>
       <c r="Q63" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -5088,7 +5218,7 @@
         <v>46.582691692499999</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D64">
         <v>46.320895219999997</v>
@@ -5141,7 +5271,7 @@
         <v>56.5917818275</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D65">
         <v>63.589058049999998</v>
@@ -5191,10 +5321,10 @@
         <v>20</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>223</v>
       </c>
       <c r="D66">
         <v>43.569656350000002</v>
@@ -5233,10 +5363,10 @@
         <v>0.28312399999999999</v>
       </c>
       <c r="P66" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q66" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="Q66" s="5" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -5247,7 +5377,7 @@
         <v>51.510058727500002</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D67">
         <v>52.000143639999997</v>
@@ -5277,7 +5407,7 @@
         <v>109</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N67">
         <v>0.18590000000000001</v>
@@ -5299,10 +5429,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3FED4FB-0BA6-8648-AB29-7B632ED59275}">
-  <dimension ref="A1:S127"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5361,7 +5491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -5419,8 +5549,36 @@
       <c r="S2">
         <v>6.9944759999999997</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="U2">
+        <f>31.698*H2/SUM(H2:M2)</f>
+        <v>2.4090480000000003</v>
+      </c>
+      <c r="V2">
+        <f>I2*20.915/SUM(H2:M2)</f>
+        <v>4.0156799999999997</v>
+      </c>
+      <c r="W2">
+        <f>J2*3.575/SUM(H2:M2)</f>
+        <v>0.44330000000000003</v>
+      </c>
+      <c r="X2">
+        <f>K2*1.913/SUM(H2:M2)</f>
+        <v>5.3564000000000001E-2</v>
+      </c>
+      <c r="Y2">
+        <f>L2*0.219/SUM(H2:M2)</f>
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="Z2">
+        <f>SUM(U2:Y2)</f>
+        <v>6.9434919999999991</v>
+      </c>
+      <c r="AA2">
+        <f>SUM(N2:R2)</f>
+        <v>7.0163759999999993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -5479,7 +5637,7 @@
         <v>12.988772000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:27">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -5538,7 +5696,7 @@
         <v>13.161712</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:27">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -5596,8 +5754,12 @@
       <c r="S5">
         <v>11.573484000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="U5">
+        <f>N2*SUM(H2:M2)/H2</f>
+        <v>32.657000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5656,7 +5818,7 @@
         <v>12.718780000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -5715,7 +5877,7 @@
         <v>10.72734</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -5774,7 +5936,7 @@
         <v>11.16422</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -5833,7 +5995,7 @@
         <v>10.489127999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -5892,7 +6054,7 @@
         <v>9.9028639999999992</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -5951,7 +6113,7 @@
         <v>10.567804000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -6010,7 +6172,7 @@
         <v>10.808692000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -6069,7 +6231,7 @@
         <v>7.6194759999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -6128,7 +6290,7 @@
         <v>3.5185240000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:27">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -6187,7 +6349,7 @@
         <v>9.3291400000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:27">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -12816,22 +12978,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>32</v>
-      </c>
-      <c r="I1" t="s">
-        <v>33</v>
       </c>
       <c r="J1" t="s">
         <v>3</v>
@@ -12846,40 +13008,40 @@
         <v>6</v>
       </c>
       <c r="N1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>37</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>38</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>39</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>40</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>41</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>42</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>43</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>44</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>45</v>
       </c>
       <c r="Z1" t="s">
         <v>7</v>
@@ -18719,7 +18881,7 @@
         <v>57.49086114</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N53">
         <v>1.7250869550000001</v>
@@ -18933,7 +19095,7 @@
         <v>-4.0384228000000001E-2</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J55">
         <v>50.433476059999997</v>
@@ -19724,7 +19886,7 @@
         <v>-3.4185321999999997E-2</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J62">
         <v>38.486427890000002</v>
@@ -20063,7 +20225,7 @@
         <v>-4.0408083999999997E-2</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J65">
         <v>51.276335279999998</v>
@@ -20402,7 +20564,7 @@
         <v>-4.0454401000000001E-2</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J68">
         <v>53.549883610000002</v>
@@ -22097,7 +22259,7 @@
         <v>-4.0377544000000001E-2</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J83">
         <v>28.099021740000001</v>
@@ -27408,7 +27570,7 @@
         <v>-2.1923268999999999E-2</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J130">
         <v>29.21663736</v>
@@ -27741,7 +27903,7 @@
         <v>1.7152603280000001</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H133">
         <v>1.0324234E-2</v>
@@ -29662,7 +29824,7 @@
         <v>1.573885132</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H150">
         <v>-6.4703202000000001E-2</v>
@@ -31137,7 +31299,7 @@
         <v>9.892507E-3</v>
       </c>
       <c r="I163" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J163">
         <v>33.353342820000002</v>
@@ -35539,22 +35701,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>32</v>
-      </c>
-      <c r="I1" t="s">
-        <v>33</v>
       </c>
       <c r="J1" t="s">
         <v>3</v>
@@ -35569,40 +35731,40 @@
         <v>6</v>
       </c>
       <c r="N1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>37</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>38</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>39</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>40</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>41</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>42</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>43</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>44</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>45</v>
       </c>
       <c r="Z1" t="s">
         <v>7</v>
@@ -35893,7 +36055,7 @@
         <v>1.087435E-2</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J4">
         <v>62.870183310000002</v>
@@ -36345,7 +36507,7 @@
         <v>1.0836983999999999E-2</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J8">
         <v>62.023866499999997</v>
@@ -38040,7 +38202,7 @@
         <v>1.0814389000000001E-2</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J23">
         <v>49.630594649999999</v>
@@ -39170,7 +39332,7 @@
         <v>1.0850706E-2</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J33">
         <v>49.722037149999998</v>
@@ -39283,7 +39445,7 @@
         <v>1.0849037000000001E-2</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J34">
         <v>64.516713190000004</v>
@@ -39396,7 +39558,7 @@
         <v>1.0851753E-2</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J35">
         <v>62.764786770000001</v>
@@ -39509,7 +39671,7 @@
         <v>1.0848524E-2</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J36">
         <v>30.876989689999998</v>
@@ -39735,7 +39897,7 @@
         <v>-4.0071408000000003E-2</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J38">
         <v>89.661542299999994</v>
@@ -39848,7 +40010,7 @@
         <v>-4.0071565000000003E-2</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J39">
         <v>73.460761700000006</v>
@@ -40074,7 +40236,7 @@
         <v>1.0848340999999999E-2</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J41">
         <v>35.794268099999996</v>
@@ -42673,7 +42835,7 @@
         <v>-3.9438149999999998E-2</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J64">
         <v>93.256614909999996</v>
@@ -43125,7 +43287,7 @@
         <v>1.0828310000000001E-2</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J68">
         <v>64.764628490000007</v>
@@ -43577,7 +43739,7 @@
         <v>1.0807615E-2</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J72">
         <v>62.231978050000002</v>
@@ -44142,7 +44304,7 @@
         <v>-1.8143459000000001E-2</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J77">
         <v>102.5074609</v>
@@ -44594,7 +44756,7 @@
         <v>9.8958980000000002E-3</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J81">
         <v>84.053351730000003</v>
@@ -45385,7 +45547,7 @@
         <v>9.9551569999999992E-3</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J88">
         <v>82.115083170000005</v>
@@ -46063,7 +46225,7 @@
         <v>9.9031589999999999E-3</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J94">
         <v>69.282708139999997</v>
@@ -46515,7 +46677,7 @@
         <v>9.8514069999999995E-3</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J98">
         <v>38.094268419999999</v>
@@ -49679,7 +49841,7 @@
         <v>9.9630729999999994E-3</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J126">
         <v>93.887455130000006</v>
@@ -50018,7 +50180,7 @@
         <v>-4.0456842E-2</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J129">
         <v>47.3647858</v>
@@ -50696,7 +50858,7 @@
         <v>9.8765980000000003E-3</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J135">
         <v>59.037385530000002</v>
@@ -50922,7 +51084,7 @@
         <v>9.8577339999999999E-3</v>
       </c>
       <c r="I137" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J137">
         <v>67.363400920000004</v>
@@ -51148,7 +51310,7 @@
         <v>9.857055E-3</v>
       </c>
       <c r="I139" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J139">
         <v>45.253920860000001</v>
@@ -51939,7 +52101,7 @@
         <v>9.8914199999999997E-3</v>
       </c>
       <c r="I146" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J146">
         <v>77.215643479999997</v>
@@ -52391,7 +52553,7 @@
         <v>9.9690379999999995E-3</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J150">
         <v>69.942284720000004</v>
@@ -52617,7 +52779,7 @@
         <v>9.8869679999999995E-3</v>
       </c>
       <c r="I152" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J152">
         <v>36.253004519999998</v>
@@ -52843,7 +53005,7 @@
         <v>9.8636330000000001E-3</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J154">
         <v>54.552453409999998</v>
@@ -54199,7 +54361,7 @@
         <v>9.9869090000000004E-3</v>
       </c>
       <c r="I166" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J166">
         <v>59.913109370000001</v>
@@ -54533,22 +54695,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>32</v>
-      </c>
-      <c r="I1" t="s">
-        <v>33</v>
       </c>
       <c r="J1" t="s">
         <v>3</v>
@@ -54563,40 +54725,40 @@
         <v>6</v>
       </c>
       <c r="N1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>37</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>38</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>39</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>40</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>41</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>42</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>43</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>44</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>45</v>
       </c>
       <c r="Z1" t="s">
         <v>7</v>
@@ -54976,7 +55138,7 @@
         <v>1.0816101999999999E-2</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J5">
         <v>31.84129167</v>
@@ -55404,7 +55566,7 @@
         <v>1.0834508E-2</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9">
         <v>29.933633369999999</v>
@@ -57437,7 +57599,7 @@
         <v>-8.6923309999999993E-3</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J28">
         <v>112.4926214</v>
@@ -57758,7 +57920,7 @@
         <v>1.0849354E-2</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J31">
         <v>36.381240949999999</v>
@@ -59256,7 +59418,7 @@
         <v>9.892484E-3</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J45">
         <v>77.095910140000001</v>
@@ -59898,7 +60060,7 @@
         <v>9.8998360000000004E-3</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J51">
         <v>50.624082270000002</v>
@@ -61182,7 +61344,7 @@
         <v>9.9029860000000008E-3</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J63">
         <v>88.211839420000004</v>
@@ -63643,7 +63805,7 @@
         <v>9.8935140000000008E-3</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J86">
         <v>30.40697655</v>
@@ -65355,7 +65517,7 @@
         <v>-4.0421502999999998E-2</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J102">
         <v>49.708414179999998</v>

--- a/source data/BO_iteration.xlsx
+++ b/source data/BO_iteration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dangerlin/Documents/GitHub/SDL-for-low-temperature-ZIB-electrolyte-optimiztion/source data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CAC691-58A4-7C4A-BF89-E71A17C8B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2A2D9B-1ECA-E14C-8A8A-F4698469C4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="1" xr2:uid="{C0319422-2C05-7840-8738-65B20D86A76B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="60160" windowHeight="33840" activeTab="5" xr2:uid="{C0319422-2C05-7840-8738-65B20D86A76B}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Content" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="172">
   <si>
     <t>Mode</t>
   </si>
@@ -607,46 +607,19 @@
     <t>53.88003487500001</t>
   </si>
   <si>
-    <t>2.8738159999999997</t>
-  </si>
-  <si>
-    <t>0.40555599999999997</t>
-  </si>
-  <si>
-    <t>3.9967399999999995</t>
-  </si>
-  <si>
     <t>0.2207550843301207</t>
   </si>
   <si>
     <t>0.3868842640690503</t>
   </si>
   <si>
-    <t>6.7876840000000005</t>
-  </si>
-  <si>
     <t>0.11993091942246459</t>
-  </si>
-  <si>
-    <t>1.4369079999999999</t>
-  </si>
-  <si>
-    <t>0.7293000000000001</t>
   </si>
   <si>
     <t>1.1088427702207486</t>
   </si>
   <si>
-    <t>15.283475999999999</t>
-  </si>
-  <si>
-    <t>15.717471999999999</t>
-  </si>
-  <si>
     <t>0.31688776510097305</t>
-  </si>
-  <si>
-    <t>2.9645879999999996</t>
   </si>
   <si>
     <t>60.664655419999995</t>
@@ -655,19 +628,10 @@
     <t>0.4507102971183678</t>
   </si>
   <si>
-    <t>1.0010000000000001</t>
-  </si>
-  <si>
-    <t>4.768572000000001</t>
-  </si>
-  <si>
     <t>68.32491903249999</t>
   </si>
   <si>
     <t>0.6625718824531347</t>
-  </si>
-  <si>
-    <t>12.279031999999999</t>
   </si>
   <si>
     <t>0.45801993564319476</t>
@@ -676,22 +640,10 @@
     <t>1.4179041612384322</t>
   </si>
   <si>
-    <t>0.5720000000000001</t>
-  </si>
-  <si>
     <t>2.757547355057879</t>
   </si>
   <si>
     <t>0.41859772422076225</t>
-  </si>
-  <si>
-    <t>1.3062799999999999</t>
-  </si>
-  <si>
-    <t>0.28600000000000003</t>
-  </si>
-  <si>
-    <t>0.060444000000000005</t>
   </si>
   <si>
     <t>36.72075082666667</t>
@@ -712,19 +664,10 @@
     <t>0.18810642367511635</t>
   </si>
   <si>
-    <t>5.481528000000001</t>
-  </si>
-  <si>
     <t>2.026883318739625</t>
   </si>
   <si>
-    <t>9.666471999999999</t>
-  </si>
-  <si>
     <t>0.6494440449890824</t>
-  </si>
-  <si>
-    <t>1.7668519999999999</t>
   </si>
   <si>
     <t>0.38525999109399206</t>
@@ -734,12 +677,6 @@
   </si>
   <si>
     <t>0.6942665810177673</t>
-  </si>
-  <si>
-    <t>1.1440000000000001</t>
-  </si>
-  <si>
-    <t>6.5996879999999996</t>
   </si>
   <si>
     <t>0.49530731734543004</t>
@@ -754,22 +691,10 @@
     <t>0.15061109114819485</t>
   </si>
   <si>
-    <t>4.476547999999999</t>
-  </si>
-  <si>
     <t>0.7581717667625103</t>
   </si>
   <si>
     <t>0.5591424189446453</t>
-  </si>
-  <si>
-    <t>3.2279640000000005</t>
-  </si>
-  <si>
-    <t>0.035916000000000003</t>
-  </si>
-  <si>
-    <t>10.688351999999998</t>
   </si>
   <si>
     <t>47.04579585250001</t>
@@ -778,37 +703,16 @@
     <t>0.5161493741710436</t>
   </si>
   <si>
-    <t>0.17599599999999999</t>
-  </si>
-  <si>
-    <t>0.12088800000000001</t>
-  </si>
-  <si>
-    <t>1.9502200000000003</t>
-  </si>
-  <si>
     <t>28.629007063333333</t>
   </si>
   <si>
     <t>1.4764739334736934</t>
   </si>
   <si>
-    <t>4.833235999999999</t>
-  </si>
-  <si>
-    <t>0.018396000000000003</t>
-  </si>
-  <si>
-    <t>6.826931999999999</t>
-  </si>
-  <si>
     <t>45.703182979999994</t>
   </si>
   <si>
     <t>1.7934715286720417</t>
-  </si>
-  <si>
-    <t>0.056940000000000004</t>
   </si>
   <si>
     <t>1.2930151084552908</t>
@@ -820,31 +724,16 @@
     <t>0.8807187615970081</t>
   </si>
   <si>
-    <t>0.29842799999999997</t>
-  </si>
-  <si>
-    <t>8.433271999999999</t>
-  </si>
-  <si>
     <t>16.292930253333335</t>
   </si>
   <si>
     <t>1.090726717165428</t>
   </si>
   <si>
-    <t>15.936615999999999</t>
-  </si>
-  <si>
-    <t>17.154619999999998</t>
-  </si>
-  <si>
     <t>1.2548409653125085</t>
   </si>
   <si>
     <t>0.3194630195708421</t>
-  </si>
-  <si>
-    <t>4.330487999999999</t>
   </si>
   <si>
     <t>39.203241337499996</t>
@@ -859,13 +748,7 @@
     <t>1.0665826041012425</t>
   </si>
   <si>
-    <t>4.110379999999999</t>
-  </si>
-  <si>
     <t>1.2881385508355896</t>
-  </si>
-  <si>
-    <t>12.655899999999999</t>
   </si>
   <si>
     <t>42.932141092500004</t>
@@ -874,31 +757,16 @@
     <t>0.5220898295378614</t>
   </si>
   <si>
-    <t>0.042924000000000004</t>
-  </si>
-  <si>
-    <t>3.0093880000000004</t>
-  </si>
-  <si>
     <t>54.351613773333334</t>
   </si>
   <si>
     <t>0.5826598898492974</t>
   </si>
   <si>
-    <t>9.407152000000002</t>
-  </si>
-  <si>
     <t>0.35436298508875935</t>
   </si>
   <si>
-    <t>0.10074000000000001</t>
-  </si>
-  <si>
     <t>0.2984635599740694</t>
-  </si>
-  <si>
-    <t>0.14300000000000002</t>
   </si>
   <si>
     <t>56.01757197333333</t>
@@ -910,25 +778,10 @@
     <t>0.4612388101067615</t>
   </si>
   <si>
-    <t>0.35199199999999997</t>
-  </si>
-  <si>
-    <t>0.021900000000000003</t>
-  </si>
-  <si>
-    <t>5.335827999999999</t>
-  </si>
-  <si>
     <t>0.22861875332547804</t>
   </si>
   <si>
-    <t>4.844315999999999</t>
-  </si>
-  <si>
     <t>0.3195678248727552</t>
-  </si>
-  <si>
-    <t>4.3018920000000005</t>
   </si>
   <si>
     <t>49.528466294999994</t>
@@ -937,19 +790,10 @@
     <t>0.26082957448494254</t>
   </si>
   <si>
-    <t>4.4580720000000005</t>
-  </si>
-  <si>
     <t>17.005722176666666</t>
   </si>
   <si>
     <t>1.1690348904381527</t>
-  </si>
-  <si>
-    <t>13.454683999999999</t>
-  </si>
-  <si>
-    <t>15.231891999999998</t>
   </si>
   <si>
     <t>24.907431009999996</t>
@@ -958,28 +802,13 @@
     <t>0.22830100510890622</t>
   </si>
   <si>
-    <t>0.6531399999999999</t>
-  </si>
-  <si>
-    <t>0.028908000000000003</t>
-  </si>
-  <si>
-    <t>2.7003839999999997</t>
-  </si>
-  <si>
     <t>43.081764754999995</t>
   </si>
   <si>
     <t>2.117327112700659</t>
   </si>
   <si>
-    <t>3.5269559999999998</t>
-  </si>
-  <si>
     <t>0.4164443271310923</t>
-  </si>
-  <si>
-    <t>4.508647999999999</t>
   </si>
   <si>
     <t>0.23279896239353962</t>
@@ -994,16 +823,7 @@
     <t>1.112975369474277</t>
   </si>
   <si>
-    <t>0.036792000000000005</t>
-  </si>
-  <si>
-    <t>10.021576000000001</t>
-  </si>
-  <si>
     <t>0.7369421843935279</t>
-  </si>
-  <si>
-    <t>7.0539119999999995</t>
   </si>
   <si>
     <t>random_v_bo campaign</t>
@@ -1796,13 +1616,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>230</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="95">
@@ -1816,7 +1636,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>231</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="95">
@@ -1830,7 +1650,7 @@
         <v>54</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>229</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="95">
@@ -1968,10 +1788,10 @@
         <v>1.43</v>
       </c>
       <c r="O2">
-        <v>0.14538799999999999</v>
+        <v>0.14538800000000002</v>
       </c>
       <c r="P2">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="Q2">
         <v>8.1164240000000003</v>
@@ -2014,20 +1834,20 @@
       <c r="L3">
         <v>61</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>94</v>
+      <c r="M3" s="5">
+        <v>2.8738159999999997</v>
       </c>
       <c r="N3">
         <v>0.65780000000000005</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>95</v>
+      <c r="O3" s="5">
+        <v>0.40555599999999997</v>
       </c>
       <c r="P3">
-        <v>5.9568000000000003E-2</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>96</v>
+        <v>5.9567999999999996E-2</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>3.9967399999999995</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -2038,7 +1858,7 @@
         <v>39.517174095000001</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D4">
         <v>39.16172675</v>
@@ -2071,7 +1891,7 @@
         <v>0.91439599999999999</v>
       </c>
       <c r="N4">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="O4">
         <v>0.68102799999999997</v>
@@ -2091,7 +1911,7 @@
         <v>74.083560152499999</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D5">
         <v>73.497387380000006</v>
@@ -2121,10 +1941,10 @@
         <v>129</v>
       </c>
       <c r="M5">
-        <v>6.4007719999999999</v>
+        <v>6.400771999999999</v>
       </c>
       <c r="N5">
-        <v>0.1573</v>
+        <v>0.15730000000000002</v>
       </c>
       <c r="O5">
         <v>0.19895199999999999</v>
@@ -2132,8 +1952,8 @@
       <c r="P5">
         <v>3.066E-2</v>
       </c>
-      <c r="Q5" s="5" t="s">
-        <v>99</v>
+      <c r="Q5" s="5">
+        <v>6.7876839999999996</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -2144,7 +1964,7 @@
         <v>52.898363297499998</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D6">
         <v>52.881947140000001</v>
@@ -2173,11 +1993,11 @@
       <c r="L6">
         <v>91</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>102</v>
+      <c r="M6" s="5">
+        <v>1.4369079999999999</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0.72930000000000006</v>
       </c>
       <c r="O6">
         <v>0.26782</v>
@@ -2197,7 +2017,7 @@
         <v>39.953147244999997</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D7">
         <v>38.174922680000002</v>
@@ -2226,20 +2046,20 @@
       <c r="L7">
         <v>90</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>104</v>
+      <c r="M7" s="5">
+        <v>15.283475999999999</v>
       </c>
       <c r="N7">
         <v>0.3861</v>
       </c>
       <c r="O7">
-        <v>3.8260000000000002E-2</v>
+        <v>3.8259999999999995E-2</v>
       </c>
       <c r="P7">
-        <v>9.6360000000000005E-3</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>105</v>
+        <v>9.6359999999999987E-3</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>15.717471999999999</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -2250,7 +2070,7 @@
         <v>57.21813925</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D8">
         <v>56.76311862</v>
@@ -2283,7 +2103,7 @@
         <v>1.828792</v>
       </c>
       <c r="N8">
-        <v>0.94379999999999997</v>
+        <v>0.94380000000000008</v>
       </c>
       <c r="O8">
         <v>0.16834399999999999</v>
@@ -2291,8 +2111,8 @@
       <c r="P8">
         <v>2.3651999999999999E-2</v>
       </c>
-      <c r="Q8" s="5" t="s">
-        <v>107</v>
+      <c r="Q8" s="5">
+        <v>2.9645879999999996</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -2300,10 +2120,10 @@
         <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>60.740653760000001</v>
@@ -2335,8 +2155,8 @@
       <c r="M9">
         <v>3.6575839999999999</v>
       </c>
-      <c r="N9" s="5" t="s">
-        <v>110</v>
+      <c r="N9" s="5">
+        <v>1.0009999999999999</v>
       </c>
       <c r="O9">
         <v>9.9475999999999995E-2</v>
@@ -2344,8 +2164,8 @@
       <c r="P9">
         <v>1.0512000000000001E-2</v>
       </c>
-      <c r="Q9" s="5" t="s">
-        <v>111</v>
+      <c r="Q9" s="5">
+        <v>4.7685719999999998</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -2353,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C10">
         <v>0.526246489632614</v>
@@ -2386,7 +2206,7 @@
         <v>77</v>
       </c>
       <c r="M10">
-        <v>9.0133320000000001</v>
+        <v>9.0133319999999983</v>
       </c>
       <c r="N10">
         <v>7.1499999999999994E-2</v>
@@ -2398,7 +2218,7 @@
         <v>7.5336E-2</v>
       </c>
       <c r="Q10">
-        <v>9.2596439999999998</v>
+        <v>9.259643999999998</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -2409,7 +2229,7 @@
         <v>48.656278100000002</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D11">
         <v>49.002003170000002</v>
@@ -2448,7 +2268,7 @@
         <v>0.16834399999999999</v>
       </c>
       <c r="P11">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="Q11">
         <v>3.6945239999999999</v>
@@ -2491,11 +2311,11 @@
       <c r="L12">
         <v>102</v>
       </c>
-      <c r="M12" s="5" t="s">
-        <v>114</v>
+      <c r="M12" s="5">
+        <v>12.279031999999999</v>
       </c>
       <c r="N12">
-        <v>0.20019999999999999</v>
+        <v>0.20020000000000002</v>
       </c>
       <c r="O12">
         <v>0.107128</v>
@@ -2515,7 +2335,7 @@
         <v>52.933969677500002</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D13">
         <v>52.706491149999998</v>
@@ -2545,10 +2365,10 @@
         <v>87</v>
       </c>
       <c r="M13">
-        <v>5.0944919999999998</v>
+        <v>5.0944919999999989</v>
       </c>
       <c r="N13">
-        <v>0.20019999999999999</v>
+        <v>0.20020000000000002</v>
       </c>
       <c r="O13">
         <v>0.57389999999999997</v>
@@ -2557,7 +2377,7 @@
         <v>3.066E-2</v>
       </c>
       <c r="Q13">
-        <v>5.8992519999999997</v>
+        <v>5.8992519999999988</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -2568,7 +2388,7 @@
         <v>39.682550677499997</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D14">
         <v>38.268316319999997</v>
@@ -2598,13 +2418,13 @@
         <v>39</v>
       </c>
       <c r="M14">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="N14">
         <v>1.5444</v>
       </c>
       <c r="O14">
-        <v>0.22955999999999999</v>
+        <v>0.22956000000000001</v>
       </c>
       <c r="P14">
         <v>4.7303999999999999E-2</v>
@@ -2653,8 +2473,8 @@
       <c r="M15">
         <v>20.116712</v>
       </c>
-      <c r="N15" s="5" t="s">
-        <v>117</v>
+      <c r="N15" s="5">
+        <v>0.57199999999999995</v>
       </c>
       <c r="O15">
         <v>6.1216E-2</v>
@@ -2674,7 +2494,7 @@
         <v>54.45862511</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D16">
         <v>52.004763179999998</v>
@@ -2727,7 +2547,7 @@
         <v>45.916521227499999</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="D17">
         <v>46.545090799999997</v>
@@ -2756,20 +2576,20 @@
       <c r="L17">
         <v>130</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>121</v>
+      <c r="M17" s="5">
+        <v>1.3062799999999997</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0.28599999999999998</v>
       </c>
       <c r="O17">
         <v>0.160692</v>
       </c>
-      <c r="P17" s="5" t="s">
-        <v>122</v>
+      <c r="P17" s="5">
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="Q17">
-        <v>1.8134159999999999</v>
+        <v>1.8134159999999997</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -2777,10 +2597,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D18">
         <v>38.504118099999999</v>
@@ -2816,7 +2636,7 @@
         <v>1.2726999999999999</v>
       </c>
       <c r="O18">
-        <v>0.30608000000000002</v>
+        <v>0.30607999999999996</v>
       </c>
       <c r="P18">
         <v>6.6575999999999996E-2</v>
@@ -2833,7 +2653,7 @@
         <v>39.98774126</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D19">
         <v>44.528613980000003</v>
@@ -2886,7 +2706,7 @@
         <v>38.087868784999998</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D20">
         <v>37.051213250000004</v>
@@ -2922,7 +2742,7 @@
         <v>1.5444</v>
       </c>
       <c r="O20">
-        <v>0.22190799999999999</v>
+        <v>0.22190800000000002</v>
       </c>
       <c r="P20">
         <v>6.3948000000000005E-2</v>
@@ -2936,10 +2756,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D21">
         <v>44.894928849999999</v>
@@ -2980,8 +2800,8 @@
       <c r="P21">
         <v>5.5188000000000001E-2</v>
       </c>
-      <c r="Q21" s="5" t="s">
-        <v>129</v>
+      <c r="Q21" s="5">
+        <v>5.4815280000000008</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2992,7 +2812,7 @@
         <v>59.166765507500003</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D22">
         <v>57.888635649999998</v>
@@ -3021,11 +2841,11 @@
       <c r="L22">
         <v>89</v>
       </c>
-      <c r="M22" s="5" t="s">
-        <v>131</v>
+      <c r="M22" s="5">
+        <v>9.6664720000000006</v>
       </c>
       <c r="N22">
-        <v>0.55769999999999997</v>
+        <v>0.55770000000000008</v>
       </c>
       <c r="O22">
         <v>6.8867999999999999E-2</v>
@@ -3034,7 +2854,7 @@
         <v>3.4164E-2</v>
       </c>
       <c r="Q22">
-        <v>10.327204</v>
+        <v>10.327204000000002</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -3045,7 +2865,7 @@
         <v>30.025825112500002</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="D23">
         <v>30.91275641</v>
@@ -3075,7 +2895,7 @@
         <v>85</v>
       </c>
       <c r="M23">
-        <v>0.78376800000000002</v>
+        <v>0.78376799999999991</v>
       </c>
       <c r="N23">
         <v>0.35749999999999998</v>
@@ -3086,8 +2906,8 @@
       <c r="P23">
         <v>5.1684000000000001E-2</v>
       </c>
-      <c r="Q23" s="5" t="s">
-        <v>133</v>
+      <c r="Q23" s="5">
+        <v>1.7668519999999999</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -3128,7 +2948,7 @@
         <v>11</v>
       </c>
       <c r="M24">
-        <v>4.0494680000000001</v>
+        <v>4.0494679999999992</v>
       </c>
       <c r="N24">
         <v>0.2145</v>
@@ -3140,7 +2960,7 @@
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="Q24">
-        <v>5.6052840000000002</v>
+        <v>5.6052839999999993</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -3151,7 +2971,7 @@
         <v>44.418483864999999</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D25">
         <v>43.953496659999999</v>
@@ -3187,7 +3007,7 @@
         <v>0.81510000000000005</v>
       </c>
       <c r="O25">
-        <v>0.45911999999999997</v>
+        <v>0.45912000000000003</v>
       </c>
       <c r="P25">
         <v>7.5336E-2</v>
@@ -3204,7 +3024,7 @@
         <v>51.919963320000001</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D26">
         <v>51.646000600000001</v>
@@ -3234,7 +3054,7 @@
         <v>73</v>
       </c>
       <c r="M26">
-        <v>6.2701440000000002</v>
+        <v>6.2701439999999993</v>
       </c>
       <c r="N26">
         <v>0.2288</v>
@@ -3246,7 +3066,7 @@
         <v>3.7668E-2</v>
       </c>
       <c r="Q26">
-        <v>7.0722519999999998</v>
+        <v>7.0722519999999989</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -3257,7 +3077,7 @@
         <v>50.467251564999998</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D27">
         <v>49.303560660000002</v>
@@ -3287,10 +3107,10 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>5.3557480000000002</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>137</v>
+        <v>5.3557479999999993</v>
+      </c>
+      <c r="N27" s="5">
+        <v>1.1439999999999999</v>
       </c>
       <c r="O27">
         <v>8.4171999999999997E-2</v>
@@ -3298,8 +3118,8 @@
       <c r="P27">
         <v>1.5768000000000001E-2</v>
       </c>
-      <c r="Q27" s="5" t="s">
-        <v>138</v>
+      <c r="Q27" s="5">
+        <v>6.5996879999999987</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -3310,7 +3130,7 @@
         <v>47.054673972499998</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D28">
         <v>46.224606780000002</v>
@@ -3340,7 +3160,7 @@
         <v>7</v>
       </c>
       <c r="M28">
-        <v>7.707052</v>
+        <v>7.7070519999999991</v>
       </c>
       <c r="N28">
         <v>0.12870000000000001</v>
@@ -3352,7 +3172,7 @@
         <v>9.1104000000000004E-2</v>
       </c>
       <c r="Q28">
-        <v>8.470148</v>
+        <v>8.4701479999999982</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -3360,10 +3180,10 @@
         <v>19</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D29">
         <v>28.79088243</v>
@@ -3402,7 +3222,7 @@
         <v>0.97945599999999999</v>
       </c>
       <c r="P29">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="Q29">
         <v>9.7890800000000002</v>
@@ -3416,7 +3236,7 @@
         <v>64.1891300825</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="D30">
         <v>64.044459579999995</v>
@@ -3446,10 +3266,10 @@
         <v>101</v>
       </c>
       <c r="M30">
-        <v>4.0494680000000001</v>
+        <v>4.0494679999999992</v>
       </c>
       <c r="N30">
-        <v>0.1716</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="O30">
         <v>0.18364800000000001</v>
@@ -3457,8 +3277,8 @@
       <c r="P30">
         <v>7.1831999999999993E-2</v>
       </c>
-      <c r="Q30" s="5" t="s">
-        <v>143</v>
+      <c r="Q30" s="5">
+        <v>4.4765479999999984</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -3469,7 +3289,7 @@
         <v>36.5237768</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D31">
         <v>35.710041259999997</v>
@@ -3505,7 +3325,7 @@
         <v>1.4729000000000001</v>
       </c>
       <c r="O31">
-        <v>0.45146799999999998</v>
+        <v>0.45146800000000004</v>
       </c>
       <c r="P31">
         <v>7.0080000000000003E-3</v>
@@ -3522,7 +3342,7 @@
         <v>54.608795227500003</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D32">
         <v>55.335758200000001</v>
@@ -3558,13 +3378,13 @@
         <v>1.0725</v>
       </c>
       <c r="O32">
-        <v>3.8260000000000002E-2</v>
+        <v>3.8259999999999995E-2</v>
       </c>
       <c r="P32">
         <v>2.7156E-2</v>
       </c>
-      <c r="Q32" s="5" t="s">
-        <v>146</v>
+      <c r="Q32" s="5">
+        <v>3.2279640000000005</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -3605,10 +3425,10 @@
         <v>56</v>
       </c>
       <c r="M33">
-        <v>1.567536</v>
+        <v>1.5675359999999998</v>
       </c>
       <c r="N33">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="O33">
         <v>0.244864</v>
@@ -3617,7 +3437,7 @@
         <v>0.12614400000000001</v>
       </c>
       <c r="Q33">
-        <v>2.0243440000000001</v>
+        <v>2.0243439999999997</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -3666,8 +3486,8 @@
       <c r="O34">
         <v>6.8867999999999999E-2</v>
       </c>
-      <c r="P34" s="5" t="s">
-        <v>147</v>
+      <c r="P34" s="5">
+        <v>3.5915999999999997E-2</v>
       </c>
       <c r="Q34">
         <v>12.835632</v>
@@ -3720,10 +3540,10 @@
         <v>0.49737999999999999</v>
       </c>
       <c r="P35">
-        <v>2.9784000000000001E-2</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>148</v>
+        <v>2.9783999999999998E-2</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>10.688351999999998</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -3731,10 +3551,10 @@
         <v>19</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D36">
         <v>47.829798220000001</v>
@@ -3764,19 +3584,19 @@
         <v>71</v>
       </c>
       <c r="M36">
-        <v>1.567536</v>
+        <v>1.5675359999999998</v>
       </c>
       <c r="N36">
-        <v>8.5800000000000001E-2</v>
-      </c>
-      <c r="O36" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="P36" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>153</v>
+        <v>8.5800000000000015E-2</v>
+      </c>
+      <c r="O36" s="5">
+        <v>0.17599600000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>0.12088800000000001</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>1.9502200000000001</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -3784,10 +3604,10 @@
         <v>19</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="D37">
         <v>29.869636610000001</v>
@@ -3816,20 +3636,20 @@
       <c r="L37">
         <v>19</v>
       </c>
-      <c r="M37" s="5" t="s">
-        <v>156</v>
+      <c r="M37" s="5">
+        <v>4.8332360000000003</v>
       </c>
       <c r="N37">
-        <v>1.4014</v>
+        <v>1.4014000000000002</v>
       </c>
       <c r="O37">
         <v>0.57389999999999997</v>
       </c>
-      <c r="P37" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q37" s="5" t="s">
-        <v>158</v>
+      <c r="P37" s="5">
+        <v>1.8395999999999999E-2</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>6.8269320000000002</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -3837,10 +3657,10 @@
         <v>19</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="D38">
         <v>48.302143129999997</v>
@@ -3878,8 +3698,8 @@
       <c r="O38">
         <v>0.18364800000000001</v>
       </c>
-      <c r="P38" s="5" t="s">
-        <v>161</v>
+      <c r="P38" s="5">
+        <v>5.6939999999999998E-2</v>
       </c>
       <c r="Q38">
         <v>8.3422560000000008</v>
@@ -3893,7 +3713,7 @@
         <v>43.912943492499998</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D39">
         <v>43.807258959999999</v>
@@ -3932,7 +3752,7 @@
         <v>0.3826</v>
       </c>
       <c r="P39">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="Q39">
         <v>4.8614160000000002</v>
@@ -3943,10 +3763,10 @@
         <v>20</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="D40">
         <v>34.971083950000001</v>
@@ -3976,19 +3796,19 @@
         <v>6</v>
       </c>
       <c r="M40">
-        <v>6.792656</v>
+        <v>6.7926559999999991</v>
       </c>
       <c r="N40">
         <v>1.2869999999999999</v>
       </c>
-      <c r="O40" s="5" t="s">
-        <v>165</v>
+      <c r="O40" s="5">
+        <v>0.29842799999999997</v>
       </c>
       <c r="P40">
         <v>5.5188000000000001E-2</v>
       </c>
-      <c r="Q40" s="5" t="s">
-        <v>166</v>
+      <c r="Q40" s="5">
+        <v>8.4332719999999988</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -3996,10 +3816,10 @@
         <v>20</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="D41">
         <v>17.629161109999998</v>
@@ -4028,8 +3848,8 @@
       <c r="L41">
         <v>13</v>
       </c>
-      <c r="M41" s="5" t="s">
-        <v>169</v>
+      <c r="M41" s="5">
+        <v>15.936615999999999</v>
       </c>
       <c r="N41">
         <v>0.84370000000000001</v>
@@ -4040,8 +3860,8 @@
       <c r="P41">
         <v>7.0080000000000003E-3</v>
       </c>
-      <c r="Q41" s="5" t="s">
-        <v>170</v>
+      <c r="Q41" s="5">
+        <v>17.154619999999998</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -4052,7 +3872,7 @@
         <v>42.693942667500004</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="D42">
         <v>41.585500430000003</v>
@@ -4082,10 +3902,10 @@
         <v>37</v>
       </c>
       <c r="M42">
-        <v>4.3107240000000004</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>110</v>
+        <v>4.3107239999999996</v>
+      </c>
+      <c r="N42" s="5">
+        <v>1.0009999999999999</v>
       </c>
       <c r="O42">
         <v>0.35964400000000002</v>
@@ -4105,7 +3925,7 @@
         <v>59.239201352499997</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="D43">
         <v>59.21154035</v>
@@ -4146,8 +3966,8 @@
       <c r="P43">
         <v>2.7156E-2</v>
       </c>
-      <c r="Q43" s="5" t="s">
-        <v>173</v>
+      <c r="Q43" s="5">
+        <v>4.330487999999999</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -4155,10 +3975,10 @@
         <v>20</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="D44">
         <v>37.165418899999999</v>
@@ -4211,7 +4031,7 @@
         <v>42.565158369999999</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="D45">
         <v>43.152021740000002</v>
@@ -4244,7 +4064,7 @@
         <v>4.1800959999999998</v>
       </c>
       <c r="N45">
-        <v>0.70069999999999999</v>
+        <v>0.7007000000000001</v>
       </c>
       <c r="O45">
         <v>0.3826</v>
@@ -4264,7 +4084,7 @@
         <v>50.865378542499997</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="D46">
         <v>49.076958099999999</v>
@@ -4294,10 +4114,10 @@
         <v>61</v>
       </c>
       <c r="M46">
-        <v>3.0044439999999999</v>
+        <v>3.0044439999999994</v>
       </c>
       <c r="N46">
-        <v>0.94379999999999997</v>
+        <v>0.94380000000000008</v>
       </c>
       <c r="O46">
         <v>8.4171999999999997E-2</v>
@@ -4305,8 +4125,8 @@
       <c r="P46">
         <v>7.7964000000000006E-2</v>
       </c>
-      <c r="Q46" s="5" t="s">
-        <v>178</v>
+      <c r="Q46" s="5">
+        <v>4.1103799999999993</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -4317,7 +4137,7 @@
         <v>51.105464947500003</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="D47">
         <v>49.192516959999999</v>
@@ -4346,20 +4166,20 @@
       <c r="L47">
         <v>87</v>
       </c>
-      <c r="M47" s="5" t="s">
-        <v>114</v>
+      <c r="M47" s="5">
+        <v>12.279031999999999</v>
       </c>
       <c r="N47">
         <v>0.2288</v>
       </c>
       <c r="O47">
-        <v>0.11477999999999999</v>
+        <v>0.11478000000000001</v>
       </c>
       <c r="P47">
         <v>3.3287999999999998E-2</v>
       </c>
-      <c r="Q47" s="5" t="s">
-        <v>180</v>
+      <c r="Q47" s="5">
+        <v>12.655899999999999</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -4367,10 +4187,10 @@
         <v>19</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="D48">
         <v>42.311381820000001</v>
@@ -4399,20 +4219,20 @@
       <c r="L48">
         <v>67</v>
       </c>
-      <c r="M48" s="5" t="s">
-        <v>120</v>
+      <c r="M48" s="5">
+        <v>1.3062799999999997</v>
       </c>
       <c r="N48">
-        <v>1.5301</v>
+        <v>1.5301000000000002</v>
       </c>
       <c r="O48">
         <v>0.13008400000000001</v>
       </c>
-      <c r="P48" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q48" s="5" t="s">
-        <v>184</v>
+      <c r="P48" s="5">
+        <v>4.2923999999999997E-2</v>
+      </c>
+      <c r="Q48" s="5">
+        <v>3.0093880000000004</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -4420,10 +4240,10 @@
         <v>19</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="D49">
         <v>39.021679239999997</v>
@@ -4461,11 +4281,11 @@
       <c r="O49">
         <v>0.20660400000000001</v>
       </c>
-      <c r="P49" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q49" s="5" t="s">
-        <v>187</v>
+      <c r="P49" s="5">
+        <v>6.0444000000000005E-2</v>
+      </c>
+      <c r="Q49" s="5">
+        <v>9.4071520000000017</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -4476,7 +4296,7 @@
         <v>42.947345802500003</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="D50">
         <v>43.43559741</v>
@@ -4514,8 +4334,8 @@
       <c r="O50">
         <v>5.3564000000000001E-2</v>
       </c>
-      <c r="P50" s="5" t="s">
-        <v>189</v>
+      <c r="P50" s="5">
+        <v>0.10074</v>
       </c>
       <c r="Q50">
         <v>2.0983000000000001</v>
@@ -4529,7 +4349,7 @@
         <v>36.774583759999999</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="D51">
         <v>36.427164300000001</v>
@@ -4559,10 +4379,10 @@
         <v>20</v>
       </c>
       <c r="M51">
-        <v>3.1350720000000001</v>
-      </c>
-      <c r="N51" s="5" t="s">
-        <v>191</v>
+        <v>3.1350719999999996</v>
+      </c>
+      <c r="N51" s="5">
+        <v>0.14299999999999999</v>
       </c>
       <c r="O51">
         <v>0.91058799999999995</v>
@@ -4612,10 +4432,10 @@
         <v>79</v>
       </c>
       <c r="M52">
-        <v>3.1350720000000001</v>
+        <v>3.1350719999999996</v>
       </c>
       <c r="N52">
-        <v>0.41470000000000001</v>
+        <v>0.41470000000000007</v>
       </c>
       <c r="O52">
         <v>0.757548</v>
@@ -4632,10 +4452,10 @@
         <v>20</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>192</v>
+        <v>148</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="D53">
         <v>58.376072559999997</v>
@@ -4688,7 +4508,7 @@
         <v>60.302358515000002</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>194</v>
+        <v>150</v>
       </c>
       <c r="D54">
         <v>59.678462619999998</v>
@@ -4717,20 +4537,20 @@
       <c r="L54">
         <v>133</v>
       </c>
-      <c r="M54" s="5" t="s">
-        <v>156</v>
+      <c r="M54" s="5">
+        <v>4.8332360000000003</v>
       </c>
       <c r="N54">
         <v>0.12870000000000001</v>
       </c>
-      <c r="O54" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="P54" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q54" s="5" t="s">
-        <v>197</v>
+      <c r="O54" s="5">
+        <v>0.35199200000000003</v>
+      </c>
+      <c r="P54" s="5">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>5.3358280000000002</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -4741,7 +4561,7 @@
         <v>61.182410417500002</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="D55">
         <v>61.002644850000003</v>
@@ -4771,19 +4591,19 @@
         <v>147</v>
       </c>
       <c r="M55">
-        <v>4.3107240000000004</v>
+        <v>4.3107239999999996</v>
       </c>
       <c r="N55">
         <v>0.2288</v>
       </c>
       <c r="O55">
-        <v>0.29077599999999998</v>
+        <v>0.29077600000000003</v>
       </c>
       <c r="P55">
         <v>1.4016000000000001E-2</v>
       </c>
-      <c r="Q55" s="5" t="s">
-        <v>199</v>
+      <c r="Q55" s="5">
+        <v>4.8443159999999992</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -4794,7 +4614,7 @@
         <v>50.737554317499999</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="D56">
         <v>50.460411039999997</v>
@@ -4824,10 +4644,10 @@
         <v>75</v>
       </c>
       <c r="M56">
-        <v>3.1350720000000001</v>
-      </c>
-      <c r="N56" s="5" t="s">
-        <v>110</v>
+        <v>3.1350719999999996</v>
+      </c>
+      <c r="N56" s="5">
+        <v>1.0009999999999999</v>
       </c>
       <c r="O56">
         <v>0.107128</v>
@@ -4835,8 +4655,8 @@
       <c r="P56">
         <v>5.8692000000000001E-2</v>
       </c>
-      <c r="Q56" s="5" t="s">
-        <v>201</v>
+      <c r="Q56" s="5">
+        <v>4.3018919999999996</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -4897,10 +4717,10 @@
         <v>19</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="D58">
         <v>49.31990132</v>
@@ -4930,10 +4750,10 @@
         <v>40</v>
       </c>
       <c r="M58">
-        <v>3.396328</v>
+        <v>3.3963279999999996</v>
       </c>
       <c r="N58">
-        <v>0.82940000000000003</v>
+        <v>0.82940000000000014</v>
       </c>
       <c r="O58">
         <v>0.137736</v>
@@ -4941,8 +4761,8 @@
       <c r="P58">
         <v>9.4607999999999998E-2</v>
       </c>
-      <c r="Q58" s="5" t="s">
-        <v>204</v>
+      <c r="Q58" s="5">
+        <v>4.4580720000000005</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -4950,10 +4770,10 @@
         <v>19</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="D59">
         <v>42.700642500000001</v>
@@ -4983,7 +4803,7 @@
         <v>80</v>
       </c>
       <c r="M59">
-        <v>10.972752</v>
+        <v>10.972751999999998</v>
       </c>
       <c r="N59">
         <v>0.32890000000000003</v>
@@ -4995,7 +4815,7 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="Q59">
-        <v>11.675312</v>
+        <v>11.675311999999998</v>
       </c>
     </row>
     <row r="60" spans="1:17">
@@ -5035,8 +4855,8 @@
       <c r="L60">
         <v>5</v>
       </c>
-      <c r="M60" s="5" t="s">
-        <v>207</v>
+      <c r="M60" s="5">
+        <v>13.454683999999999</v>
       </c>
       <c r="N60">
         <v>1.573</v>
@@ -5047,8 +4867,8 @@
       <c r="P60">
         <v>5.2560000000000003E-3</v>
       </c>
-      <c r="Q60" s="5" t="s">
-        <v>208</v>
+      <c r="Q60" s="5">
+        <v>15.231891999999998</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -5056,10 +4876,10 @@
         <v>19</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>209</v>
+        <v>157</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="D61">
         <v>25.110166209999999</v>
@@ -5088,20 +4908,20 @@
       <c r="L61">
         <v>16</v>
       </c>
-      <c r="M61" s="5" t="s">
-        <v>211</v>
+      <c r="M61" s="5">
+        <v>0.65313999999999983</v>
       </c>
       <c r="N61">
-        <v>1.1153999999999999</v>
+        <v>1.1154000000000002</v>
       </c>
       <c r="O61">
-        <v>0.90293599999999996</v>
-      </c>
-      <c r="P61" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q61" s="5" t="s">
-        <v>213</v>
+        <v>0.90293600000000007</v>
+      </c>
+      <c r="P61" s="5">
+        <v>2.8908E-2</v>
+      </c>
+      <c r="Q61" s="5">
+        <v>2.7003840000000001</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -5109,10 +4929,10 @@
         <v>19</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="D62">
         <v>40.560747689999999</v>
@@ -5141,8 +4961,8 @@
       <c r="L62">
         <v>93</v>
       </c>
-      <c r="M62" s="5" t="s">
-        <v>216</v>
+      <c r="M62" s="5">
+        <v>3.5269559999999998</v>
       </c>
       <c r="N62">
         <v>1.2298</v>
@@ -5165,7 +4985,7 @@
         <v>45.376144932499997</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="D63">
         <v>45.720019999999998</v>
@@ -5195,7 +5015,7 @@
         <v>44</v>
       </c>
       <c r="M63">
-        <v>3.396328</v>
+        <v>3.3963279999999996</v>
       </c>
       <c r="N63">
         <v>0.84370000000000001</v>
@@ -5204,10 +5024,10 @@
         <v>0.18364800000000001</v>
       </c>
       <c r="P63">
-        <v>8.4972000000000006E-2</v>
-      </c>
-      <c r="Q63" s="5" t="s">
-        <v>218</v>
+        <v>8.4971999999999992E-2</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>4.5086479999999991</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -5218,7 +5038,7 @@
         <v>46.582691692499999</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="D64">
         <v>46.320895219999997</v>
@@ -5248,19 +5068,19 @@
         <v>83</v>
       </c>
       <c r="M64">
-        <v>3.0044439999999999</v>
+        <v>3.0044439999999994</v>
       </c>
       <c r="N64">
-        <v>0.31459999999999999</v>
+        <v>0.31460000000000005</v>
       </c>
       <c r="O64">
         <v>0.35964400000000002</v>
       </c>
       <c r="P64">
-        <v>6.5699999999999995E-2</v>
+        <v>6.5700000000000008E-2</v>
       </c>
       <c r="Q64">
-        <v>3.7443879999999998</v>
+        <v>3.7443879999999994</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -5271,7 +5091,7 @@
         <v>56.5917818275</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="D65">
         <v>63.589058049999998</v>
@@ -5301,7 +5121,7 @@
         <v>117</v>
       </c>
       <c r="M65">
-        <v>3.1350720000000001</v>
+        <v>3.1350719999999996</v>
       </c>
       <c r="N65">
         <v>0.98670000000000002</v>
@@ -5321,10 +5141,10 @@
         <v>20</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="D66">
         <v>43.569656350000002</v>
@@ -5357,16 +5177,16 @@
         <v>9.1439599999999999</v>
       </c>
       <c r="N66">
-        <v>0.55769999999999997</v>
+        <v>0.55770000000000008</v>
       </c>
       <c r="O66">
-        <v>0.28312399999999999</v>
-      </c>
-      <c r="P66" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q66" s="5" t="s">
-        <v>224</v>
+        <v>0.28312400000000004</v>
+      </c>
+      <c r="P66" s="5">
+        <v>3.6791999999999998E-2</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>10.021576000000001</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -5377,7 +5197,7 @@
         <v>51.510058727500002</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>225</v>
+        <v>166</v>
       </c>
       <c r="D67">
         <v>52.000143639999997</v>
@@ -5406,8 +5226,8 @@
       <c r="L67">
         <v>109</v>
       </c>
-      <c r="M67" s="5" t="s">
-        <v>226</v>
+      <c r="M67" s="5">
+        <v>7.0539119999999995</v>
       </c>
       <c r="N67">
         <v>0.18590000000000001</v>
@@ -5429,10 +5249,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3FED4FB-0BA6-8648-AB29-7B632ED59275}">
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5491,7 +5311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -5532,7 +5352,7 @@
         <v>120</v>
       </c>
       <c r="N2">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O2">
         <v>4.0156799999999997</v>
@@ -5547,38 +5367,10 @@
         <v>2.1899999999999999E-2</v>
       </c>
       <c r="S2">
-        <v>6.9944759999999997</v>
-      </c>
-      <c r="U2">
-        <f>31.698*H2/SUM(H2:M2)</f>
-        <v>2.4090480000000003</v>
-      </c>
-      <c r="V2">
-        <f>I2*20.915/SUM(H2:M2)</f>
-        <v>4.0156799999999997</v>
-      </c>
-      <c r="W2">
-        <f>J2*3.575/SUM(H2:M2)</f>
-        <v>0.44330000000000003</v>
-      </c>
-      <c r="X2">
-        <f>K2*1.913/SUM(H2:M2)</f>
-        <v>5.3564000000000001E-2</v>
-      </c>
-      <c r="Y2">
-        <f>L2*0.219/SUM(H2:M2)</f>
-        <v>2.1899999999999999E-2</v>
-      </c>
-      <c r="Z2">
-        <f>SUM(U2:Y2)</f>
-        <v>6.9434919999999991</v>
-      </c>
-      <c r="AA2">
-        <f>SUM(N2:R2)</f>
-        <v>7.0163759999999993</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27">
+        <v>7.0163759999999984</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -5619,7 +5411,7 @@
         <v>28</v>
       </c>
       <c r="N3">
-        <v>1.3062800000000001</v>
+        <v>1.3062799999999997</v>
       </c>
       <c r="O3">
         <v>10.95946</v>
@@ -5634,10 +5426,10 @@
         <v>2.0147999999999999E-2</v>
       </c>
       <c r="S3">
-        <v>12.988772000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27">
+        <v>13.00892</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -5684,19 +5476,19 @@
         <v>10.37384</v>
       </c>
       <c r="P4">
-        <v>0.41470000000000001</v>
+        <v>0.41470000000000007</v>
       </c>
       <c r="Q4">
-        <v>0.28312399999999999</v>
+        <v>0.28312400000000004</v>
       </c>
       <c r="R4">
         <v>2.8908E-2</v>
       </c>
       <c r="S4">
-        <v>13.161712</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
+        <v>13.190619999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -5737,7 +5529,7 @@
         <v>41</v>
       </c>
       <c r="N5">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O5">
         <v>8.2823399999999996</v>
@@ -5752,14 +5544,10 @@
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="S5">
-        <v>11.573484000000001</v>
-      </c>
-      <c r="U5">
-        <f>N2*SUM(H2:M2)/H2</f>
-        <v>32.657000000000004</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
+        <v>11.591003999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5800,25 +5588,25 @@
         <v>40</v>
       </c>
       <c r="N6">
-        <v>0.65314000000000005</v>
+        <v>0.65313999999999983</v>
       </c>
       <c r="O6">
-        <v>11.712400000000001</v>
+        <v>11.712399999999999</v>
       </c>
       <c r="P6">
-        <v>0.20019999999999999</v>
+        <v>0.20020000000000002</v>
       </c>
       <c r="Q6">
-        <v>0.15304000000000001</v>
+        <v>0.15303999999999998</v>
       </c>
       <c r="R6">
         <v>2.7156E-2</v>
       </c>
       <c r="S6">
-        <v>12.718780000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27">
+        <v>12.745936</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -5859,10 +5647,10 @@
         <v>58</v>
       </c>
       <c r="N7">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O7">
-        <v>7.6130599999999999</v>
+        <v>7.6130599999999991</v>
       </c>
       <c r="P7">
         <v>0.25740000000000002</v>
@@ -5874,10 +5662,10 @@
         <v>1.3140000000000001E-2</v>
       </c>
       <c r="S7">
-        <v>10.72734</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
+        <v>10.740479999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -5918,7 +5706,7 @@
         <v>37</v>
       </c>
       <c r="N8">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O8">
         <v>7.8640400000000001</v>
@@ -5933,10 +5721,10 @@
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="S8">
-        <v>11.16422</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27">
+        <v>11.18174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -5992,10 +5780,10 @@
         <v>2.3651999999999999E-2</v>
       </c>
       <c r="S9">
-        <v>10.489127999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27">
+        <v>10.512779999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -6042,7 +5830,7 @@
         <v>7.4457399999999998</v>
       </c>
       <c r="P10">
-        <v>0.31459999999999999</v>
+        <v>0.31460000000000005</v>
       </c>
       <c r="Q10">
         <v>0.31373200000000001</v>
@@ -6051,10 +5839,10 @@
         <v>2.5403999999999999E-2</v>
       </c>
       <c r="S10">
-        <v>9.9028639999999992</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27">
+        <v>9.928268000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -6095,7 +5883,7 @@
         <v>55</v>
       </c>
       <c r="N11">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O11">
         <v>7.3620799999999997</v>
@@ -6110,10 +5898,10 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="S11">
-        <v>10.567804000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27">
+        <v>10.581819999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -6157,7 +5945,7 @@
         <v>2.3513039999999998</v>
       </c>
       <c r="O12">
-        <v>7.69672</v>
+        <v>7.6967199999999991</v>
       </c>
       <c r="P12">
         <v>0.50049999999999994</v>
@@ -6169,10 +5957,10 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="S12">
-        <v>10.808692000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27">
+        <v>10.822707999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -6213,7 +6001,7 @@
         <v>97</v>
       </c>
       <c r="N13">
-        <v>1.3062800000000001</v>
+        <v>1.3062799999999997</v>
       </c>
       <c r="O13">
         <v>5.6888800000000002</v>
@@ -6228,10 +6016,10 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="S13">
-        <v>7.6194759999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
+        <v>7.6334920000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -6272,10 +6060,10 @@
         <v>161</v>
       </c>
       <c r="N14">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O14">
-        <v>0.41830000000000001</v>
+        <v>0.41829999999999995</v>
       </c>
       <c r="P14">
         <v>0.45760000000000001</v>
@@ -6287,10 +6075,10 @@
         <v>1.0512000000000001E-2</v>
       </c>
       <c r="S14">
-        <v>3.5185240000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27">
+        <v>3.5290359999999992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -6331,7 +6119,7 @@
         <v>76</v>
       </c>
       <c r="N15">
-        <v>0.65314000000000005</v>
+        <v>0.65313999999999983</v>
       </c>
       <c r="O15">
         <v>8.0313599999999994</v>
@@ -6340,16 +6128,16 @@
         <v>0.30030000000000001</v>
       </c>
       <c r="Q15">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="R15">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="S15">
-        <v>9.3291400000000007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27">
+        <v>9.3352719999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -6396,16 +6184,16 @@
         <v>8.7006399999999999</v>
       </c>
       <c r="P16">
-        <v>0.1716</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="Q16">
         <v>0.374948</v>
       </c>
       <c r="R16">
-        <v>3.9419999999999997E-2</v>
+        <v>3.9420000000000004E-2</v>
       </c>
       <c r="S16">
-        <v>11.598492</v>
+        <v>11.637911999999998</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -6461,10 +6249,10 @@
         <v>0.36729600000000001</v>
       </c>
       <c r="R17">
-        <v>3.8544000000000002E-2</v>
+        <v>3.8543999999999995E-2</v>
       </c>
       <c r="S17">
-        <v>9.8770919999999993</v>
+        <v>9.9156359999999992</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -6508,7 +6296,7 @@
         <v>66</v>
       </c>
       <c r="N18">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O18">
         <v>7.4457399999999998</v>
@@ -6523,7 +6311,7 @@
         <v>1.5768000000000001E-2</v>
       </c>
       <c r="S18">
-        <v>10.431319999999999</v>
+        <v>10.447087999999999</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -6573,16 +6361,16 @@
         <v>9.3699200000000005</v>
       </c>
       <c r="P19">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="Q19">
-        <v>0.28312399999999999</v>
+        <v>0.28312400000000004</v>
       </c>
       <c r="R19">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="S19">
-        <v>12.347548</v>
+        <v>12.362439999999999</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -6626,7 +6414,7 @@
         <v>38</v>
       </c>
       <c r="N20">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O20">
         <v>7.8640400000000001</v>
@@ -6635,13 +6423,13 @@
         <v>0.32890000000000003</v>
       </c>
       <c r="Q20">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="R20">
         <v>2.7156E-2</v>
       </c>
       <c r="S20">
-        <v>11.019212</v>
+        <v>11.046368000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -6691,16 +6479,16 @@
         <v>8.5333199999999998</v>
       </c>
       <c r="P21">
-        <v>0.1716</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="Q21">
         <v>0.27547199999999999</v>
       </c>
       <c r="R21">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="S21">
-        <v>11.331696000000001</v>
+        <v>11.356223999999999</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -6744,7 +6532,7 @@
         <v>50</v>
       </c>
       <c r="N22">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O22">
         <v>7.8640400000000001</v>
@@ -6756,10 +6544,10 @@
         <v>0.27547199999999999</v>
       </c>
       <c r="R22">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="S22">
-        <v>10.950343999999999</v>
+        <v>10.974872000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -6803,13 +6591,13 @@
         <v>35</v>
       </c>
       <c r="N23">
-        <v>1.567536</v>
+        <v>1.5675359999999998</v>
       </c>
       <c r="O23">
         <v>8.0313599999999994</v>
       </c>
       <c r="P23">
-        <v>0.31459999999999999</v>
+        <v>0.31460000000000005</v>
       </c>
       <c r="Q23">
         <v>0.35199200000000003</v>
@@ -6818,7 +6606,7 @@
         <v>3.4164E-2</v>
       </c>
       <c r="S23">
-        <v>10.265488</v>
+        <v>10.299652</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -6862,22 +6650,22 @@
         <v>59</v>
       </c>
       <c r="N24">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O24">
         <v>6.7764600000000002</v>
       </c>
       <c r="P24">
-        <v>0.40039999999999998</v>
+        <v>0.40040000000000003</v>
       </c>
       <c r="Q24">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="R24">
         <v>1.5768000000000001E-2</v>
       </c>
       <c r="S24">
-        <v>10.003132000000001</v>
+        <v>10.0189</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -6921,13 +6709,13 @@
         <v>40</v>
       </c>
       <c r="N25">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O25">
         <v>7.7803800000000001</v>
       </c>
       <c r="P25">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="Q25">
         <v>0.329036</v>
@@ -6936,7 +6724,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="S25">
-        <v>10.934547999999999</v>
+        <v>10.961703999999999</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -6983,7 +6771,7 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O26">
-        <v>7.6130599999999999</v>
+        <v>7.6130599999999991</v>
       </c>
       <c r="P26">
         <v>0.37180000000000002</v>
@@ -6995,7 +6783,7 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="S26">
-        <v>10.557528</v>
+        <v>10.571543999999998</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -7042,10 +6830,10 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O27">
-        <v>7.69672</v>
+        <v>7.6967199999999991</v>
       </c>
       <c r="P27">
-        <v>0.41470000000000001</v>
+        <v>0.41470000000000007</v>
       </c>
       <c r="Q27">
         <v>0.27547199999999999</v>
@@ -7054,7 +6842,7 @@
         <v>3.4164E-2</v>
       </c>
       <c r="S27">
-        <v>10.607568000000001</v>
+        <v>10.641732000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -7098,7 +6886,7 @@
         <v>49</v>
       </c>
       <c r="N28">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O28">
         <v>7.9477000000000002</v>
@@ -7113,7 +6901,7 @@
         <v>1.8395999999999999E-2</v>
       </c>
       <c r="S28">
-        <v>11.060976</v>
+        <v>11.079371999999998</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -7157,7 +6945,7 @@
         <v>56</v>
       </c>
       <c r="N29">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O29">
         <v>7.2784199999999997</v>
@@ -7172,7 +6960,7 @@
         <v>1.0512000000000001E-2</v>
       </c>
       <c r="S29">
-        <v>10.574584</v>
+        <v>10.585096</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -7231,7 +7019,7 @@
         <v>2.5403999999999999E-2</v>
       </c>
       <c r="S30">
-        <v>8.9859679999999997</v>
+        <v>9.0113719999999979</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -7275,13 +7063,13 @@
         <v>25</v>
       </c>
       <c r="N31">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O31">
-        <v>7.6130599999999999</v>
+        <v>7.6130599999999991</v>
       </c>
       <c r="P31">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="Q31">
         <v>0.374948</v>
@@ -7290,7 +7078,7 @@
         <v>3.6791999999999998E-2</v>
       </c>
       <c r="S31">
-        <v>10.813140000000001</v>
+        <v>10.849931999999997</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -7340,7 +7128,7 @@
         <v>8.1986799999999995</v>
       </c>
       <c r="P32">
-        <v>0.20019999999999999</v>
+        <v>0.20020000000000002</v>
       </c>
       <c r="Q32">
         <v>0.36729600000000001</v>
@@ -7349,7 +7137,7 @@
         <v>3.1536000000000002E-2</v>
       </c>
       <c r="S32">
-        <v>10.986852000000001</v>
+        <v>11.018388</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -7402,13 +7190,13 @@
         <v>0.2717</v>
       </c>
       <c r="Q33">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="R33">
         <v>3.5040000000000002E-2</v>
       </c>
       <c r="S33">
-        <v>10.0212</v>
+        <v>10.056240000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -7458,7 +7246,7 @@
         <v>7.4457399999999998</v>
       </c>
       <c r="P34">
-        <v>0.20019999999999999</v>
+        <v>0.20020000000000002</v>
       </c>
       <c r="Q34">
         <v>0.31373200000000001</v>
@@ -7467,7 +7255,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="S34">
-        <v>10.180348</v>
+        <v>10.196992</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -7523,10 +7311,10 @@
         <v>0.26016800000000001</v>
       </c>
       <c r="R35">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="S35">
-        <v>10.141083999999999</v>
+        <v>10.165611999999999</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -7570,7 +7358,7 @@
         <v>60</v>
       </c>
       <c r="N36">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O36">
         <v>5.7725400000000002</v>
@@ -7582,10 +7370,10 @@
         <v>0.374948</v>
       </c>
       <c r="R36">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="S36">
-        <v>9.1442200000000007</v>
+        <v>9.1591119999999986</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -7641,10 +7429,10 @@
         <v>0.137736</v>
       </c>
       <c r="R37">
-        <v>3.8544000000000002E-2</v>
+        <v>3.8543999999999995E-2</v>
       </c>
       <c r="S37">
-        <v>10.116612</v>
+        <v>10.155156</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -7703,7 +7491,7 @@
         <v>4.2048000000000002E-2</v>
       </c>
       <c r="S38">
-        <v>11.790304000000001</v>
+        <v>11.832351999999998</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -7756,13 +7544,13 @@
         <v>0.2145</v>
       </c>
       <c r="Q39">
-        <v>0.14538799999999999</v>
+        <v>0.14538800000000002</v>
       </c>
       <c r="R39">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="S39">
-        <v>10.899596000000001</v>
+        <v>10.918868</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -7818,10 +7606,10 @@
         <v>0.26016800000000001</v>
       </c>
       <c r="R40">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="S40">
-        <v>10.29834</v>
+        <v>10.322868000000001</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -7880,7 +7668,7 @@
         <v>4.2923999999999997E-2</v>
       </c>
       <c r="S41">
-        <v>10.491496</v>
+        <v>10.534419999999997</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -7930,16 +7718,16 @@
         <v>8.2823399999999996</v>
       </c>
       <c r="P42">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="Q42">
         <v>0.244864</v>
       </c>
       <c r="R42">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="S42">
-        <v>11.221708</v>
+        <v>11.227839999999999</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -7989,7 +7777,7 @@
         <v>8.1986799999999995</v>
       </c>
       <c r="P43">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="Q43">
         <v>0.244864</v>
@@ -7998,7 +7786,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="S43">
-        <v>11.00742</v>
+        <v>11.01618</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -8045,10 +7833,10 @@
         <v>2.3513039999999998</v>
       </c>
       <c r="O44">
-        <v>4.8522800000000004</v>
+        <v>4.8522799999999995</v>
       </c>
       <c r="P44">
-        <v>0.1716</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="Q44">
         <v>0.137736</v>
@@ -8057,7 +7845,7 @@
         <v>7.8840000000000004E-3</v>
       </c>
       <c r="S44">
-        <v>7.5129200000000003</v>
+        <v>7.5208039999999992</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -8107,7 +7895,7 @@
         <v>7.8640400000000001</v>
       </c>
       <c r="P45">
-        <v>0.1573</v>
+        <v>0.15730000000000002</v>
       </c>
       <c r="Q45">
         <v>0.321384</v>
@@ -8116,7 +7904,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="S45">
-        <v>10.5634</v>
+        <v>10.580043999999999</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -8163,7 +7951,7 @@
         <v>2.3513039999999998</v>
       </c>
       <c r="O46">
-        <v>6.6928000000000001</v>
+        <v>6.6927999999999992</v>
       </c>
       <c r="P46">
         <v>0.24310000000000001</v>
@@ -8175,7 +7963,7 @@
         <v>1.1388000000000001E-2</v>
       </c>
       <c r="S46">
-        <v>9.5626759999999997</v>
+        <v>9.5740639999999999</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -8234,7 +8022,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="S47">
-        <v>9.2339680000000008</v>
+        <v>9.2611240000000006</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -8293,7 +8081,7 @@
         <v>2.5403999999999999E-2</v>
       </c>
       <c r="S48">
-        <v>10.659328</v>
+        <v>10.684731999999999</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -8352,7 +8140,7 @@
         <v>2.6280000000000001E-2</v>
       </c>
       <c r="S49">
-        <v>10.168787999999999</v>
+        <v>10.195067999999999</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -8411,7 +8199,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="S50">
-        <v>10.157031999999999</v>
+        <v>10.165792000000001</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -8458,7 +8246,7 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O51">
-        <v>7.69672</v>
+        <v>7.6967199999999991</v>
       </c>
       <c r="P51">
         <v>0.25740000000000002</v>
@@ -8470,7 +8258,7 @@
         <v>1.3140000000000001E-2</v>
       </c>
       <c r="S51">
-        <v>10.549744</v>
+        <v>10.562884</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -8517,7 +8305,7 @@
         <v>2.3513039999999998</v>
       </c>
       <c r="O52">
-        <v>7.1111000000000004</v>
+        <v>7.1110999999999995</v>
       </c>
       <c r="P52">
         <v>0.44330000000000003</v>
@@ -8529,7 +8317,7 @@
         <v>1.5768000000000001E-2</v>
       </c>
       <c r="S52">
-        <v>10.15822</v>
+        <v>10.173988</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -8573,7 +8361,7 @@
         <v>66</v>
       </c>
       <c r="N53">
-        <v>1.3062800000000001</v>
+        <v>1.3062799999999997</v>
       </c>
       <c r="O53">
         <v>7.2784199999999997</v>
@@ -8585,10 +8373,10 @@
         <v>0.25251600000000002</v>
       </c>
       <c r="R53">
-        <v>3.2412000000000003E-2</v>
+        <v>3.2411999999999996E-2</v>
       </c>
       <c r="S53">
-        <v>9.0803159999999998</v>
+        <v>9.1127280000000006</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -8635,19 +8423,19 @@
         <v>2.3513039999999998</v>
       </c>
       <c r="O54">
-        <v>7.1111000000000004</v>
+        <v>7.1110999999999995</v>
       </c>
       <c r="P54">
         <v>0.45760000000000001</v>
       </c>
       <c r="Q54">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="R54">
         <v>1.8395999999999999E-2</v>
       </c>
       <c r="S54">
-        <v>10.264343999999999</v>
+        <v>10.282739999999999</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -8691,7 +8479,7 @@
         <v>45</v>
       </c>
       <c r="N55">
-        <v>1.4369080000000001</v>
+        <v>1.4369079999999999</v>
       </c>
       <c r="O55">
         <v>9.3699200000000005</v>
@@ -8700,13 +8488,13 @@
         <v>0.2288</v>
       </c>
       <c r="Q55">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="R55">
         <v>1.8395999999999999E-2</v>
       </c>
       <c r="S55">
-        <v>11.379968</v>
+        <v>11.398363999999999</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -8762,10 +8550,10 @@
         <v>0.13008400000000001</v>
       </c>
       <c r="R56">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="S56">
-        <v>10.274139999999999</v>
+        <v>10.280272</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -8809,13 +8597,13 @@
         <v>56</v>
       </c>
       <c r="N57">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O57">
-        <v>6.9437800000000003</v>
+        <v>6.9437799999999994</v>
       </c>
       <c r="P57">
-        <v>0.62919999999999998</v>
+        <v>0.62920000000000009</v>
       </c>
       <c r="Q57">
         <v>0.329036</v>
@@ -8824,7 +8612,7 @@
         <v>4.3800000000000002E-3</v>
       </c>
       <c r="S57">
-        <v>10.383948</v>
+        <v>10.388328</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -8871,7 +8659,7 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O58">
-        <v>7.6130599999999999</v>
+        <v>7.6130599999999991</v>
       </c>
       <c r="P58">
         <v>0.57199999999999995</v>
@@ -8883,7 +8671,7 @@
         <v>3.3287999999999998E-2</v>
       </c>
       <c r="S58">
-        <v>10.543472</v>
+        <v>10.576759999999998</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -8942,7 +8730,7 @@
         <v>3.5040000000000002E-2</v>
       </c>
       <c r="S59">
-        <v>10.4625</v>
+        <v>10.497539999999999</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -8998,10 +8786,10 @@
         <v>0.35964400000000002</v>
       </c>
       <c r="R60">
-        <v>1.2264000000000001E-2</v>
+        <v>1.2263999999999999E-2</v>
       </c>
       <c r="S60">
-        <v>9.0714159999999993</v>
+        <v>9.0836799999999993</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -9051,7 +8839,7 @@
         <v>7.2784199999999997</v>
       </c>
       <c r="P61">
-        <v>0.20019999999999999</v>
+        <v>0.20020000000000002</v>
       </c>
       <c r="Q61">
         <v>0.31373200000000001</v>
@@ -9060,7 +8848,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="S61">
-        <v>10.013028</v>
+        <v>10.029672</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -9104,7 +8892,7 @@
         <v>49</v>
       </c>
       <c r="N62">
-        <v>1.698164</v>
+        <v>1.6981639999999998</v>
       </c>
       <c r="O62">
         <v>8.5333199999999998</v>
@@ -9119,7 +8907,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="S62">
-        <v>10.805248000000001</v>
+        <v>10.832404</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -9175,10 +8963,10 @@
         <v>0.27547199999999999</v>
       </c>
       <c r="R63">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="S63">
-        <v>10.02576</v>
+        <v>10.045032000000001</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -9237,7 +9025,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="S64">
-        <v>10.09226</v>
+        <v>10.119415999999999</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -9293,10 +9081,10 @@
         <v>0.1913</v>
       </c>
       <c r="R65">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="S65">
-        <v>8.5906559999999992</v>
+        <v>8.6151840000000011</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -9349,13 +9137,13 @@
         <v>0.58630000000000004</v>
       </c>
       <c r="Q66">
-        <v>0.30608000000000002</v>
+        <v>0.30607999999999996</v>
       </c>
       <c r="R66">
         <v>2.1024000000000001E-2</v>
       </c>
       <c r="S66">
-        <v>10.558795999999999</v>
+        <v>10.57982</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -9399,13 +9187,13 @@
         <v>56</v>
       </c>
       <c r="N67">
-        <v>1.698164</v>
+        <v>1.6981639999999998</v>
       </c>
       <c r="O67">
         <v>8.3659999999999997</v>
       </c>
       <c r="P67">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="Q67">
         <v>0.25251600000000002</v>
@@ -9414,7 +9202,7 @@
         <v>2.1024000000000001E-2</v>
       </c>
       <c r="S67">
-        <v>10.659879999999999</v>
+        <v>10.680904</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -9458,13 +9246,13 @@
         <v>79</v>
       </c>
       <c r="N68">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O68">
-        <v>0.41830000000000001</v>
+        <v>0.41829999999999995</v>
       </c>
       <c r="P68">
-        <v>0.70069999999999999</v>
+        <v>0.7007000000000001</v>
       </c>
       <c r="Q68">
         <v>0.374948</v>
@@ -9473,7 +9261,7 @@
         <v>4.2923999999999997E-2</v>
       </c>
       <c r="S68">
-        <v>3.9758800000000001</v>
+        <v>4.0188039999999994</v>
       </c>
     </row>
     <row r="69" spans="1:19">
@@ -9523,7 +9311,7 @@
         <v>7.7803800000000001</v>
       </c>
       <c r="P69">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="Q69">
         <v>0.36729600000000001</v>
@@ -9532,7 +9320,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="S69">
-        <v>10.842180000000001</v>
+        <v>10.869335999999999</v>
       </c>
     </row>
     <row r="70" spans="1:19">
@@ -9579,7 +9367,7 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O70">
-        <v>7.1111000000000004</v>
+        <v>7.1110999999999995</v>
       </c>
       <c r="P70">
         <v>0.2145</v>
@@ -9591,7 +9379,7 @@
         <v>2.1024000000000001E-2</v>
       </c>
       <c r="S70">
-        <v>9.8064440000000008</v>
+        <v>9.8274679999999996</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -9644,13 +9432,13 @@
         <v>0.51480000000000004</v>
       </c>
       <c r="Q71">
-        <v>0.29842800000000003</v>
+        <v>0.29842799999999997</v>
       </c>
       <c r="R71">
-        <v>3.2412000000000003E-2</v>
+        <v>3.2411999999999996E-2</v>
       </c>
       <c r="S71">
-        <v>10.563304</v>
+        <v>10.595715999999999</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -9697,7 +9485,7 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O72">
-        <v>7.6130599999999999</v>
+        <v>7.6130599999999991</v>
       </c>
       <c r="P72">
         <v>0.42899999999999999</v>
@@ -9709,7 +9497,7 @@
         <v>2.8032000000000001E-2</v>
       </c>
       <c r="S72">
-        <v>10.476991999999999</v>
+        <v>10.505023999999999</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -9753,7 +9541,7 @@
         <v>32</v>
       </c>
       <c r="N73">
-        <v>1.698164</v>
+        <v>1.6981639999999998</v>
       </c>
       <c r="O73">
         <v>8.7006399999999999</v>
@@ -9768,7 +9556,7 @@
         <v>4.1172E-2</v>
       </c>
       <c r="S73">
-        <v>10.964916000000001</v>
+        <v>11.006088</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -9815,7 +9603,7 @@
         <v>2.3513039999999998</v>
       </c>
       <c r="O74">
-        <v>6.9437800000000003</v>
+        <v>6.9437799999999994</v>
       </c>
       <c r="P74">
         <v>0.37180000000000002</v>
@@ -9827,7 +9615,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="S74">
-        <v>9.9959199999999999</v>
+        <v>10.00468</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -9886,7 +9674,7 @@
         <v>3.4164E-2</v>
       </c>
       <c r="S75">
-        <v>8.7899320000000003</v>
+        <v>8.8240960000000008</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -9930,7 +9718,7 @@
         <v>55</v>
       </c>
       <c r="N76">
-        <v>1.698164</v>
+        <v>1.6981639999999998</v>
       </c>
       <c r="O76">
         <v>8.7006399999999999</v>
@@ -9942,10 +9730,10 @@
         <v>0.23721200000000001</v>
       </c>
       <c r="R76">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="S76">
-        <v>10.993516</v>
+        <v>11.012788</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -9989,7 +9777,7 @@
         <v>154</v>
       </c>
       <c r="N77">
-        <v>1.567536</v>
+        <v>1.5675359999999998</v>
       </c>
       <c r="O77">
         <v>4.35032</v>
@@ -9998,13 +9786,13 @@
         <v>7.1499999999999994E-2</v>
       </c>
       <c r="Q77">
-        <v>0.11477999999999999</v>
+        <v>0.11478000000000001</v>
       </c>
       <c r="R77">
         <v>1.0512000000000001E-2</v>
       </c>
       <c r="S77">
-        <v>6.1041359999999996</v>
+        <v>6.1146479999999999</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -10054,7 +9842,7 @@
         <v>7.3620799999999997</v>
       </c>
       <c r="P78">
-        <v>0.1716</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="Q78">
         <v>0.13008400000000001</v>
@@ -10063,7 +9851,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="S78">
-        <v>9.8844399999999997</v>
+        <v>9.8932000000000002</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -10107,7 +9895,7 @@
         <v>76</v>
       </c>
       <c r="N79">
-        <v>1.567536</v>
+        <v>1.5675359999999998</v>
       </c>
       <c r="O79">
         <v>5.4379</v>
@@ -10122,7 +9910,7 @@
         <v>2.8032000000000001E-2</v>
       </c>
       <c r="S79">
-        <v>7.7155519999999997</v>
+        <v>7.7435839999999994</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -10175,13 +9963,13 @@
         <v>0.45760000000000001</v>
       </c>
       <c r="Q80">
-        <v>0.14538799999999999</v>
+        <v>0.14538800000000002</v>
       </c>
       <c r="R80">
         <v>4.2048000000000002E-2</v>
       </c>
       <c r="S80">
-        <v>10.212160000000001</v>
+        <v>10.254208</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -10240,7 +10028,7 @@
         <v>3.1536000000000002E-2</v>
       </c>
       <c r="S81">
-        <v>10.202351999999999</v>
+        <v>10.233887999999999</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -10284,7 +10072,7 @@
         <v>41</v>
       </c>
       <c r="N82">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O82">
         <v>8.5333199999999998</v>
@@ -10299,7 +10087,7 @@
         <v>3.066E-2</v>
       </c>
       <c r="S82">
-        <v>11.560416</v>
+        <v>11.591075999999999</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -10358,7 +10146,7 @@
         <v>2.6280000000000001E-2</v>
       </c>
       <c r="S83">
-        <v>10.470508000000001</v>
+        <v>10.496787999999999</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -10417,7 +10205,7 @@
         <v>3.3287999999999998E-2</v>
       </c>
       <c r="S84">
-        <v>9.9861880000000003</v>
+        <v>10.019476000000001</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -10464,7 +10252,7 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O85">
-        <v>7.69672</v>
+        <v>7.6967199999999991</v>
       </c>
       <c r="P85">
         <v>0.28599999999999998</v>
@@ -10473,10 +10261,10 @@
         <v>0.26782</v>
       </c>
       <c r="R85">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="S85">
-        <v>10.471216</v>
+        <v>10.480852000000001</v>
       </c>
     </row>
     <row r="86" spans="1:19">
@@ -10520,7 +10308,7 @@
         <v>44</v>
       </c>
       <c r="N86">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O86">
         <v>7.3620799999999997</v>
@@ -10535,7 +10323,7 @@
         <v>2.8032000000000001E-2</v>
       </c>
       <c r="S86">
-        <v>10.489656</v>
+        <v>10.517687999999998</v>
       </c>
     </row>
     <row r="87" spans="1:19">
@@ -10582,19 +10370,19 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O87">
-        <v>6.1908399999999997</v>
+        <v>6.1908400000000006</v>
       </c>
       <c r="P87">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="Q87">
-        <v>0.15304000000000001</v>
+        <v>0.15303999999999998</v>
       </c>
       <c r="R87">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="S87">
-        <v>8.6503560000000004</v>
+        <v>8.6652480000000018</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -10638,10 +10426,10 @@
         <v>44</v>
       </c>
       <c r="N88">
-        <v>1.698164</v>
+        <v>1.6981639999999998</v>
       </c>
       <c r="O88">
-        <v>8.9516200000000001</v>
+        <v>8.9516199999999984</v>
       </c>
       <c r="P88">
         <v>0.32890000000000003</v>
@@ -10653,7 +10441,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="S88">
-        <v>11.223547999999999</v>
+        <v>11.250703999999999</v>
       </c>
     </row>
     <row r="89" spans="1:19">
@@ -10700,10 +10488,10 @@
         <v>2.3513039999999998</v>
       </c>
       <c r="O89">
-        <v>6.1908399999999997</v>
+        <v>6.1908400000000006</v>
       </c>
       <c r="P89">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="Q89">
         <v>0.1913</v>
@@ -10712,7 +10500,7 @@
         <v>2.2776000000000001E-2</v>
       </c>
       <c r="S89">
-        <v>8.8192439999999994</v>
+        <v>8.8420200000000015</v>
       </c>
     </row>
     <row r="90" spans="1:19">
@@ -10759,7 +10547,7 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O90">
-        <v>7.69672</v>
+        <v>7.6967199999999991</v>
       </c>
       <c r="P90">
         <v>0.25740000000000002</v>
@@ -10771,7 +10559,7 @@
         <v>2.6280000000000001E-2</v>
       </c>
       <c r="S90">
-        <v>10.450267999999999</v>
+        <v>10.476548000000001</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -10830,7 +10618,7 @@
         <v>1.8395999999999999E-2</v>
       </c>
       <c r="S91">
-        <v>10.621736</v>
+        <v>10.640131999999999</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -10874,22 +10662,22 @@
         <v>73</v>
       </c>
       <c r="N92">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O92">
-        <v>7.69672</v>
+        <v>7.6967199999999991</v>
       </c>
       <c r="P92">
-        <v>0.40039999999999998</v>
+        <v>0.40040000000000003</v>
       </c>
       <c r="Q92">
         <v>0.18364800000000001</v>
       </c>
       <c r="R92">
-        <v>1.2264000000000001E-2</v>
+        <v>1.2263999999999999E-2</v>
       </c>
       <c r="S92">
-        <v>10.762700000000001</v>
+        <v>10.774963999999999</v>
       </c>
     </row>
     <row r="93" spans="1:19">
@@ -10933,7 +10721,7 @@
         <v>21</v>
       </c>
       <c r="N93">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O93">
         <v>7.2784199999999997</v>
@@ -10948,7 +10736,7 @@
         <v>2.7156E-2</v>
       </c>
       <c r="S93">
-        <v>10.7502</v>
+        <v>10.777355999999999</v>
       </c>
     </row>
     <row r="94" spans="1:19">
@@ -10995,10 +10783,10 @@
         <v>2.3513039999999998</v>
       </c>
       <c r="O94">
-        <v>6.9437800000000003</v>
+        <v>6.9437799999999994</v>
       </c>
       <c r="P94">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="Q94">
         <v>0.33668799999999999</v>
@@ -11007,7 +10795,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="S94">
-        <v>9.9749719999999993</v>
+        <v>9.9837319999999998</v>
       </c>
     </row>
     <row r="95" spans="1:19">
@@ -11054,7 +10842,7 @@
         <v>1.045024</v>
       </c>
       <c r="O95">
-        <v>3.84836</v>
+        <v>3.8483599999999996</v>
       </c>
       <c r="P95">
         <v>0.1144</v>
@@ -11066,7 +10854,7 @@
         <v>4.0295999999999998E-2</v>
       </c>
       <c r="S95">
-        <v>5.1684760000000001</v>
+        <v>5.2087719999999988</v>
       </c>
     </row>
     <row r="96" spans="1:19">
@@ -11119,13 +10907,13 @@
         <v>0.42899999999999999</v>
       </c>
       <c r="Q96">
-        <v>0.28312399999999999</v>
+        <v>0.28312400000000004</v>
       </c>
       <c r="R96">
         <v>1.5768000000000001E-2</v>
       </c>
       <c r="S96">
-        <v>12.219060000000001</v>
+        <v>12.234828</v>
       </c>
     </row>
     <row r="97" spans="1:19">
@@ -11184,7 +10972,7 @@
         <v>2.3651999999999999E-2</v>
       </c>
       <c r="S97">
-        <v>9.5787279999999999</v>
+        <v>9.6023800000000001</v>
       </c>
     </row>
     <row r="98" spans="1:19">
@@ -11234,7 +11022,7 @@
         <v>7.4457399999999998</v>
       </c>
       <c r="P98">
-        <v>0.68640000000000001</v>
+        <v>0.68640000000000012</v>
       </c>
       <c r="Q98">
         <v>0.122432</v>
@@ -11243,7 +11031,7 @@
         <v>2.3651999999999999E-2</v>
       </c>
       <c r="S98">
-        <v>10.083364</v>
+        <v>10.107016000000002</v>
       </c>
     </row>
     <row r="99" spans="1:19">
@@ -11290,7 +11078,7 @@
         <v>1.1756519999999999</v>
       </c>
       <c r="O99">
-        <v>11.21044</v>
+        <v>11.210439999999998</v>
       </c>
       <c r="P99">
         <v>0.2288</v>
@@ -11302,7 +11090,7 @@
         <v>7.0080000000000003E-3</v>
       </c>
       <c r="S99">
-        <v>12.829148</v>
+        <v>12.836155999999999</v>
       </c>
     </row>
     <row r="100" spans="1:19">
@@ -11346,7 +11134,7 @@
         <v>23</v>
       </c>
       <c r="N100">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O100">
         <v>9.3699200000000005</v>
@@ -11361,7 +11149,7 @@
         <v>2.8908E-2</v>
       </c>
       <c r="S100">
-        <v>12.466888000000001</v>
+        <v>12.495796</v>
       </c>
     </row>
     <row r="101" spans="1:19">
@@ -11411,16 +11199,16 @@
         <v>7.2784199999999997</v>
       </c>
       <c r="P101">
-        <v>0.55769999999999997</v>
+        <v>0.55770000000000008</v>
       </c>
       <c r="Q101">
-        <v>0.29077599999999998</v>
+        <v>0.29077600000000003</v>
       </c>
       <c r="R101">
         <v>2.7156E-2</v>
       </c>
       <c r="S101">
-        <v>10.347572</v>
+        <v>10.374727999999999</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -11473,13 +11261,13 @@
         <v>0.58630000000000004</v>
       </c>
       <c r="Q102">
-        <v>0.29077599999999998</v>
+        <v>0.29077600000000003</v>
       </c>
       <c r="R102">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="S102">
-        <v>5.2729119999999998</v>
+        <v>5.302696000000001</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -11532,13 +11320,13 @@
         <v>0.25740000000000002</v>
       </c>
       <c r="Q103">
-        <v>0.29842800000000003</v>
+        <v>0.29842799999999997</v>
       </c>
       <c r="R103">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="S103">
-        <v>9.6835920000000009</v>
+        <v>9.6932279999999995</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -11582,7 +11370,7 @@
         <v>79</v>
       </c>
       <c r="N104">
-        <v>2.481932</v>
+        <v>2.4819319999999996</v>
       </c>
       <c r="O104">
         <v>7.1947599999999996</v>
@@ -11597,7 +11385,7 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="S104">
-        <v>10.165660000000001</v>
+        <v>10.179675999999999</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -11656,7 +11444,7 @@
         <v>2.5403999999999999E-2</v>
       </c>
       <c r="S105">
-        <v>10.506308000000001</v>
+        <v>10.531711999999999</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -11706,16 +11494,16 @@
         <v>7.3620799999999997</v>
       </c>
       <c r="P106">
-        <v>0.31459999999999999</v>
+        <v>0.31460000000000005</v>
       </c>
       <c r="Q106">
         <v>0.26016800000000001</v>
       </c>
       <c r="R106">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="S106">
-        <v>10.288152</v>
+        <v>10.303044</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -11762,7 +11550,7 @@
         <v>2.2206760000000001</v>
       </c>
       <c r="O107">
-        <v>6.1908399999999997</v>
+        <v>6.1908400000000006</v>
       </c>
       <c r="P107">
         <v>0.32890000000000003</v>
@@ -11774,7 +11562,7 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="S107">
-        <v>9.1000599999999991</v>
+        <v>9.1140760000000007</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -11821,19 +11609,19 @@
         <v>1.828792</v>
       </c>
       <c r="O108">
-        <v>7.69672</v>
+        <v>7.6967199999999991</v>
       </c>
       <c r="P108">
-        <v>0.40039999999999998</v>
+        <v>0.40040000000000003</v>
       </c>
       <c r="Q108">
         <v>0.27547199999999999</v>
       </c>
       <c r="R108">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="S108">
-        <v>10.201383999999999</v>
+        <v>10.225911999999999</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -11877,7 +11665,7 @@
         <v>56</v>
       </c>
       <c r="N109">
-        <v>1.698164</v>
+        <v>1.6981639999999998</v>
       </c>
       <c r="O109">
         <v>8.1986799999999995</v>
@@ -11892,7 +11680,7 @@
         <v>2.6280000000000001E-2</v>
       </c>
       <c r="S109">
-        <v>10.435359999999999</v>
+        <v>10.461639999999999</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -11948,10 +11736,10 @@
         <v>0.26016800000000001</v>
       </c>
       <c r="R110">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="S110">
-        <v>9.5004039999999996</v>
+        <v>9.5152960000000011</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -12010,7 +11798,7 @@
         <v>2.3651999999999999E-2</v>
       </c>
       <c r="S111">
-        <v>6.3589919999999998</v>
+        <v>6.3826440000000009</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -12057,10 +11845,10 @@
         <v>1.1756519999999999</v>
       </c>
       <c r="O112">
-        <v>3.5137200000000002</v>
+        <v>3.5137199999999997</v>
       </c>
       <c r="P112">
-        <v>0.1573</v>
+        <v>0.15730000000000002</v>
       </c>
       <c r="Q112">
         <v>0.95650000000000002</v>
@@ -12069,7 +11857,7 @@
         <v>4.8180000000000001E-2</v>
       </c>
       <c r="S112">
-        <v>5.803172</v>
+        <v>5.8513520000000003</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -12113,22 +11901,22 @@
         <v>73</v>
       </c>
       <c r="N113">
-        <v>6.9232839999999998</v>
+        <v>6.9510883534136543</v>
       </c>
       <c r="O113">
         <v>0</v>
       </c>
       <c r="P113">
-        <v>0.1716</v>
+        <v>0.17228915662650604</v>
       </c>
       <c r="Q113">
-        <v>0.78815599999999997</v>
+        <v>0.79132128514056232</v>
       </c>
       <c r="R113">
-        <v>7.0080000000000003E-3</v>
+        <v>7.0361445783132534E-3</v>
       </c>
       <c r="S113">
-        <v>7.8830400000000003</v>
+        <v>7.9217349397590358</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -12172,22 +11960,22 @@
         <v>0</v>
       </c>
       <c r="N114">
-        <v>15.022220000000001</v>
+        <v>15.08255020080321</v>
       </c>
       <c r="O114">
-        <v>1.6732</v>
+        <v>1.6799196787148594</v>
       </c>
       <c r="P114">
-        <v>0.92949999999999999</v>
+        <v>0.93323293172690758</v>
       </c>
       <c r="Q114">
-        <v>0.31373200000000001</v>
+        <v>0.31499196787148598</v>
       </c>
       <c r="R114">
-        <v>7.0080000000000003E-3</v>
+        <v>7.0361445783132534E-3</v>
       </c>
       <c r="S114">
-        <v>17.938652000000001</v>
+        <v>18.017730923694778</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -12234,7 +12022,7 @@
         <v>4.7026079999999997</v>
       </c>
       <c r="O115">
-        <v>2.9281000000000001</v>
+        <v>2.9280999999999997</v>
       </c>
       <c r="P115">
         <v>0.57199999999999995</v>
@@ -12246,7 +12034,7 @@
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="S115">
-        <v>9.0520800000000001</v>
+        <v>9.0695999999999994</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -12296,7 +12084,7 @@
         <v>0.50195999999999996</v>
       </c>
       <c r="P116">
-        <v>0.80079999999999996</v>
+        <v>0.80080000000000007</v>
       </c>
       <c r="Q116">
         <v>8.4171999999999997E-2</v>
@@ -12305,7 +12093,7 @@
         <v>7.0080000000000003E-3</v>
       </c>
       <c r="S116">
-        <v>9.2246120000000005</v>
+        <v>9.2316200000000013</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -12349,22 +12137,22 @@
         <v>46</v>
       </c>
       <c r="N117">
-        <v>12.540288</v>
+        <v>12.540287999999999</v>
       </c>
       <c r="O117">
         <v>2.0914999999999999</v>
       </c>
       <c r="P117">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="Q117">
-        <v>0.22955999999999999</v>
+        <v>0.22956000000000001</v>
       </c>
       <c r="R117">
         <v>4.1172E-2</v>
       </c>
       <c r="S117">
-        <v>14.947148</v>
+        <v>14.988319999999998</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -12423,7 +12211,7 @@
         <v>5.2560000000000003E-3</v>
       </c>
       <c r="S118">
-        <v>7.3592760000000004</v>
+        <v>7.3645319999999996</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -12482,7 +12270,7 @@
         <v>3.7668E-2</v>
       </c>
       <c r="S119">
-        <v>3.792224</v>
+        <v>3.8298920000000001</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -12526,7 +12314,7 @@
         <v>143</v>
       </c>
       <c r="N120">
-        <v>3.5269560000000002</v>
+        <v>3.5269559999999998</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -12541,7 +12329,7 @@
         <v>2.2776000000000001E-2</v>
       </c>
       <c r="S120">
-        <v>3.9933480000000001</v>
+        <v>4.0161239999999996</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -12585,7 +12373,7 @@
         <v>124</v>
       </c>
       <c r="N121">
-        <v>2.6125600000000002</v>
+        <v>2.6125599999999993</v>
       </c>
       <c r="O121">
         <v>1.0039199999999999</v>
@@ -12594,13 +12382,13 @@
         <v>0.32890000000000003</v>
       </c>
       <c r="Q121">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="R121">
         <v>2.2776000000000001E-2</v>
       </c>
       <c r="S121">
-        <v>4.28972</v>
+        <v>4.3124959999999994</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -12659,7 +12447,7 @@
         <v>4.6427999999999997E-2</v>
       </c>
       <c r="S122">
-        <v>7.6036080000000004</v>
+        <v>7.6500359999999992</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -12718,7 +12506,7 @@
         <v>2.2776000000000001E-2</v>
       </c>
       <c r="S123">
-        <v>2.6994400000000001</v>
+        <v>2.722216</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -12777,7 +12565,7 @@
         <v>0.12789600000000001</v>
       </c>
       <c r="S124">
-        <v>6.3853119999999999</v>
+        <v>6.5132080000000006</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -12830,7 +12618,7 @@
         <v>0.7722</v>
       </c>
       <c r="Q125">
-        <v>0.40555600000000003</v>
+        <v>0.40555599999999997</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -12895,7 +12683,7 @@
         <v>2.1024000000000001E-2</v>
       </c>
       <c r="S126">
-        <v>0.160692</v>
+        <v>0.18171599999999999</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -12954,7 +12742,7 @@
         <v>4.4676E-2</v>
       </c>
       <c r="S127">
-        <v>3.3292920000000001</v>
+        <v>3.3739679999999996</v>
       </c>
     </row>
   </sheetData>
@@ -13181,16 +12969,16 @@
         <v>1.2</v>
       </c>
       <c r="AH2">
-        <v>0.62919999999999998</v>
+        <v>0.62920000000000009</v>
       </c>
       <c r="AI2">
-        <v>0.29842800000000003</v>
+        <v>0.29842799999999997</v>
       </c>
       <c r="AJ2">
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="AK2">
-        <v>4.1851479999999999</v>
+        <v>4.1851480000000008</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -13300,7 +13088,7 @@
         <v>0.25251600000000002</v>
       </c>
       <c r="AJ3">
-        <v>9.8112000000000005E-2</v>
+        <v>9.8111999999999991E-2</v>
       </c>
       <c r="AK3">
         <v>0.93652800000000003</v>
@@ -13407,7 +13195,7 @@
         <v>1.52</v>
       </c>
       <c r="AH4">
-        <v>1.5872999999999999</v>
+        <v>1.5873000000000002</v>
       </c>
       <c r="AI4">
         <v>0.244864</v>
@@ -13416,7 +13204,7 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>4.1321640000000004</v>
+        <v>4.1321639999999995</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -13523,13 +13311,13 @@
         <v>0.45760000000000001</v>
       </c>
       <c r="AI5">
-        <v>0.58155199999999996</v>
+        <v>0.58155200000000007</v>
       </c>
       <c r="AJ5">
         <v>4.1172E-2</v>
       </c>
       <c r="AK5">
-        <v>1.4003239999999999</v>
+        <v>1.4003240000000001</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -13642,7 +13430,7 @@
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="AK6">
-        <v>3.7623160000000002</v>
+        <v>3.7623160000000007</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -13755,7 +13543,7 @@
         <v>1.3140000000000001E-2</v>
       </c>
       <c r="AK7">
-        <v>6.2289519999999996</v>
+        <v>6.2289520000000005</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -13865,7 +13653,7 @@
         <v>0.23721200000000001</v>
       </c>
       <c r="AJ8">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AK8">
         <v>4.555504</v>
@@ -14085,7 +13873,7 @@
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>0.75790000000000002</v>
+        <v>0.75790000000000013</v>
       </c>
       <c r="AI10">
         <v>0.68102799999999997</v>
@@ -14094,7 +13882,7 @@
         <v>4.6427999999999997E-2</v>
       </c>
       <c r="AK10">
-        <v>3.645356</v>
+        <v>3.6453560000000005</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -14198,7 +13986,7 @@
         <v>0.64</v>
       </c>
       <c r="AH11">
-        <v>0.90090000000000003</v>
+        <v>0.90090000000000015</v>
       </c>
       <c r="AI11">
         <v>0.52033600000000002</v>
@@ -14314,10 +14102,10 @@
         <v>7.1499999999999994E-2</v>
       </c>
       <c r="AI12">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="AJ12">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AK12">
         <v>4.885624</v>
@@ -14430,10 +14218,10 @@
         <v>0.428512</v>
       </c>
       <c r="AJ13">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="AK13">
-        <v>1.84514</v>
+        <v>1.8451400000000002</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -14540,13 +14328,13 @@
         <v>0</v>
       </c>
       <c r="AI14">
-        <v>0.22955999999999999</v>
+        <v>0.22956000000000001</v>
       </c>
       <c r="AJ14">
         <v>0.13315199999999999</v>
       </c>
       <c r="AK14">
-        <v>0.36271199999999998</v>
+        <v>0.36271200000000003</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -14653,7 +14441,7 @@
         <v>0.48620000000000002</v>
       </c>
       <c r="AI15">
-        <v>3.8260000000000002E-2</v>
+        <v>3.8259999999999995E-2</v>
       </c>
       <c r="AJ15">
         <v>1.1388000000000001E-2</v>
@@ -14769,10 +14557,10 @@
         <v>0.137736</v>
       </c>
       <c r="AJ16">
-        <v>3.9419999999999997E-2</v>
+        <v>3.9420000000000004E-2</v>
       </c>
       <c r="AK16">
-        <v>7.7661559999999996</v>
+        <v>7.7661560000000005</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -14882,10 +14670,10 @@
         <v>0.244864</v>
       </c>
       <c r="AJ17">
-        <v>3.2412000000000003E-2</v>
+        <v>3.2411999999999996E-2</v>
       </c>
       <c r="AK17">
-        <v>5.1059760000000001</v>
+        <v>5.1059759999999992</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -14998,7 +14786,7 @@
         <v>1.0512000000000001E-2</v>
       </c>
       <c r="AK18">
-        <v>11.28548</v>
+        <v>11.285480000000002</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -15102,16 +14890,16 @@
         <v>0.2</v>
       </c>
       <c r="AH19">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="AI19">
         <v>0.42086000000000001</v>
       </c>
       <c r="AJ19">
-        <v>0.11300399999999999</v>
+        <v>0.11300400000000001</v>
       </c>
       <c r="AK19">
-        <v>4.0596639999999997</v>
+        <v>4.0596640000000006</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -15224,7 +15012,7 @@
         <v>7.0080000000000003E-3</v>
       </c>
       <c r="AK20">
-        <v>5.6030040000000003</v>
+        <v>5.6030039999999994</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -15331,13 +15119,13 @@
         <v>0</v>
       </c>
       <c r="AI21">
-        <v>7.6520000000000005E-2</v>
+        <v>7.6519999999999991E-2</v>
       </c>
       <c r="AJ21">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AK21">
-        <v>4.2661559999999996</v>
+        <v>4.2661560000000005</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -15450,7 +15238,7 @@
         <v>3.1536000000000002E-2</v>
       </c>
       <c r="AK22">
-        <v>7.3067039999999999</v>
+        <v>7.3067040000000008</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -15554,16 +15342,16 @@
         <v>3.12</v>
       </c>
       <c r="AH23">
-        <v>0.10009999999999999</v>
+        <v>0.10010000000000001</v>
       </c>
       <c r="AI23">
-        <v>0.88763199999999998</v>
+        <v>0.88763200000000009</v>
       </c>
       <c r="AJ23">
         <v>1.8395999999999999E-2</v>
       </c>
       <c r="AK23">
-        <v>5.4461279999999999</v>
+        <v>5.4461280000000007</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -15670,10 +15458,10 @@
         <v>0.3861</v>
       </c>
       <c r="AI24">
-        <v>0.22190799999999999</v>
+        <v>0.22190800000000002</v>
       </c>
       <c r="AJ24">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="AK24">
         <v>5.2472799999999999</v>
@@ -15783,7 +15571,7 @@
         <v>1.8447</v>
       </c>
       <c r="AI25">
-        <v>0.45911999999999997</v>
+        <v>0.45912000000000003</v>
       </c>
       <c r="AJ25">
         <v>1.4016000000000001E-2</v>
@@ -15896,7 +15684,7 @@
         <v>0.74360000000000004</v>
       </c>
       <c r="AI26">
-        <v>0.59685600000000005</v>
+        <v>0.59685599999999994</v>
       </c>
       <c r="AJ26">
         <v>6.6575999999999996E-2</v>
@@ -16119,7 +15907,7 @@
         <v>0.36</v>
       </c>
       <c r="AH28">
-        <v>1.1153999999999999</v>
+        <v>1.1154000000000002</v>
       </c>
       <c r="AI28">
         <v>0.27547199999999999</v>
@@ -16128,7 +15916,7 @@
         <v>5.2560000000000003E-3</v>
       </c>
       <c r="AK28">
-        <v>3.856128</v>
+        <v>3.8561280000000004</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -16241,7 +16029,7 @@
         <v>7.8840000000000004E-3</v>
       </c>
       <c r="AK29">
-        <v>4.4862279999999997</v>
+        <v>4.4862280000000005</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -16354,7 +16142,7 @@
         <v>4.4676E-2</v>
       </c>
       <c r="AK30">
-        <v>4.6639720000000002</v>
+        <v>4.6639719999999993</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -16797,7 +16585,7 @@
         <v>1.8</v>
       </c>
       <c r="AH34">
-        <v>1.2441</v>
+        <v>1.2441000000000002</v>
       </c>
       <c r="AI34">
         <v>0.244864</v>
@@ -16806,7 +16594,7 @@
         <v>2.2776000000000001E-2</v>
       </c>
       <c r="AK34">
-        <v>3.3117399999999999</v>
+        <v>3.3117400000000004</v>
       </c>
     </row>
     <row r="35" spans="1:37">
@@ -16913,7 +16701,7 @@
         <v>0.85799999999999998</v>
       </c>
       <c r="AI35">
-        <v>0.22955999999999999</v>
+        <v>0.22956000000000001</v>
       </c>
       <c r="AJ35">
         <v>2.0147999999999999E-2</v>
@@ -17023,7 +16811,7 @@
         <v>2.16</v>
       </c>
       <c r="AH36">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="AI36">
         <v>6.8867999999999999E-2</v>
@@ -17032,7 +16820,7 @@
         <v>8.1467999999999999E-2</v>
       </c>
       <c r="AK36">
-        <v>3.9561359999999999</v>
+        <v>3.9561360000000003</v>
       </c>
     </row>
     <row r="37" spans="1:37">
@@ -17136,16 +16924,16 @@
         <v>0.84</v>
       </c>
       <c r="AH37">
-        <v>0.47189999999999999</v>
+        <v>0.47190000000000004</v>
       </c>
       <c r="AI37">
-        <v>0.58155199999999996</v>
+        <v>0.58155200000000007</v>
       </c>
       <c r="AJ37">
         <v>7.0080000000000003E-2</v>
       </c>
       <c r="AK37">
-        <v>3.5235319999999999</v>
+        <v>3.5235320000000003</v>
       </c>
     </row>
     <row r="38" spans="1:37">
@@ -17252,13 +17040,13 @@
         <v>0.35749999999999998</v>
       </c>
       <c r="AI38">
-        <v>0.29842800000000003</v>
+        <v>0.29842799999999997</v>
       </c>
       <c r="AJ38">
         <v>8.5847999999999994E-2</v>
       </c>
       <c r="AK38">
-        <v>1.541776</v>
+        <v>1.5417759999999998</v>
       </c>
     </row>
     <row r="39" spans="1:37">
@@ -17371,7 +17159,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AK39">
-        <v>3.7173799999999999</v>
+        <v>3.7173799999999995</v>
       </c>
     </row>
     <row r="40" spans="1:37">
@@ -17475,16 +17263,16 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="AH40">
-        <v>0.1573</v>
+        <v>0.15730000000000002</v>
       </c>
       <c r="AI40">
         <v>0.26016800000000001</v>
       </c>
       <c r="AJ40">
-        <v>6.5699999999999995E-2</v>
+        <v>6.5700000000000008E-2</v>
       </c>
       <c r="AK40">
-        <v>5.9231680000000004</v>
+        <v>5.9231679999999995</v>
       </c>
     </row>
     <row r="41" spans="1:37">
@@ -17594,10 +17382,10 @@
         <v>0.77285199999999998</v>
       </c>
       <c r="AJ41">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AK41">
-        <v>1.4368879999999999</v>
+        <v>1.4368880000000002</v>
       </c>
     </row>
     <row r="42" spans="1:37">
@@ -17701,7 +17489,7 @@
         <v>1.04</v>
       </c>
       <c r="AH42">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="AI42">
         <v>0.73459200000000002</v>
@@ -17820,7 +17608,7 @@
         <v>4.5912000000000001E-2</v>
       </c>
       <c r="AJ43">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="AK43">
         <v>6.1920440000000001</v>
@@ -17930,7 +17718,7 @@
         <v>0.2288</v>
       </c>
       <c r="AI44">
-        <v>0.66572399999999998</v>
+        <v>0.66572400000000009</v>
       </c>
       <c r="AJ44">
         <v>3.066E-2</v>
@@ -18043,13 +17831,13 @@
         <v>0</v>
       </c>
       <c r="AI45">
-        <v>7.6520000000000005E-2</v>
+        <v>7.6519999999999991E-2</v>
       </c>
       <c r="AJ45">
         <v>8.8475999999999999E-2</v>
       </c>
       <c r="AK45">
-        <v>6.9849959999999998</v>
+        <v>6.9849960000000006</v>
       </c>
     </row>
     <row r="46" spans="1:37">
@@ -18159,10 +17947,10 @@
         <v>0.321384</v>
       </c>
       <c r="AJ46">
-        <v>0.11300399999999999</v>
+        <v>0.11300400000000001</v>
       </c>
       <c r="AK46">
-        <v>3.640288</v>
+        <v>3.6402880000000004</v>
       </c>
     </row>
     <row r="47" spans="1:37">
@@ -18272,7 +18060,7 @@
         <v>0.78050399999999998</v>
       </c>
       <c r="AJ47">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AK47">
         <v>5.7273959999999997</v>
@@ -18382,7 +18170,7 @@
         <v>1.0725</v>
       </c>
       <c r="AI48">
-        <v>0.15304000000000001</v>
+        <v>0.15303999999999998</v>
       </c>
       <c r="AJ48">
         <v>2.0147999999999999E-2</v>
@@ -18608,13 +18396,13 @@
         <v>1.5444</v>
       </c>
       <c r="AI50">
-        <v>0.14538799999999999</v>
+        <v>0.14538800000000002</v>
       </c>
       <c r="AJ50">
         <v>1.1388000000000001E-2</v>
       </c>
       <c r="AK50">
-        <v>6.381176</v>
+        <v>6.3811759999999991</v>
       </c>
     </row>
     <row r="51" spans="1:37">
@@ -18721,7 +18509,7 @@
         <v>0.57199999999999995</v>
       </c>
       <c r="AI51">
-        <v>0.80345999999999995</v>
+        <v>0.80346000000000006</v>
       </c>
       <c r="AJ51">
         <v>1.4016000000000001E-2</v>
@@ -18831,16 +18619,16 @@
         <v>0</v>
       </c>
       <c r="AH52">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="AI52">
-        <v>0.11477999999999999</v>
+        <v>0.11478000000000001</v>
       </c>
       <c r="AJ52">
         <v>0.11212800000000001</v>
       </c>
       <c r="AK52">
-        <v>0.99010799999999999</v>
+        <v>0.9901080000000001</v>
       </c>
     </row>
     <row r="53" spans="1:37">
@@ -19060,7 +18848,7 @@
         <v>0.64349999999999996</v>
       </c>
       <c r="AI54">
-        <v>3.8260000000000002E-2</v>
+        <v>3.8259999999999995E-2</v>
       </c>
       <c r="AJ54">
         <v>4.3799999999999999E-2</v>
@@ -19176,10 +18964,10 @@
         <v>4.5912000000000001E-2</v>
       </c>
       <c r="AJ55">
-        <v>9.8988000000000007E-2</v>
+        <v>9.8987999999999993E-2</v>
       </c>
       <c r="AK55">
-        <v>2.7967</v>
+        <v>2.7966999999999995</v>
       </c>
     </row>
     <row r="56" spans="1:37">
@@ -19286,7 +19074,7 @@
         <v>0.12870000000000001</v>
       </c>
       <c r="AI56">
-        <v>0.56624799999999997</v>
+        <v>0.56624800000000008</v>
       </c>
       <c r="AJ56">
         <v>8.4096000000000004E-2</v>
@@ -19396,7 +19184,7 @@
         <v>0.2</v>
       </c>
       <c r="AH57">
-        <v>0.1716</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="AI57">
         <v>0.428512</v>
@@ -19631,7 +19419,7 @@
         <v>4.2048000000000002E-2</v>
       </c>
       <c r="AK59">
-        <v>3.3262960000000001</v>
+        <v>3.3262959999999997</v>
       </c>
     </row>
     <row r="60" spans="1:37">
@@ -19744,7 +19532,7 @@
         <v>1.4016000000000001E-2</v>
       </c>
       <c r="AK60">
-        <v>9.4111600000000006</v>
+        <v>9.4111599999999989</v>
       </c>
     </row>
     <row r="61" spans="1:37">
@@ -19857,7 +19645,7 @@
         <v>0.12614400000000001</v>
       </c>
       <c r="AK61">
-        <v>3.5210560000000002</v>
+        <v>3.5210559999999997</v>
       </c>
     </row>
     <row r="62" spans="1:37">
@@ -20074,7 +19862,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="AH63">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="AI63">
         <v>0.13008400000000001</v>
@@ -20083,7 +19871,7 @@
         <v>0.114756</v>
       </c>
       <c r="AK63">
-        <v>1.6480399999999999</v>
+        <v>1.6480400000000002</v>
       </c>
     </row>
     <row r="64" spans="1:37">
@@ -20196,7 +19984,7 @@
         <v>6.6575999999999996E-2</v>
       </c>
       <c r="AK64">
-        <v>7.8954880000000003</v>
+        <v>7.8954880000000012</v>
       </c>
     </row>
     <row r="65" spans="1:37">
@@ -20868,7 +20656,7 @@
         <v>1.8304</v>
       </c>
       <c r="AI70">
-        <v>0.40555600000000003</v>
+        <v>0.40555599999999997</v>
       </c>
       <c r="AJ70">
         <v>1.8395999999999999E-2</v>
@@ -20987,7 +20775,7 @@
         <v>9.7236000000000003E-2</v>
       </c>
       <c r="AK71">
-        <v>1.704072</v>
+        <v>1.7040720000000003</v>
       </c>
     </row>
     <row r="72" spans="1:37">
@@ -21094,13 +20882,13 @@
         <v>0.45760000000000001</v>
       </c>
       <c r="AI72">
-        <v>0.11477999999999999</v>
+        <v>0.11478000000000001</v>
       </c>
       <c r="AJ72">
         <v>0.1095</v>
       </c>
       <c r="AK72">
-        <v>1.8218799999999999</v>
+        <v>1.8218800000000002</v>
       </c>
     </row>
     <row r="73" spans="1:37">
@@ -21210,10 +20998,10 @@
         <v>0.137736</v>
       </c>
       <c r="AJ73">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="AK73">
-        <v>9.6598640000000007</v>
+        <v>9.6598639999999989</v>
       </c>
     </row>
     <row r="74" spans="1:37">
@@ -21326,7 +21114,7 @@
         <v>7.8840000000000004E-3</v>
       </c>
       <c r="AK74">
-        <v>7.0543519999999997</v>
+        <v>7.0543520000000006</v>
       </c>
     </row>
     <row r="75" spans="1:37">
@@ -21543,7 +21331,7 @@
         <v>0</v>
       </c>
       <c r="AH76">
-        <v>1.1583000000000001</v>
+        <v>1.1582999999999999</v>
       </c>
       <c r="AI76">
         <v>9.1824000000000003E-2</v>
@@ -21665,7 +21453,7 @@
         <v>0</v>
       </c>
       <c r="AK77">
-        <v>2.2526959999999998</v>
+        <v>2.2526960000000003</v>
       </c>
     </row>
     <row r="78" spans="1:37">
@@ -21769,13 +21557,13 @@
         <v>2.96</v>
       </c>
       <c r="AH78">
-        <v>0.75790000000000002</v>
+        <v>0.75790000000000013</v>
       </c>
       <c r="AI78">
         <v>0.26016800000000001</v>
       </c>
       <c r="AJ78">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="AK78">
         <v>4.3025960000000003</v>
@@ -21998,13 +21786,13 @@
         <v>0.12870000000000001</v>
       </c>
       <c r="AI80">
-        <v>0.45146799999999998</v>
+        <v>0.45146800000000004</v>
       </c>
       <c r="AJ80">
         <v>7.8840000000000004E-3</v>
       </c>
       <c r="AK80">
-        <v>7.4280520000000001</v>
+        <v>7.428052000000001</v>
       </c>
     </row>
     <row r="81" spans="1:37">
@@ -22108,7 +21896,7 @@
         <v>0.36</v>
       </c>
       <c r="AH81">
-        <v>1.3728</v>
+        <v>1.3728000000000002</v>
       </c>
       <c r="AI81">
         <v>0.96415200000000001</v>
@@ -22230,7 +22018,7 @@
         <v>4.4676E-2</v>
       </c>
       <c r="AK82">
-        <v>5.4443640000000002</v>
+        <v>5.4443639999999993</v>
       </c>
     </row>
     <row r="83" spans="1:37">
@@ -22447,7 +22235,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="AH84">
-        <v>1.7302999999999999</v>
+        <v>1.7303000000000002</v>
       </c>
       <c r="AI84">
         <v>0.64276800000000001</v>
@@ -22456,7 +22244,7 @@
         <v>0</v>
       </c>
       <c r="AK84">
-        <v>4.4330679999999996</v>
+        <v>4.4330680000000005</v>
       </c>
     </row>
     <row r="85" spans="1:37">
@@ -22676,10 +22464,10 @@
         <v>0.74360000000000004</v>
       </c>
       <c r="AI86">
-        <v>0.30608000000000002</v>
+        <v>0.30607999999999996</v>
       </c>
       <c r="AJ86">
-        <v>3.8544000000000002E-2</v>
+        <v>3.8543999999999995E-2</v>
       </c>
       <c r="AK86">
         <v>2.288224</v>
@@ -22786,7 +22574,7 @@
         <v>0</v>
       </c>
       <c r="AH87">
-        <v>0.68640000000000001</v>
+        <v>0.68640000000000012</v>
       </c>
       <c r="AI87">
         <v>0.321384</v>
@@ -22902,10 +22690,10 @@
         <v>0.88660000000000005</v>
       </c>
       <c r="AI88">
-        <v>3.8260000000000002E-2</v>
+        <v>3.8259999999999995E-2</v>
       </c>
       <c r="AJ88">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AK88">
         <v>6.374644</v>
@@ -23012,7 +22800,7 @@
         <v>0</v>
       </c>
       <c r="AH89">
-        <v>1.6158999999999999</v>
+        <v>1.6159000000000001</v>
       </c>
       <c r="AI89">
         <v>0.18364800000000001</v>
@@ -23241,13 +23029,13 @@
         <v>0</v>
       </c>
       <c r="AI91">
-        <v>0.22955999999999999</v>
+        <v>0.22956000000000001</v>
       </c>
       <c r="AJ91">
-        <v>9.9863999999999994E-2</v>
+        <v>9.9864000000000008E-2</v>
       </c>
       <c r="AK91">
-        <v>5.889424</v>
+        <v>5.8894240000000009</v>
       </c>
     </row>
     <row r="92" spans="1:37">
@@ -23360,7 +23148,7 @@
         <v>0</v>
       </c>
       <c r="AK92">
-        <v>3.9480080000000002</v>
+        <v>3.9480079999999997</v>
       </c>
     </row>
     <row r="93" spans="1:37">
@@ -23473,7 +23261,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AK93">
-        <v>4.16188</v>
+        <v>4.1618800000000009</v>
       </c>
     </row>
     <row r="94" spans="1:37">
@@ -23690,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="AH95">
-        <v>1.1153999999999999</v>
+        <v>1.1154000000000002</v>
       </c>
       <c r="AI95">
         <v>4.5912000000000001E-2</v>
@@ -23699,7 +23487,7 @@
         <v>0</v>
       </c>
       <c r="AK95">
-        <v>2.9013119999999999</v>
+        <v>2.9013120000000003</v>
       </c>
     </row>
     <row r="96" spans="1:37">
@@ -23803,7 +23591,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="AH96">
-        <v>0.31459999999999999</v>
+        <v>0.31460000000000005</v>
       </c>
       <c r="AI96">
         <v>4.5912000000000001E-2</v>
@@ -23916,7 +23704,7 @@
         <v>2.04</v>
       </c>
       <c r="AH97">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="AI97">
         <v>0.68102799999999997</v>
@@ -23925,7 +23713,7 @@
         <v>1.7520000000000001E-2</v>
       </c>
       <c r="AK97">
-        <v>7.264348</v>
+        <v>7.2643480000000009</v>
       </c>
     </row>
     <row r="98" spans="1:37">
@@ -24255,16 +24043,16 @@
         <v>5.6</v>
       </c>
       <c r="AH100">
-        <v>0.1573</v>
+        <v>0.15730000000000002</v>
       </c>
       <c r="AI100">
-        <v>0.22955999999999999</v>
+        <v>0.22956000000000001</v>
       </c>
       <c r="AJ100">
         <v>4.3800000000000002E-3</v>
       </c>
       <c r="AK100">
-        <v>9.2312399999999997</v>
+        <v>9.2312399999999979</v>
       </c>
     </row>
     <row r="101" spans="1:37">
@@ -24368,7 +24156,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="AH101">
-        <v>0.1716</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="AI101">
         <v>0.244864</v>
@@ -24490,7 +24278,7 @@
         <v>0.17169599999999999</v>
       </c>
       <c r="AK102">
-        <v>0.47199600000000003</v>
+        <v>0.47199599999999997</v>
       </c>
     </row>
     <row r="103" spans="1:37">
@@ -24594,13 +24382,13 @@
         <v>2.52</v>
       </c>
       <c r="AH103">
-        <v>0.90090000000000003</v>
+        <v>0.90090000000000015</v>
       </c>
       <c r="AI103">
         <v>0.20660400000000001</v>
       </c>
       <c r="AJ103">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AK103">
         <v>3.6572879999999999</v>
@@ -24829,7 +24617,7 @@
         <v>0.104244</v>
       </c>
       <c r="AK105">
-        <v>2.4052600000000002</v>
+        <v>2.4052599999999997</v>
       </c>
     </row>
     <row r="106" spans="1:37">
@@ -24933,7 +24721,7 @@
         <v>0.44</v>
       </c>
       <c r="AH106">
-        <v>0.34320000000000001</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="AI106">
         <v>0.13008400000000001</v>
@@ -24942,7 +24730,7 @@
         <v>0.104244</v>
       </c>
       <c r="AK106">
-        <v>1.3775280000000001</v>
+        <v>1.3775280000000003</v>
       </c>
     </row>
     <row r="107" spans="1:37">
@@ -25046,7 +24834,7 @@
         <v>0</v>
       </c>
       <c r="AH107">
-        <v>1.2584</v>
+        <v>1.2584000000000002</v>
       </c>
       <c r="AI107">
         <v>0.20660400000000001</v>
@@ -25055,7 +24843,7 @@
         <v>5.6939999999999998E-2</v>
       </c>
       <c r="AK107">
-        <v>1.521944</v>
+        <v>1.5219440000000002</v>
       </c>
     </row>
     <row r="108" spans="1:37">
@@ -25272,7 +25060,7 @@
         <v>0</v>
       </c>
       <c r="AH109">
-        <v>1.7588999999999999</v>
+        <v>1.7589000000000001</v>
       </c>
       <c r="AI109">
         <v>0</v>
@@ -25281,7 +25069,7 @@
         <v>7.1831999999999993E-2</v>
       </c>
       <c r="AK109">
-        <v>3.8707319999999998</v>
+        <v>3.8707320000000003</v>
       </c>
     </row>
     <row r="110" spans="1:37">
@@ -25388,7 +25176,7 @@
         <v>1.5587</v>
       </c>
       <c r="AI110">
-        <v>0.61216000000000004</v>
+        <v>0.61215999999999993</v>
       </c>
       <c r="AJ110">
         <v>1.5768000000000001E-2</v>
@@ -25498,10 +25286,10 @@
         <v>1.52</v>
       </c>
       <c r="AH111">
-        <v>0.1716</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="AI111">
-        <v>3.8260000000000002E-2</v>
+        <v>3.8259999999999995E-2</v>
       </c>
       <c r="AJ111">
         <v>0.104244</v>
@@ -25617,7 +25405,7 @@
         <v>5.3564000000000001E-2</v>
       </c>
       <c r="AJ112">
-        <v>6.0443999999999998E-2</v>
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="AK112">
         <v>1.443908</v>
@@ -25730,10 +25518,10 @@
         <v>8.4171999999999997E-2</v>
       </c>
       <c r="AJ113">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AK113">
-        <v>2.7822079999999998</v>
+        <v>2.7822080000000002</v>
       </c>
     </row>
     <row r="114" spans="1:37">
@@ -25840,10 +25628,10 @@
         <v>0.2288</v>
       </c>
       <c r="AI114">
-        <v>0.14538799999999999</v>
+        <v>0.14538800000000002</v>
       </c>
       <c r="AJ114">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="AK114">
         <v>7.6387159999999996</v>
@@ -25956,7 +25744,7 @@
         <v>0.50503200000000004</v>
       </c>
       <c r="AJ115">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AK115">
         <v>6.5776680000000001</v>
@@ -26069,10 +25857,10 @@
         <v>0</v>
       </c>
       <c r="AJ116">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AK116">
-        <v>6.5237920000000003</v>
+        <v>6.5237919999999994</v>
       </c>
     </row>
     <row r="117" spans="1:37">
@@ -26182,7 +25970,7 @@
         <v>8.4171999999999997E-2</v>
       </c>
       <c r="AJ117">
-        <v>1.2264000000000001E-2</v>
+        <v>1.2263999999999999E-2</v>
       </c>
       <c r="AK117">
         <v>2.7931360000000001</v>
@@ -26402,16 +26190,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="AH119">
-        <v>1.1153999999999999</v>
+        <v>1.1154000000000002</v>
       </c>
       <c r="AI119">
-        <v>0.29077599999999998</v>
+        <v>0.29077600000000003</v>
       </c>
       <c r="AJ119">
         <v>5.4311999999999999E-2</v>
       </c>
       <c r="AK119">
-        <v>4.9204879999999998</v>
+        <v>4.9204880000000006</v>
       </c>
     </row>
     <row r="120" spans="1:37">
@@ -26521,7 +26309,7 @@
         <v>6.8867999999999999E-2</v>
       </c>
       <c r="AJ120">
-        <v>0.15329999999999999</v>
+        <v>0.15330000000000002</v>
       </c>
       <c r="AK120">
         <v>1.6824680000000001</v>
@@ -26631,7 +26419,7 @@
         <v>1.43</v>
       </c>
       <c r="AI121">
-        <v>0.15304000000000001</v>
+        <v>0.15303999999999998</v>
       </c>
       <c r="AJ121">
         <v>3.5040000000000002E-2</v>
@@ -26744,13 +26532,13 @@
         <v>0.84370000000000001</v>
       </c>
       <c r="AI122">
-        <v>0.29077599999999998</v>
+        <v>0.29077600000000003</v>
       </c>
       <c r="AJ122">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AK122">
-        <v>6.7042599999999997</v>
+        <v>6.7042600000000006</v>
       </c>
     </row>
     <row r="123" spans="1:37">
@@ -26970,13 +26758,13 @@
         <v>0.91520000000000001</v>
       </c>
       <c r="AI124">
-        <v>0.68867999999999996</v>
+        <v>0.68868000000000007</v>
       </c>
       <c r="AJ124">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AK124">
-        <v>3.6187719999999999</v>
+        <v>3.6187720000000003</v>
       </c>
     </row>
     <row r="125" spans="1:37">
@@ -27086,10 +26874,10 @@
         <v>9.1824000000000003E-2</v>
       </c>
       <c r="AJ125">
-        <v>0.18045600000000001</v>
+        <v>0.18045599999999998</v>
       </c>
       <c r="AK125">
-        <v>0.87228000000000006</v>
+        <v>0.87227999999999994</v>
       </c>
     </row>
     <row r="126" spans="1:37">
@@ -27199,10 +26987,10 @@
         <v>4.5912000000000001E-2</v>
       </c>
       <c r="AJ126">
-        <v>6.0443999999999998E-2</v>
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="AK126">
-        <v>6.8263559999999996</v>
+        <v>6.8263560000000005</v>
       </c>
     </row>
     <row r="127" spans="1:37">
@@ -27309,7 +27097,7 @@
         <v>0</v>
       </c>
       <c r="AI127">
-        <v>0.91823999999999995</v>
+        <v>0.91824000000000006</v>
       </c>
       <c r="AJ127">
         <v>2.1899999999999999E-2</v>
@@ -27422,7 +27210,7 @@
         <v>0.50049999999999994</v>
       </c>
       <c r="AI128">
-        <v>0.29077599999999998</v>
+        <v>0.29077600000000003</v>
       </c>
       <c r="AJ128">
         <v>3.1536000000000002E-2</v>
@@ -27654,7 +27442,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AK130">
-        <v>4.4523159999999997</v>
+        <v>4.4523160000000006</v>
       </c>
     </row>
     <row r="131" spans="1:37">
@@ -28097,16 +27885,16 @@
         <v>0.48</v>
       </c>
       <c r="AH134">
-        <v>1.5872999999999999</v>
+        <v>1.5873000000000002</v>
       </c>
       <c r="AI134">
-        <v>7.6520000000000005E-2</v>
+        <v>7.6519999999999991E-2</v>
       </c>
       <c r="AJ134">
         <v>5.2560000000000003E-3</v>
       </c>
       <c r="AK134">
-        <v>5.5690759999999999</v>
+        <v>5.5690760000000008</v>
       </c>
     </row>
     <row r="135" spans="1:37">
@@ -28329,10 +28117,10 @@
         <v>0.36729600000000001</v>
       </c>
       <c r="AJ136">
-        <v>6.0443999999999998E-2</v>
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="AK136">
-        <v>4.5251400000000004</v>
+        <v>4.5251399999999995</v>
       </c>
     </row>
     <row r="137" spans="1:37">
@@ -28439,13 +28227,13 @@
         <v>0.7722</v>
       </c>
       <c r="AI137">
-        <v>0.46677200000000002</v>
+        <v>0.46677199999999996</v>
       </c>
       <c r="AJ137">
-        <v>3.9419999999999997E-2</v>
+        <v>3.9420000000000004E-2</v>
       </c>
       <c r="AK137">
-        <v>3.078392</v>
+        <v>3.0783919999999991</v>
       </c>
     </row>
     <row r="138" spans="1:37">
@@ -28549,7 +28337,7 @@
         <v>1.64</v>
       </c>
       <c r="AH138">
-        <v>2.7456</v>
+        <v>2.7456000000000005</v>
       </c>
       <c r="AI138">
         <v>0.107128</v>
@@ -28558,7 +28346,7 @@
         <v>0</v>
       </c>
       <c r="AK138">
-        <v>4.4927279999999996</v>
+        <v>4.4927280000000005</v>
       </c>
     </row>
     <row r="139" spans="1:37">
@@ -28671,7 +28459,7 @@
         <v>1.0512000000000001E-2</v>
       </c>
       <c r="AK139">
-        <v>3.1948319999999999</v>
+        <v>3.1948320000000003</v>
       </c>
     </row>
     <row r="140" spans="1:37">
@@ -28778,10 +28566,10 @@
         <v>0.2717</v>
       </c>
       <c r="AI140">
-        <v>7.6520000000000005E-2</v>
+        <v>7.6519999999999991E-2</v>
       </c>
       <c r="AJ140">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="AK140">
         <v>3.6474920000000002</v>
@@ -28891,13 +28679,13 @@
         <v>0</v>
       </c>
       <c r="AI141">
-        <v>1.3697079999999999</v>
+        <v>1.3697080000000001</v>
       </c>
       <c r="AJ141">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AK141">
-        <v>3.4993439999999998</v>
+        <v>3.4993440000000002</v>
       </c>
     </row>
     <row r="142" spans="1:37">
@@ -29123,7 +28911,7 @@
         <v>7.1831999999999993E-2</v>
       </c>
       <c r="AK143">
-        <v>1.3419000000000001</v>
+        <v>1.3418999999999999</v>
       </c>
     </row>
     <row r="144" spans="1:37">
@@ -29236,7 +29024,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="AK144">
-        <v>3.9650599999999998</v>
+        <v>3.9650600000000003</v>
       </c>
     </row>
     <row r="145" spans="1:37">
@@ -29343,13 +29131,13 @@
         <v>0.2288</v>
       </c>
       <c r="AI145">
-        <v>0.22955999999999999</v>
+        <v>0.22956000000000001</v>
       </c>
       <c r="AJ145">
         <v>2.8908E-2</v>
       </c>
       <c r="AK145">
-        <v>8.1872679999999995</v>
+        <v>8.1872679999999978</v>
       </c>
     </row>
     <row r="146" spans="1:37">
@@ -29462,7 +29250,7 @@
         <v>0</v>
       </c>
       <c r="AK146">
-        <v>3.552584</v>
+        <v>3.5525839999999995</v>
       </c>
     </row>
     <row r="147" spans="1:37">
@@ -29679,7 +29467,7 @@
         <v>0</v>
       </c>
       <c r="AH148">
-        <v>1.8733</v>
+        <v>1.8733000000000002</v>
       </c>
       <c r="AI148">
         <v>0</v>
@@ -29792,13 +29580,13 @@
         <v>1.96</v>
       </c>
       <c r="AH149">
-        <v>1.2441</v>
+        <v>1.2441000000000002</v>
       </c>
       <c r="AI149">
         <v>0.122432</v>
       </c>
       <c r="AJ149">
-        <v>5.9568000000000003E-2</v>
+        <v>5.9567999999999996E-2</v>
       </c>
       <c r="AK149">
         <v>4.8860999999999999</v>
@@ -29905,16 +29693,16 @@
         <v>0</v>
       </c>
       <c r="AH150">
-        <v>1.5158</v>
+        <v>1.5158000000000003</v>
       </c>
       <c r="AI150">
         <v>0</v>
       </c>
       <c r="AJ150">
-        <v>4.9056000000000002E-2</v>
+        <v>4.9055999999999995E-2</v>
       </c>
       <c r="AK150">
-        <v>2.0448559999999998</v>
+        <v>2.0448560000000002</v>
       </c>
     </row>
     <row r="151" spans="1:37">
@@ -30021,7 +29809,7 @@
         <v>0.32890000000000003</v>
       </c>
       <c r="AI151">
-        <v>0.34433999999999998</v>
+        <v>0.34434000000000003</v>
       </c>
       <c r="AJ151">
         <v>8.4096000000000004E-2</v>
@@ -30247,10 +30035,10 @@
         <v>1.3012999999999999</v>
       </c>
       <c r="AI153">
-        <v>0.45911999999999997</v>
+        <v>0.45912000000000003</v>
       </c>
       <c r="AJ153">
-        <v>6.0443999999999998E-2</v>
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="AK153">
         <v>3.080864</v>
@@ -30366,7 +30154,7 @@
         <v>7.0956000000000005E-2</v>
       </c>
       <c r="AK154">
-        <v>2.4473600000000002</v>
+        <v>2.4473599999999998</v>
       </c>
     </row>
     <row r="155" spans="1:37">
@@ -30473,10 +30261,10 @@
         <v>0.88660000000000005</v>
       </c>
       <c r="AI155">
-        <v>7.6520000000000005E-2</v>
+        <v>7.6519999999999991E-2</v>
       </c>
       <c r="AJ155">
-        <v>6.5699999999999995E-2</v>
+        <v>6.5700000000000008E-2</v>
       </c>
       <c r="AK155">
         <v>4.4088200000000004</v>
@@ -30589,7 +30377,7 @@
         <v>0.18364800000000001</v>
       </c>
       <c r="AJ156">
-        <v>6.0443999999999998E-2</v>
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="AK156">
         <v>1.430992</v>
@@ -30696,7 +30484,7 @@
         <v>0</v>
       </c>
       <c r="AH157">
-        <v>1.3871</v>
+        <v>1.3871000000000002</v>
       </c>
       <c r="AI157">
         <v>9.9475999999999995E-2</v>
@@ -30705,7 +30493,7 @@
         <v>3.5915999999999997E-2</v>
       </c>
       <c r="AK157">
-        <v>1.522492</v>
+        <v>1.5224920000000002</v>
       </c>
     </row>
     <row r="158" spans="1:37">
@@ -30812,13 +30600,13 @@
         <v>1.0725</v>
       </c>
       <c r="AI158">
-        <v>0.40555600000000003</v>
+        <v>0.40555599999999997</v>
       </c>
       <c r="AJ158">
         <v>7.3583999999999997E-2</v>
       </c>
       <c r="AK158">
-        <v>1.5516399999999999</v>
+        <v>1.5516400000000001</v>
       </c>
     </row>
     <row r="159" spans="1:37">
@@ -30925,13 +30713,13 @@
         <v>1.3442000000000001</v>
       </c>
       <c r="AI159">
-        <v>0.51268400000000003</v>
+        <v>0.51268399999999992</v>
       </c>
       <c r="AJ159">
         <v>3.7668E-2</v>
       </c>
       <c r="AK159">
-        <v>2.6145520000000002</v>
+        <v>2.6145519999999998</v>
       </c>
     </row>
     <row r="160" spans="1:37">
@@ -31035,7 +30823,7 @@
         <v>0.44</v>
       </c>
       <c r="AH160">
-        <v>0.62919999999999998</v>
+        <v>0.62920000000000009</v>
       </c>
       <c r="AI160">
         <v>1.0177160000000001</v>
@@ -31044,7 +30832,7 @@
         <v>2.6280000000000001E-2</v>
       </c>
       <c r="AK160">
-        <v>2.1131959999999999</v>
+        <v>2.1131960000000003</v>
       </c>
     </row>
     <row r="161" spans="1:37">
@@ -31261,7 +31049,7 @@
         <v>3.72</v>
       </c>
       <c r="AH162">
-        <v>0.68640000000000001</v>
+        <v>0.68640000000000012</v>
       </c>
       <c r="AI162">
         <v>0</v>
@@ -31374,16 +31162,16 @@
         <v>0</v>
       </c>
       <c r="AH163">
-        <v>8.5800000000000001E-2</v>
+        <v>8.5800000000000015E-2</v>
       </c>
       <c r="AI163">
-        <v>7.6520000000000005E-2</v>
+        <v>7.6519999999999991E-2</v>
       </c>
       <c r="AJ163">
         <v>4.3800000000000002E-3</v>
       </c>
       <c r="AK163">
-        <v>12.0467</v>
+        <v>12.046700000000001</v>
       </c>
     </row>
     <row r="164" spans="1:37">
@@ -31496,7 +31284,7 @@
         <v>4.3800000000000002E-3</v>
       </c>
       <c r="AK164">
-        <v>12.757732000000001</v>
+        <v>12.757731999999999</v>
       </c>
     </row>
     <row r="165" spans="1:37">
@@ -31600,7 +31388,7 @@
         <v>0</v>
       </c>
       <c r="AH165">
-        <v>1.7302999999999999</v>
+        <v>1.7303000000000002</v>
       </c>
       <c r="AI165">
         <v>8.4171999999999997E-2</v>
@@ -31609,7 +31397,7 @@
         <v>5.8692000000000001E-2</v>
       </c>
       <c r="AK165">
-        <v>2.2331639999999999</v>
+        <v>2.2331640000000004</v>
       </c>
     </row>
     <row r="166" spans="1:37">
@@ -31716,7 +31504,7 @@
         <v>1.5587</v>
       </c>
       <c r="AI166">
-        <v>0.15304000000000001</v>
+        <v>0.15303999999999998</v>
       </c>
       <c r="AJ166">
         <v>6.3072000000000003E-2</v>
@@ -31832,10 +31620,10 @@
         <v>0</v>
       </c>
       <c r="AJ167">
-        <v>0.13139999999999999</v>
+        <v>0.13140000000000002</v>
       </c>
       <c r="AK167">
-        <v>1.5895999999999999</v>
+        <v>1.5896000000000001</v>
       </c>
     </row>
     <row r="168" spans="1:37">
@@ -32171,10 +31959,10 @@
         <v>6.8867999999999999E-2</v>
       </c>
       <c r="AJ170">
-        <v>6.9204000000000002E-2</v>
+        <v>6.9203999999999988E-2</v>
       </c>
       <c r="AK170">
-        <v>3.1707719999999999</v>
+        <v>3.1707720000000004</v>
       </c>
     </row>
     <row r="171" spans="1:37">
@@ -32278,7 +32066,7 @@
         <v>2</v>
       </c>
       <c r="AH171">
-        <v>0.68640000000000001</v>
+        <v>0.68640000000000012</v>
       </c>
       <c r="AI171">
         <v>0.137736</v>
@@ -32287,7 +32075,7 @@
         <v>0.114756</v>
       </c>
       <c r="AK171">
-        <v>2.9388920000000001</v>
+        <v>2.9388919999999996</v>
       </c>
     </row>
     <row r="172" spans="1:37">
@@ -32397,7 +32185,7 @@
         <v>9.1824000000000003E-2</v>
       </c>
       <c r="AJ172">
-        <v>3.9419999999999997E-2</v>
+        <v>3.9420000000000004E-2</v>
       </c>
       <c r="AK172">
         <v>3.3411439999999999</v>
@@ -32620,13 +32408,13 @@
         <v>2.6598000000000002</v>
       </c>
       <c r="AI174">
-        <v>0.29077599999999998</v>
+        <v>0.29077600000000003</v>
       </c>
       <c r="AJ174">
-        <v>1.2264000000000001E-2</v>
+        <v>1.2263999999999999E-2</v>
       </c>
       <c r="AK174">
-        <v>3.4428399999999999</v>
+        <v>3.4428400000000003</v>
       </c>
     </row>
     <row r="175" spans="1:37">
@@ -32730,7 +32518,7 @@
         <v>1.04</v>
       </c>
       <c r="AH175">
-        <v>0.68640000000000001</v>
+        <v>0.68640000000000012</v>
       </c>
       <c r="AI175">
         <v>8.4171999999999997E-2</v>
@@ -32846,7 +32634,7 @@
         <v>0.24310000000000001</v>
       </c>
       <c r="AI176">
-        <v>0.14538799999999999</v>
+        <v>0.14538800000000002</v>
       </c>
       <c r="AJ176">
         <v>1.5768000000000001E-2</v>
@@ -32959,7 +32747,7 @@
         <v>0.25740000000000002</v>
       </c>
       <c r="AI177">
-        <v>0.29077599999999998</v>
+        <v>0.29077600000000003</v>
       </c>
       <c r="AJ177">
         <v>8.5847999999999994E-2</v>
@@ -33298,7 +33086,7 @@
         <v>0.45760000000000001</v>
       </c>
       <c r="AI180">
-        <v>0.71163600000000005</v>
+        <v>0.71163599999999994</v>
       </c>
       <c r="AJ180">
         <v>5.6939999999999998E-2</v>
@@ -33408,7 +33196,7 @@
         <v>1.92</v>
       </c>
       <c r="AH181">
-        <v>0.68640000000000001</v>
+        <v>0.68640000000000012</v>
       </c>
       <c r="AI181">
         <v>0.61981200000000003</v>
@@ -33521,7 +33309,7 @@
         <v>2</v>
       </c>
       <c r="AH182">
-        <v>1.2584</v>
+        <v>1.2584000000000002</v>
       </c>
       <c r="AI182">
         <v>4.5912000000000001E-2</v>
@@ -33530,7 +33318,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AK182">
-        <v>4.8209559999999998</v>
+        <v>4.8209560000000007</v>
       </c>
     </row>
     <row r="183" spans="1:37">
@@ -33634,10 +33422,10 @@
         <v>0</v>
       </c>
       <c r="AH183">
-        <v>0.40039999999999998</v>
+        <v>0.40040000000000003</v>
       </c>
       <c r="AI183">
-        <v>0.56624799999999997</v>
+        <v>0.56624800000000008</v>
       </c>
       <c r="AJ183">
         <v>1.8395999999999999E-2</v>
@@ -33869,7 +33657,7 @@
         <v>4.6427999999999997E-2</v>
       </c>
       <c r="AK185">
-        <v>2.0038719999999999</v>
+        <v>2.0038720000000003</v>
       </c>
     </row>
     <row r="186" spans="1:37">
@@ -33979,7 +33767,7 @@
         <v>0.92589200000000005</v>
       </c>
       <c r="AJ186">
-        <v>4.9056000000000002E-2</v>
+        <v>4.9055999999999995E-2</v>
       </c>
       <c r="AK186">
         <v>3.7749480000000002</v>
@@ -34095,7 +33883,7 @@
         <v>7.8840000000000004E-3</v>
       </c>
       <c r="AK187">
-        <v>7.7233080000000003</v>
+        <v>7.7233079999999994</v>
       </c>
     </row>
     <row r="188" spans="1:37">
@@ -34199,13 +33987,13 @@
         <v>0.2</v>
       </c>
       <c r="AH188">
-        <v>0.95809999999999995</v>
+        <v>0.95810000000000006</v>
       </c>
       <c r="AI188">
-        <v>0.15304000000000001</v>
+        <v>0.15303999999999998</v>
       </c>
       <c r="AJ188">
-        <v>7.7088000000000004E-2</v>
+        <v>7.708799999999999E-2</v>
       </c>
       <c r="AK188">
         <v>3.4282279999999998</v>
@@ -34312,7 +34100,7 @@
         <v>0.36</v>
       </c>
       <c r="AH189">
-        <v>0.95809999999999995</v>
+        <v>0.95810000000000006</v>
       </c>
       <c r="AI189">
         <v>0.214256</v>
@@ -34321,7 +34109,7 @@
         <v>0.11388</v>
       </c>
       <c r="AK189">
-        <v>2.2462360000000001</v>
+        <v>2.2462359999999997</v>
       </c>
     </row>
     <row r="190" spans="1:37">
@@ -34660,7 +34448,7 @@
         <v>5.2560000000000003E-3</v>
       </c>
       <c r="AK192">
-        <v>8.7729040000000005</v>
+        <v>8.7729039999999987</v>
       </c>
     </row>
     <row r="193" spans="1:37">
@@ -34773,7 +34561,7 @@
         <v>0</v>
       </c>
       <c r="AK193">
-        <v>3.8340000000000001</v>
+        <v>3.8339999999999996</v>
       </c>
     </row>
     <row r="194" spans="1:37">
@@ -34999,7 +34787,7 @@
         <v>2.3651999999999999E-2</v>
       </c>
       <c r="AK195">
-        <v>2.7719800000000001</v>
+        <v>2.7719799999999997</v>
       </c>
     </row>
     <row r="196" spans="1:37">
@@ -35106,7 +34894,7 @@
         <v>0.18590000000000001</v>
       </c>
       <c r="AI196">
-        <v>0.22955999999999999</v>
+        <v>0.22956000000000001</v>
       </c>
       <c r="AJ196">
         <v>4.2923999999999997E-2</v>
@@ -35329,13 +35117,13 @@
         <v>0</v>
       </c>
       <c r="AH198">
-        <v>0.40039999999999998</v>
+        <v>0.40040000000000003</v>
       </c>
       <c r="AI198">
         <v>0.160692</v>
       </c>
       <c r="AJ198">
-        <v>0.111252</v>
+        <v>0.11125199999999999</v>
       </c>
       <c r="AK198">
         <v>1.092344</v>
@@ -35445,10 +35233,10 @@
         <v>0.6149</v>
       </c>
       <c r="AI199">
-        <v>0.15304000000000001</v>
+        <v>0.15303999999999998</v>
       </c>
       <c r="AJ199">
-        <v>3.9419999999999997E-2</v>
+        <v>3.9420000000000004E-2</v>
       </c>
       <c r="AK199">
         <v>7.6473599999999999</v>
@@ -36017,7 +35805,7 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.90947999999999996</v>
+        <v>0.90948000000000007</v>
       </c>
       <c r="AI3">
         <v>0.46400000000000002</v>
@@ -36026,7 +35814,7 @@
         <v>7.5336E-2</v>
       </c>
       <c r="AK3">
-        <v>4.2088159999999997</v>
+        <v>4.2088160000000006</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -36356,7 +36144,7 @@
         <v>0.24</v>
       </c>
       <c r="AH6">
-        <v>0.39467999999999998</v>
+        <v>0.39468000000000003</v>
       </c>
       <c r="AI6">
         <v>0.99199999999999999</v>
@@ -36469,7 +36257,7 @@
         <v>2.56</v>
       </c>
       <c r="AH7">
-        <v>0.18876000000000001</v>
+        <v>0.18875999999999998</v>
       </c>
       <c r="AI7">
         <v>1.296</v>
@@ -36582,16 +36370,16 @@
         <v>1.4</v>
       </c>
       <c r="AH8">
-        <v>0.25740000000000002</v>
+        <v>0.25739999999999996</v>
       </c>
       <c r="AI8">
         <v>0.27200000000000002</v>
       </c>
       <c r="AJ8">
-        <v>6.0443999999999998E-2</v>
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="AK8">
-        <v>4.0298439999999998</v>
+        <v>4.0298440000000006</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -36701,10 +36489,10 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="AJ9">
-        <v>6.0443999999999998E-2</v>
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="AK9">
-        <v>7.078964</v>
+        <v>7.0789640000000009</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -36817,7 +36605,7 @@
         <v>8.3220000000000002E-2</v>
       </c>
       <c r="AK10">
-        <v>7.0398199999999997</v>
+        <v>7.0398200000000006</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -37269,7 +37057,7 @@
         <v>0</v>
       </c>
       <c r="AK14">
-        <v>7.8390000000000004</v>
+        <v>7.8389999999999995</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -37379,10 +37167,10 @@
         <v>0.70399999999999996</v>
       </c>
       <c r="AJ15">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AK15">
-        <v>8.5188919999999992</v>
+        <v>8.518892000000001</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -37486,7 +37274,7 @@
         <v>0.8</v>
       </c>
       <c r="AH16">
-        <v>0.25740000000000002</v>
+        <v>0.25739999999999996</v>
       </c>
       <c r="AI16">
         <v>0.94399999999999995</v>
@@ -37599,7 +37387,7 @@
         <v>2.48</v>
       </c>
       <c r="AH17">
-        <v>1.83612</v>
+        <v>1.8361200000000002</v>
       </c>
       <c r="AI17">
         <v>0.128</v>
@@ -37834,7 +37622,7 @@
         <v>0</v>
       </c>
       <c r="AK19">
-        <v>10.214399999999999</v>
+        <v>10.214400000000001</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -38277,13 +38065,13 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="AH23">
-        <v>0.41183999999999998</v>
+        <v>0.41184000000000004</v>
       </c>
       <c r="AI23">
         <v>0.128</v>
       </c>
       <c r="AJ23">
-        <v>4.9056000000000002E-2</v>
+        <v>4.9055999999999995E-2</v>
       </c>
       <c r="AK23">
         <v>7.3288960000000003</v>
@@ -38396,10 +38184,10 @@
         <v>0.60799999999999998</v>
       </c>
       <c r="AJ24">
-        <v>7.8839999999999993E-2</v>
+        <v>7.8840000000000007E-2</v>
       </c>
       <c r="AK24">
-        <v>5.2500400000000003</v>
+        <v>5.2500399999999994</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -38503,7 +38291,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="AH25">
-        <v>1.5615600000000001</v>
+        <v>1.5615599999999998</v>
       </c>
       <c r="AI25">
         <v>1.36</v>
@@ -38729,16 +38517,16 @@
         <v>0.24</v>
       </c>
       <c r="AH27">
-        <v>2.2307999999999999</v>
+        <v>2.2308000000000003</v>
       </c>
       <c r="AI27">
         <v>0</v>
       </c>
       <c r="AJ27">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="AK27">
-        <v>3.0353279999999998</v>
+        <v>3.0353280000000007</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -38848,10 +38636,10 @@
         <v>0.35199999999999998</v>
       </c>
       <c r="AJ28">
-        <v>3.2412000000000003E-2</v>
+        <v>3.2411999999999996E-2</v>
       </c>
       <c r="AK28">
-        <v>9.3302119999999995</v>
+        <v>9.3302120000000013</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -38964,7 +38752,7 @@
         <v>2.1899999999999999E-2</v>
       </c>
       <c r="AK29">
-        <v>6.1219000000000001</v>
+        <v>6.1218999999999992</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -39077,7 +38865,7 @@
         <v>5.8692000000000001E-2</v>
       </c>
       <c r="AK30">
-        <v>7.4316519999999997</v>
+        <v>7.4316520000000006</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -39294,7 +39082,7 @@
         <v>2.48</v>
       </c>
       <c r="AH32">
-        <v>0.90947999999999996</v>
+        <v>0.90948000000000007</v>
       </c>
       <c r="AI32">
         <v>1.248</v>
@@ -39303,7 +39091,7 @@
         <v>1.8395999999999999E-2</v>
       </c>
       <c r="AK32">
-        <v>5.7958759999999998</v>
+        <v>5.7958760000000007</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -39529,7 +39317,7 @@
         <v>4.3800000000000002E-3</v>
       </c>
       <c r="AK34">
-        <v>5.4375400000000003</v>
+        <v>5.4375400000000012</v>
       </c>
     </row>
     <row r="35" spans="1:37">
@@ -39633,7 +39421,7 @@
         <v>1.24</v>
       </c>
       <c r="AH35">
-        <v>0.82367999999999997</v>
+        <v>0.82368000000000008</v>
       </c>
       <c r="AI35">
         <v>0.752</v>
@@ -39978,10 +39766,10 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="AJ38">
-        <v>3.9419999999999997E-2</v>
+        <v>3.9420000000000004E-2</v>
       </c>
       <c r="AK38">
-        <v>5.6784999999999997</v>
+        <v>5.6785000000000005</v>
       </c>
     </row>
     <row r="39" spans="1:37">
@@ -40094,7 +39882,7 @@
         <v>0.108624</v>
       </c>
       <c r="AK39">
-        <v>3.866784</v>
+        <v>3.8667839999999996</v>
       </c>
     </row>
     <row r="40" spans="1:37">
@@ -40198,13 +39986,13 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="AH40">
-        <v>0.18876000000000001</v>
+        <v>0.18875999999999998</v>
       </c>
       <c r="AI40">
         <v>1.4079999999999999</v>
       </c>
       <c r="AJ40">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AK40">
         <v>6.2265439999999996</v>
@@ -40311,7 +40099,7 @@
         <v>0</v>
       </c>
       <c r="AH41">
-        <v>0.75504000000000004</v>
+        <v>0.75503999999999993</v>
       </c>
       <c r="AI41">
         <v>0.752</v>
@@ -40320,7 +40108,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="AK41">
-        <v>7.9358000000000004</v>
+        <v>7.9357999999999995</v>
       </c>
     </row>
     <row r="42" spans="1:37">
@@ -40424,7 +40212,7 @@
         <v>0.36</v>
       </c>
       <c r="AH42">
-        <v>0.37752000000000002</v>
+        <v>0.37751999999999997</v>
       </c>
       <c r="AI42">
         <v>0.35199999999999998</v>
@@ -40433,7 +40221,7 @@
         <v>4.2048000000000002E-2</v>
       </c>
       <c r="AK42">
-        <v>4.6715679999999997</v>
+        <v>4.6715680000000006</v>
       </c>
     </row>
     <row r="43" spans="1:37">
@@ -40882,10 +40670,10 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="AJ46">
-        <v>9.8988000000000007E-2</v>
+        <v>9.8987999999999993E-2</v>
       </c>
       <c r="AK46">
-        <v>2.6694279999999999</v>
+        <v>2.6694280000000004</v>
       </c>
     </row>
     <row r="47" spans="1:37">
@@ -41111,7 +40899,7 @@
         <v>8.3220000000000002E-2</v>
       </c>
       <c r="AK48">
-        <v>5.3192199999999996</v>
+        <v>5.3192200000000005</v>
       </c>
     </row>
     <row r="49" spans="1:37">
@@ -41224,7 +41012,7 @@
         <v>3.6791999999999998E-2</v>
       </c>
       <c r="AK49">
-        <v>2.7481119999999999</v>
+        <v>2.7481120000000003</v>
       </c>
     </row>
     <row r="50" spans="1:37">
@@ -41337,7 +41125,7 @@
         <v>4.1172E-2</v>
       </c>
       <c r="AK50">
-        <v>6.6731319999999998</v>
+        <v>6.6731320000000007</v>
       </c>
     </row>
     <row r="51" spans="1:37">
@@ -41560,10 +41348,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ52">
-        <v>1.2264000000000001E-2</v>
+        <v>1.2263999999999999E-2</v>
       </c>
       <c r="AK52">
-        <v>6.8044640000000003</v>
+        <v>6.8044639999999994</v>
       </c>
     </row>
     <row r="53" spans="1:37">
@@ -41667,7 +41455,7 @@
         <v>5.84</v>
       </c>
       <c r="AH53">
-        <v>0.29171999999999998</v>
+        <v>0.29172000000000003</v>
       </c>
       <c r="AI53">
         <v>0</v>
@@ -41676,7 +41464,7 @@
         <v>3.3287999999999998E-2</v>
       </c>
       <c r="AK53">
-        <v>7.845008</v>
+        <v>7.8450079999999991</v>
       </c>
     </row>
     <row r="54" spans="1:37">
@@ -41786,7 +41574,7 @@
         <v>0.752</v>
       </c>
       <c r="AJ54">
-        <v>6.0443999999999998E-2</v>
+        <v>6.0444000000000005E-2</v>
       </c>
       <c r="AK54">
         <v>4.4982439999999997</v>
@@ -41902,7 +41690,7 @@
         <v>4.2048000000000002E-2</v>
       </c>
       <c r="AK55">
-        <v>8.4180480000000006</v>
+        <v>8.4180479999999989</v>
       </c>
     </row>
     <row r="56" spans="1:37">
@@ -42128,7 +41916,7 @@
         <v>5.0807999999999999E-2</v>
       </c>
       <c r="AK57">
-        <v>4.4141279999999998</v>
+        <v>4.4141280000000007</v>
       </c>
     </row>
     <row r="58" spans="1:37">
@@ -42354,7 +42142,7 @@
         <v>0.123516</v>
       </c>
       <c r="AK59">
-        <v>3.0297559999999999</v>
+        <v>3.0297560000000003</v>
       </c>
     </row>
     <row r="60" spans="1:37">
@@ -42580,7 +42368,7 @@
         <v>0</v>
       </c>
       <c r="AK61">
-        <v>5.3726799999999999</v>
+        <v>5.3726800000000008</v>
       </c>
     </row>
     <row r="62" spans="1:37">
@@ -42690,7 +42478,7 @@
         <v>0.72</v>
       </c>
       <c r="AJ62">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="AK62">
         <v>1.065312</v>
@@ -42806,7 +42594,7 @@
         <v>7.9715999999999995E-2</v>
       </c>
       <c r="AK63">
-        <v>5.7477159999999996</v>
+        <v>5.7477160000000005</v>
       </c>
     </row>
     <row r="64" spans="1:37">
@@ -42910,7 +42698,7 @@
         <v>1.84</v>
       </c>
       <c r="AH64">
-        <v>2.4367200000000002</v>
+        <v>2.4367199999999998</v>
       </c>
       <c r="AI64">
         <v>0</v>
@@ -43023,7 +42811,7 @@
         <v>4.2</v>
       </c>
       <c r="AH65">
-        <v>1.08108</v>
+        <v>1.0810799999999998</v>
       </c>
       <c r="AI65">
         <v>0.224</v>
@@ -43136,7 +42924,7 @@
         <v>5.16</v>
       </c>
       <c r="AH66">
-        <v>0.87516000000000005</v>
+        <v>0.87515999999999994</v>
       </c>
       <c r="AI66">
         <v>0.36799999999999999</v>
@@ -43145,7 +42933,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AK66">
-        <v>7.6198040000000002</v>
+        <v>7.6198040000000011</v>
       </c>
     </row>
     <row r="67" spans="1:37">
@@ -43249,7 +43037,7 @@
         <v>0</v>
       </c>
       <c r="AH67">
-        <v>1.5615600000000001</v>
+        <v>1.5615599999999998</v>
       </c>
       <c r="AI67">
         <v>0.112</v>
@@ -43258,7 +43046,7 @@
         <v>1.8395999999999999E-2</v>
       </c>
       <c r="AK67">
-        <v>6.0119559999999996</v>
+        <v>6.0119560000000005</v>
       </c>
     </row>
     <row r="68" spans="1:37">
@@ -43362,7 +43150,7 @@
         <v>4.8</v>
       </c>
       <c r="AH68">
-        <v>0.41183999999999998</v>
+        <v>0.41184000000000004</v>
       </c>
       <c r="AI68">
         <v>0.28799999999999998</v>
@@ -43475,13 +43263,13 @@
         <v>1.6</v>
       </c>
       <c r="AH69">
-        <v>0.29171999999999998</v>
+        <v>0.29172000000000003</v>
       </c>
       <c r="AI69">
         <v>0.89600000000000002</v>
       </c>
       <c r="AJ69">
-        <v>4.9931999999999997E-2</v>
+        <v>4.9932000000000004E-2</v>
       </c>
       <c r="AK69">
         <v>6.7976520000000002</v>
@@ -43710,7 +43498,7 @@
         <v>9.7236000000000003E-2</v>
       </c>
       <c r="AK71">
-        <v>4.6972360000000002</v>
+        <v>4.6972359999999993</v>
       </c>
     </row>
     <row r="72" spans="1:37">
@@ -43820,7 +43608,7 @@
         <v>1.04</v>
       </c>
       <c r="AJ72">
-        <v>5.9568000000000003E-2</v>
+        <v>5.9567999999999996E-2</v>
       </c>
       <c r="AK72">
         <v>6.1027680000000002</v>
@@ -44046,7 +43834,7 @@
         <v>2.64</v>
       </c>
       <c r="AJ74">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="AK74">
         <v>5.2661319999999998</v>
@@ -44153,7 +43941,7 @@
         <v>1.24</v>
       </c>
       <c r="AH75">
-        <v>0.41183999999999998</v>
+        <v>0.41184000000000004</v>
       </c>
       <c r="AI75">
         <v>0.24</v>
@@ -44379,13 +44167,13 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="AH77">
-        <v>0.10296</v>
+        <v>0.10296000000000001</v>
       </c>
       <c r="AI77">
         <v>0</v>
       </c>
       <c r="AJ77">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AK77">
         <v>5.5578519999999996</v>
@@ -44492,16 +44280,16 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="AH78">
-        <v>0.10296</v>
+        <v>0.10296000000000001</v>
       </c>
       <c r="AI78">
         <v>0</v>
       </c>
       <c r="AJ78">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AK78">
-        <v>5.5178520000000004</v>
+        <v>5.5178519999999995</v>
       </c>
     </row>
     <row r="79" spans="1:37">
@@ -44718,7 +44506,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="AH80">
-        <v>0.63492000000000004</v>
+        <v>0.63491999999999993</v>
       </c>
       <c r="AI80">
         <v>0.17599999999999999</v>
@@ -44727,7 +44515,7 @@
         <v>3.7668E-2</v>
       </c>
       <c r="AK80">
-        <v>2.928588</v>
+        <v>2.9285880000000004</v>
       </c>
     </row>
     <row r="81" spans="1:37">
@@ -44837,7 +44625,7 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="AJ81">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AK81">
         <v>4.1828640000000004</v>
@@ -44953,7 +44741,7 @@
         <v>8.4096000000000004E-2</v>
       </c>
       <c r="AK82">
-        <v>3.7583359999999999</v>
+        <v>3.7583360000000003</v>
       </c>
     </row>
     <row r="83" spans="1:37">
@@ -45509,7 +45297,7 @@
         <v>0.68</v>
       </c>
       <c r="AH87">
-        <v>1.35564</v>
+        <v>1.3556400000000002</v>
       </c>
       <c r="AI87">
         <v>0.8</v>
@@ -45518,7 +45306,7 @@
         <v>7.0956000000000005E-2</v>
       </c>
       <c r="AK87">
-        <v>3.3265959999999999</v>
+        <v>3.3265960000000003</v>
       </c>
     </row>
     <row r="88" spans="1:37">
@@ -45631,7 +45419,7 @@
         <v>2.8908E-2</v>
       </c>
       <c r="AK88">
-        <v>5.3452279999999996</v>
+        <v>5.3452280000000005</v>
       </c>
     </row>
     <row r="89" spans="1:37">
@@ -45848,13 +45636,13 @@
         <v>0.2</v>
       </c>
       <c r="AH90">
-        <v>1.1668799999999999</v>
+        <v>1.1668800000000001</v>
       </c>
       <c r="AI90">
         <v>2.3199999999999998</v>
       </c>
       <c r="AJ90">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="AK90">
         <v>3.693012</v>
@@ -45961,13 +45749,13 @@
         <v>0.24</v>
       </c>
       <c r="AH91">
-        <v>0.25740000000000002</v>
+        <v>0.25739999999999996</v>
       </c>
       <c r="AI91">
         <v>0.96</v>
       </c>
       <c r="AJ91">
-        <v>0.11300399999999999</v>
+        <v>0.11300400000000001</v>
       </c>
       <c r="AK91">
         <v>1.5704039999999999</v>
@@ -46306,7 +46094,7 @@
         <v>0.36799999999999999</v>
       </c>
       <c r="AJ94">
-        <v>3.8544000000000002E-2</v>
+        <v>3.8543999999999995E-2</v>
       </c>
       <c r="AK94">
         <v>6.5127040000000003</v>
@@ -46639,7 +46427,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="AH97">
-        <v>0.70355999999999996</v>
+        <v>0.70356000000000007</v>
       </c>
       <c r="AI97">
         <v>0.27200000000000002</v>
@@ -46752,16 +46540,16 @@
         <v>0</v>
       </c>
       <c r="AH98">
-        <v>0.49764000000000003</v>
+        <v>0.49763999999999997</v>
       </c>
       <c r="AI98">
         <v>0.624</v>
       </c>
       <c r="AJ98">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="AK98">
-        <v>9.1209120000000006</v>
+        <v>9.1209120000000024</v>
       </c>
     </row>
     <row r="99" spans="1:37">
@@ -46978,7 +46766,7 @@
         <v>7.52</v>
       </c>
       <c r="AH100">
-        <v>0.20591999999999999</v>
+        <v>0.20592000000000002</v>
       </c>
       <c r="AI100">
         <v>0.112</v>
@@ -46987,7 +46775,7 @@
         <v>1.5768000000000001E-2</v>
       </c>
       <c r="AK100">
-        <v>7.853688</v>
+        <v>7.8536879999999991</v>
       </c>
     </row>
     <row r="101" spans="1:37">
@@ -47091,7 +46879,7 @@
         <v>3.2</v>
       </c>
       <c r="AH101">
-        <v>0.20591999999999999</v>
+        <v>0.20592000000000002</v>
       </c>
       <c r="AI101">
         <v>0.33600000000000002</v>
@@ -47430,7 +47218,7 @@
         <v>2.96</v>
       </c>
       <c r="AH104">
-        <v>0.51480000000000004</v>
+        <v>0.51479999999999992</v>
       </c>
       <c r="AI104">
         <v>1.84</v>
@@ -47543,7 +47331,7 @@
         <v>2.52</v>
       </c>
       <c r="AH105">
-        <v>0.87516000000000005</v>
+        <v>0.87515999999999994</v>
       </c>
       <c r="AI105">
         <v>0.83199999999999996</v>
@@ -47662,10 +47450,10 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="AJ106">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="AK106">
-        <v>8.2058319999999991</v>
+        <v>8.2058320000000009</v>
       </c>
     </row>
     <row r="107" spans="1:37">
@@ -47769,7 +47557,7 @@
         <v>0</v>
       </c>
       <c r="AH107">
-        <v>0.37752000000000002</v>
+        <v>0.37751999999999997</v>
       </c>
       <c r="AI107">
         <v>0.08</v>
@@ -47888,7 +47676,7 @@
         <v>0.70399999999999996</v>
       </c>
       <c r="AJ108">
-        <v>0.11913600000000001</v>
+        <v>0.11913599999999999</v>
       </c>
       <c r="AK108">
         <v>0.82313599999999998</v>
@@ -48001,7 +47789,7 @@
         <v>1.232</v>
       </c>
       <c r="AJ109">
-        <v>6.4824000000000007E-2</v>
+        <v>6.4823999999999993E-2</v>
       </c>
       <c r="AK109">
         <v>1.796824</v>
@@ -48334,7 +48122,7 @@
         <v>0</v>
       </c>
       <c r="AH112">
-        <v>0.66923999999999995</v>
+        <v>0.66924000000000006</v>
       </c>
       <c r="AI112">
         <v>0.08</v>
@@ -48569,7 +48357,7 @@
         <v>0.11826</v>
       </c>
       <c r="AK114">
-        <v>2.1701800000000002</v>
+        <v>2.1701799999999998</v>
       </c>
     </row>
     <row r="115" spans="1:37">
@@ -48682,7 +48470,7 @@
         <v>2.2776000000000001E-2</v>
       </c>
       <c r="AK115">
-        <v>2.3780960000000002</v>
+        <v>2.3780959999999998</v>
       </c>
     </row>
     <row r="116" spans="1:37">
@@ -48786,7 +48574,7 @@
         <v>0</v>
       </c>
       <c r="AH116">
-        <v>0.66923999999999995</v>
+        <v>0.66924000000000006</v>
       </c>
       <c r="AI116">
         <v>0.752</v>
@@ -48795,7 +48583,7 @@
         <v>3.3287999999999998E-2</v>
       </c>
       <c r="AK116">
-        <v>8.7145279999999996</v>
+        <v>8.7145280000000014</v>
       </c>
     </row>
     <row r="117" spans="1:37">
@@ -48908,7 +48696,7 @@
         <v>2.2776000000000001E-2</v>
       </c>
       <c r="AK117">
-        <v>2.8805360000000002</v>
+        <v>2.8805359999999998</v>
       </c>
     </row>
     <row r="118" spans="1:37">
@@ -49018,7 +48806,7 @@
         <v>0.32</v>
       </c>
       <c r="AJ118">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="AK118">
         <v>8.093712</v>
@@ -49131,10 +48919,10 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="AJ119">
-        <v>0.11300399999999999</v>
+        <v>0.11300400000000001</v>
       </c>
       <c r="AK119">
-        <v>3.2234440000000002</v>
+        <v>3.2234440000000006</v>
       </c>
     </row>
     <row r="120" spans="1:37">
@@ -49238,7 +49026,7 @@
         <v>1.64</v>
       </c>
       <c r="AH120">
-        <v>1.8018000000000001</v>
+        <v>1.8017999999999998</v>
       </c>
       <c r="AI120">
         <v>0.56000000000000005</v>
@@ -49247,7 +49035,7 @@
         <v>0</v>
       </c>
       <c r="AK120">
-        <v>4.0018000000000002</v>
+        <v>4.0017999999999994</v>
       </c>
     </row>
     <row r="121" spans="1:37">
@@ -49351,7 +49139,7 @@
         <v>1.36</v>
       </c>
       <c r="AH121">
-        <v>0.63492000000000004</v>
+        <v>0.63491999999999993</v>
       </c>
       <c r="AI121">
         <v>0.432</v>
@@ -49464,7 +49252,7 @@
         <v>0.2</v>
       </c>
       <c r="AH122">
-        <v>0.49764000000000003</v>
+        <v>0.49763999999999997</v>
       </c>
       <c r="AI122">
         <v>1.1359999999999999</v>
@@ -49812,7 +49600,7 @@
         <v>1.3140000000000001E-2</v>
       </c>
       <c r="AK125">
-        <v>7.6371399999999996</v>
+        <v>7.6371400000000005</v>
       </c>
     </row>
     <row r="126" spans="1:37">
@@ -50255,7 +50043,7 @@
         <v>0</v>
       </c>
       <c r="AH129">
-        <v>0.75504000000000004</v>
+        <v>0.75503999999999993</v>
       </c>
       <c r="AI129">
         <v>1.008</v>
@@ -50264,7 +50052,7 @@
         <v>7.7964000000000006E-2</v>
       </c>
       <c r="AK129">
-        <v>2.3810039999999999</v>
+        <v>2.3810040000000003</v>
       </c>
     </row>
     <row r="130" spans="1:37">
@@ -50594,7 +50382,7 @@
         <v>7.36</v>
       </c>
       <c r="AH132">
-        <v>0.66923999999999995</v>
+        <v>0.66924000000000006</v>
       </c>
       <c r="AI132">
         <v>0</v>
@@ -50707,7 +50495,7 @@
         <v>1.36</v>
       </c>
       <c r="AH133">
-        <v>0.37752000000000002</v>
+        <v>0.37751999999999997</v>
       </c>
       <c r="AI133">
         <v>0.76800000000000002</v>
@@ -50820,13 +50608,13 @@
         <v>3.24</v>
       </c>
       <c r="AH134">
-        <v>0.51480000000000004</v>
+        <v>0.51479999999999992</v>
       </c>
       <c r="AI134">
         <v>1.8879999999999999</v>
       </c>
       <c r="AJ134">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="AK134">
         <v>6.4889320000000001</v>
@@ -51046,7 +50834,7 @@
         <v>1.64</v>
       </c>
       <c r="AH136">
-        <v>0.10296</v>
+        <v>0.10296000000000001</v>
       </c>
       <c r="AI136">
         <v>0.65600000000000003</v>
@@ -51055,7 +50843,7 @@
         <v>0.103368</v>
       </c>
       <c r="AK136">
-        <v>3.5223279999999999</v>
+        <v>3.5223280000000003</v>
       </c>
     </row>
     <row r="137" spans="1:37">
@@ -51159,7 +50947,7 @@
         <v>0.64</v>
       </c>
       <c r="AH137">
-        <v>2.6426400000000001</v>
+        <v>2.6426399999999997</v>
       </c>
       <c r="AI137">
         <v>0</v>
@@ -51278,7 +51066,7 @@
         <v>0.78400000000000003</v>
       </c>
       <c r="AJ138">
-        <v>0.138408</v>
+        <v>0.13840799999999998</v>
       </c>
       <c r="AK138">
         <v>1.4543680000000001</v>
@@ -51385,7 +51173,7 @@
         <v>0.48</v>
       </c>
       <c r="AH139">
-        <v>0.63492000000000004</v>
+        <v>0.63491999999999993</v>
       </c>
       <c r="AI139">
         <v>0.68799999999999994</v>
@@ -51498,13 +51286,13 @@
         <v>1.64</v>
       </c>
       <c r="AH140">
-        <v>2.1621600000000001</v>
+        <v>2.1621599999999996</v>
       </c>
       <c r="AI140">
         <v>0.128</v>
       </c>
       <c r="AJ140">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="AK140">
         <v>3.954688</v>
@@ -51620,7 +51408,7 @@
         <v>0.14629200000000001</v>
       </c>
       <c r="AK141">
-        <v>1.986772</v>
+        <v>1.9867720000000002</v>
       </c>
     </row>
     <row r="142" spans="1:37">
@@ -51837,7 +51625,7 @@
         <v>0.44</v>
       </c>
       <c r="AH143">
-        <v>0.39467999999999998</v>
+        <v>0.39468000000000003</v>
       </c>
       <c r="AI143">
         <v>1.1200000000000001</v>
@@ -51846,7 +51634,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AK143">
-        <v>7.3113239999999999</v>
+        <v>7.3113240000000008</v>
       </c>
     </row>
     <row r="144" spans="1:37">
@@ -51956,7 +51744,7 @@
         <v>0.81599999999999995</v>
       </c>
       <c r="AJ144">
-        <v>0.111252</v>
+        <v>0.11125199999999999</v>
       </c>
       <c r="AK144">
         <v>2.3676119999999998</v>
@@ -52063,7 +51851,7 @@
         <v>0</v>
       </c>
       <c r="AH145">
-        <v>0.49764000000000003</v>
+        <v>0.49763999999999997</v>
       </c>
       <c r="AI145">
         <v>0.68799999999999994</v>
@@ -52072,7 +51860,7 @@
         <v>7.0080000000000003E-3</v>
       </c>
       <c r="AK145">
-        <v>10.432648</v>
+        <v>10.432648000000002</v>
       </c>
     </row>
     <row r="146" spans="1:37">
@@ -52176,7 +51964,7 @@
         <v>1.24</v>
       </c>
       <c r="AH146">
-        <v>2.1621600000000001</v>
+        <v>2.1621599999999996</v>
       </c>
       <c r="AI146">
         <v>0.16</v>
@@ -52185,7 +51973,7 @@
         <v>2.1899999999999999E-2</v>
       </c>
       <c r="AK146">
-        <v>4.54406</v>
+        <v>4.5440599999999991</v>
       </c>
     </row>
     <row r="147" spans="1:37">
@@ -52402,7 +52190,7 @@
         <v>4.28</v>
       </c>
       <c r="AH148">
-        <v>0.66923999999999995</v>
+        <v>0.66924000000000006</v>
       </c>
       <c r="AI148">
         <v>0.86399999999999999</v>
@@ -52521,10 +52309,10 @@
         <v>1.52</v>
       </c>
       <c r="AJ149">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AK149">
-        <v>4.7502639999999996</v>
+        <v>4.7502640000000005</v>
       </c>
     </row>
     <row r="150" spans="1:37">
@@ -52628,7 +52416,7 @@
         <v>2.88</v>
       </c>
       <c r="AH150">
-        <v>0.49764000000000003</v>
+        <v>0.49763999999999997</v>
       </c>
       <c r="AI150">
         <v>1.024</v>
@@ -52637,7 +52425,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="AK150">
-        <v>4.7103999999999999</v>
+        <v>4.710399999999999</v>
       </c>
     </row>
     <row r="151" spans="1:37">
@@ -52747,7 +52535,7 @@
         <v>0.24</v>
       </c>
       <c r="AJ151">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AK151">
         <v>6.3742760000000001</v>
@@ -52854,7 +52642,7 @@
         <v>2.04</v>
       </c>
       <c r="AH152">
-        <v>0.70355999999999996</v>
+        <v>0.70356000000000007</v>
       </c>
       <c r="AI152">
         <v>1.1519999999999999</v>
@@ -52863,7 +52651,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AK152">
-        <v>7.4522040000000001</v>
+        <v>7.4522040000000009</v>
       </c>
     </row>
     <row r="153" spans="1:37">
@@ -53086,7 +52874,7 @@
         <v>0</v>
       </c>
       <c r="AJ154">
-        <v>8.4972000000000006E-2</v>
+        <v>8.4971999999999992E-2</v>
       </c>
       <c r="AK154">
         <v>6.673972</v>
@@ -53538,10 +53326,10 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="AJ158">
-        <v>0.11913600000000001</v>
+        <v>0.11913599999999999</v>
       </c>
       <c r="AK158">
-        <v>3.931136</v>
+        <v>3.9311360000000004</v>
       </c>
     </row>
     <row r="159" spans="1:37">
@@ -53651,7 +53439,7 @@
         <v>0.112</v>
       </c>
       <c r="AJ159">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AK159">
         <v>3.450904</v>
@@ -53758,7 +53546,7 @@
         <v>0.64</v>
       </c>
       <c r="AH160">
-        <v>1.59588</v>
+        <v>1.5958800000000002</v>
       </c>
       <c r="AI160">
         <v>0</v>
@@ -53877,7 +53665,7 @@
         <v>0.70399999999999996</v>
       </c>
       <c r="AJ161">
-        <v>0.11913600000000001</v>
+        <v>0.11913599999999999</v>
       </c>
       <c r="AK161">
         <v>1.8347359999999999</v>
@@ -54210,7 +53998,7 @@
         <v>2.84</v>
       </c>
       <c r="AH164">
-        <v>0.58343999999999996</v>
+        <v>0.58344000000000007</v>
       </c>
       <c r="AI164">
         <v>0.128</v>
@@ -54219,7 +54007,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AK164">
-        <v>5.6080839999999998</v>
+        <v>5.6080840000000007</v>
       </c>
     </row>
     <row r="165" spans="1:37">
@@ -54329,7 +54117,7 @@
         <v>0.28799999999999998</v>
       </c>
       <c r="AJ165">
-        <v>9.8112000000000005E-2</v>
+        <v>9.8111999999999991E-2</v>
       </c>
       <c r="AK165">
         <v>2.5928719999999998</v>
@@ -54445,7 +54233,7 @@
         <v>0</v>
       </c>
       <c r="AK166">
-        <v>6.1178800000000004</v>
+        <v>6.1178799999999995</v>
       </c>
     </row>
     <row r="167" spans="1:37">
@@ -54895,7 +54683,7 @@
         <v>5.5188000000000001E-2</v>
       </c>
       <c r="AI2">
-        <v>2.791188</v>
+        <v>2.7911879999999996</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -54999,10 +54787,10 @@
         <v>0.79800000000000004</v>
       </c>
       <c r="AH3">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AI3">
-        <v>5.7076359999999999</v>
+        <v>5.7076360000000008</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -55216,7 +55004,7 @@
         <v>4.2048000000000002E-2</v>
       </c>
       <c r="AI5">
-        <v>6.6120479999999997</v>
+        <v>6.6120480000000006</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -55427,7 +55215,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>6.4824000000000007E-2</v>
+        <v>6.4823999999999993E-2</v>
       </c>
       <c r="AI7">
         <v>4.7328239999999999</v>
@@ -55644,7 +55432,7 @@
         <v>2.1024000000000001E-2</v>
       </c>
       <c r="AI9">
-        <v>5.5710240000000004</v>
+        <v>5.5710239999999995</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -55962,7 +55750,7 @@
         <v>1.5960000000000001</v>
       </c>
       <c r="AH12">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AI12">
         <v>4.5857840000000003</v>
@@ -56072,7 +55860,7 @@
         <v>0</v>
       </c>
       <c r="AI13">
-        <v>2.8839999999999999</v>
+        <v>2.8840000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -56179,7 +55967,7 @@
         <v>0</v>
       </c>
       <c r="AI14">
-        <v>3.4079999999999999</v>
+        <v>3.4080000000000004</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -56286,7 +56074,7 @@
         <v>1.5768000000000001E-2</v>
       </c>
       <c r="AI15">
-        <v>0.97176799999999997</v>
+        <v>0.97176800000000008</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -56497,7 +56285,7 @@
         <v>1.0780000000000001</v>
       </c>
       <c r="AH17">
-        <v>2.4528000000000001E-2</v>
+        <v>2.4527999999999998E-2</v>
       </c>
       <c r="AI17">
         <v>2.7825280000000001</v>
@@ -56607,7 +56395,7 @@
         <v>0.121764</v>
       </c>
       <c r="AI18">
-        <v>4.2637640000000001</v>
+        <v>4.2637639999999992</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -56711,7 +56499,7 @@
         <v>0.35</v>
       </c>
       <c r="AH19">
-        <v>7.8839999999999993E-2</v>
+        <v>7.8840000000000007E-2</v>
       </c>
       <c r="AI19">
         <v>0.90883999999999998</v>
@@ -56821,7 +56609,7 @@
         <v>4.5552000000000002E-2</v>
       </c>
       <c r="AI20">
-        <v>8.8335519999999992</v>
+        <v>8.833552000000001</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -56925,7 +56713,7 @@
         <v>0.99399999999999999</v>
       </c>
       <c r="AH21">
-        <v>1.2264000000000001E-2</v>
+        <v>1.2263999999999999E-2</v>
       </c>
       <c r="AI21">
         <v>1.6142639999999999</v>
@@ -57035,7 +56823,7 @@
         <v>0</v>
       </c>
       <c r="AI22">
-        <v>3.82</v>
+        <v>3.8200000000000003</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -57356,7 +57144,7 @@
         <v>3.6791999999999998E-2</v>
       </c>
       <c r="AI25">
-        <v>4.336792</v>
+        <v>4.3367920000000009</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -57460,10 +57248,10 @@
         <v>0.21</v>
       </c>
       <c r="AH26">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AI26">
-        <v>4.8728920000000002</v>
+        <v>4.8728919999999993</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -57570,7 +57358,7 @@
         <v>3.5915999999999997E-2</v>
       </c>
       <c r="AI27">
-        <v>6.9779159999999996</v>
+        <v>6.9779160000000005</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -57784,7 +57572,7 @@
         <v>0</v>
       </c>
       <c r="AI29">
-        <v>6.6719999999999997</v>
+        <v>6.6720000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -57995,10 +57783,10 @@
         <v>0.434</v>
       </c>
       <c r="AH31">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AI31">
-        <v>8.1237840000000006</v>
+        <v>8.1237839999999988</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -58105,7 +57893,7 @@
         <v>7.2707999999999995E-2</v>
       </c>
       <c r="AI32">
-        <v>3.8527079999999998</v>
+        <v>3.8527080000000002</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -58212,7 +58000,7 @@
         <v>0.102492</v>
       </c>
       <c r="AI33">
-        <v>3.3784920000000001</v>
+        <v>3.3784919999999996</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -58423,7 +58211,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="AH35">
-        <v>1.2264000000000001E-2</v>
+        <v>1.2263999999999999E-2</v>
       </c>
       <c r="AI35">
         <v>9.416264</v>
@@ -58533,7 +58321,7 @@
         <v>7.9715999999999995E-2</v>
       </c>
       <c r="AI36">
-        <v>3.8157160000000001</v>
+        <v>3.8157159999999997</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -58640,7 +58428,7 @@
         <v>7.6212000000000002E-2</v>
       </c>
       <c r="AI37">
-        <v>2.7562120000000001</v>
+        <v>2.7562119999999997</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -58854,7 +58642,7 @@
         <v>1.8395999999999999E-2</v>
       </c>
       <c r="AI39">
-        <v>4.8383960000000004</v>
+        <v>4.8383959999999995</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -59386,7 +59174,7 @@
         <v>0.47599999999999998</v>
       </c>
       <c r="AH44">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="AI44">
         <v>4.3192719999999998</v>
@@ -59817,7 +59605,7 @@
         <v>4.7303999999999999E-2</v>
       </c>
       <c r="AI48">
-        <v>6.6933040000000004</v>
+        <v>6.6933039999999986</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -60031,7 +59819,7 @@
         <v>8.7600000000000004E-3</v>
       </c>
       <c r="AI50">
-        <v>3.4227599999999998</v>
+        <v>3.4227600000000002</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -60349,7 +60137,7 @@
         <v>3.1219999999999999</v>
       </c>
       <c r="AH53">
-        <v>6.1320000000000003E-3</v>
+        <v>6.1319999999999994E-3</v>
       </c>
       <c r="AI53">
         <v>3.3361320000000001</v>
@@ -60884,10 +60672,10 @@
         <v>1.246</v>
       </c>
       <c r="AH58">
-        <v>6.5699999999999995E-2</v>
+        <v>6.5700000000000008E-2</v>
       </c>
       <c r="AI58">
-        <v>3.5876999999999999</v>
+        <v>3.5877000000000003</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -60994,7 +60782,7 @@
         <v>4.3800000000000002E-3</v>
       </c>
       <c r="AI59">
-        <v>3.4283800000000002</v>
+        <v>3.4283799999999998</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -61208,7 +60996,7 @@
         <v>7.8840000000000004E-3</v>
       </c>
       <c r="AI61">
-        <v>3.1098840000000001</v>
+        <v>3.1098839999999996</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -61636,7 +61424,7 @@
         <v>4.1172E-2</v>
       </c>
       <c r="AI65">
-        <v>5.1271719999999998</v>
+        <v>5.1271720000000007</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -62064,7 +61852,7 @@
         <v>8.9352000000000001E-2</v>
       </c>
       <c r="AI69">
-        <v>1.6133519999999999</v>
+        <v>1.6133520000000001</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -62171,7 +61959,7 @@
         <v>4.5552000000000002E-2</v>
       </c>
       <c r="AI70">
-        <v>2.4355519999999999</v>
+        <v>2.4355519999999995</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -62275,7 +62063,7 @@
         <v>0.44800000000000001</v>
       </c>
       <c r="AH71">
-        <v>0.107748</v>
+        <v>0.10774800000000001</v>
       </c>
       <c r="AI71">
         <v>3.0677479999999999</v>
@@ -62492,7 +62280,7 @@
         <v>4.3799999999999999E-2</v>
       </c>
       <c r="AI73">
-        <v>3.5017999999999998</v>
+        <v>3.5018000000000002</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -62596,10 +62384,10 @@
         <v>2.7160000000000002</v>
       </c>
       <c r="AH74">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AI74">
-        <v>3.9388920000000001</v>
+        <v>3.9388920000000005</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -62703,10 +62491,10 @@
         <v>2.87</v>
       </c>
       <c r="AH75">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AI75">
-        <v>4.4156360000000001</v>
+        <v>4.415636000000001</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -62810,10 +62598,10 @@
         <v>0.39200000000000002</v>
       </c>
       <c r="AH76">
-        <v>0.120888</v>
+        <v>0.12088800000000001</v>
       </c>
       <c r="AI76">
-        <v>2.4008880000000001</v>
+        <v>2.4008879999999997</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -62917,7 +62705,7 @@
         <v>1.0640000000000001</v>
       </c>
       <c r="AH77">
-        <v>2.9784000000000001E-2</v>
+        <v>2.9783999999999998E-2</v>
       </c>
       <c r="AI77">
         <v>2.6457839999999999</v>
@@ -63131,10 +62919,10 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="AH79">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AI79">
-        <v>4.3076359999999996</v>
+        <v>4.3076360000000005</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -63238,10 +63026,10 @@
         <v>1.3160000000000001</v>
       </c>
       <c r="AH80">
-        <v>4.9056000000000002E-2</v>
+        <v>4.9055999999999995E-2</v>
       </c>
       <c r="AI80">
-        <v>2.293056</v>
+        <v>2.2930560000000004</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -63345,7 +63133,7 @@
         <v>1.302</v>
       </c>
       <c r="AH81">
-        <v>6.9204000000000002E-2</v>
+        <v>6.9203999999999988E-2</v>
       </c>
       <c r="AI81">
         <v>1.819204</v>
@@ -63452,10 +63240,10 @@
         <v>0</v>
       </c>
       <c r="AH82">
-        <v>3.8544000000000002E-2</v>
+        <v>3.8543999999999995E-2</v>
       </c>
       <c r="AI82">
-        <v>0.58254399999999995</v>
+        <v>0.58254400000000006</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -63562,7 +63350,7 @@
         <v>7.5336E-2</v>
       </c>
       <c r="AI83">
-        <v>2.943336</v>
+        <v>2.9433360000000004</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -63669,7 +63457,7 @@
         <v>5.2560000000000003E-3</v>
       </c>
       <c r="AI84">
-        <v>3.3672559999999998</v>
+        <v>3.3672560000000002</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -63990,7 +63778,7 @@
         <v>1.6643999999999999E-2</v>
       </c>
       <c r="AI87">
-        <v>6.0666440000000001</v>
+        <v>6.066644000000001</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -64204,7 +63992,7 @@
         <v>0.14716799999999999</v>
       </c>
       <c r="AI89">
-        <v>0.86316800000000005</v>
+        <v>0.86316799999999994</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -64415,7 +64203,7 @@
         <v>0.79800000000000004</v>
       </c>
       <c r="AH91">
-        <v>9.8112000000000005E-2</v>
+        <v>9.8111999999999991E-2</v>
       </c>
       <c r="AI91">
         <v>0.89611200000000002</v>
@@ -64843,10 +64631,10 @@
         <v>1.6379999999999999</v>
       </c>
       <c r="AH95">
-        <v>3.8544000000000002E-2</v>
+        <v>3.8543999999999995E-2</v>
       </c>
       <c r="AI95">
-        <v>2.6085440000000002</v>
+        <v>2.6085439999999998</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -64953,7 +64741,7 @@
         <v>0.14103599999999999</v>
       </c>
       <c r="AI96">
-        <v>0.587036</v>
+        <v>0.58703599999999989</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -65060,7 +64848,7 @@
         <v>3.5040000000000002E-2</v>
       </c>
       <c r="AI97">
-        <v>2.6570399999999998</v>
+        <v>2.6570400000000003</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -65167,7 +64955,7 @@
         <v>4.1172E-2</v>
       </c>
       <c r="AI98">
-        <v>3.0871719999999998</v>
+        <v>3.0871720000000002</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -65274,7 +65062,7 @@
         <v>0</v>
       </c>
       <c r="AI99">
-        <v>11.11</v>
+        <v>11.110000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -65488,7 +65276,7 @@
         <v>2.0147999999999999E-2</v>
       </c>
       <c r="AI101">
-        <v>2.9321480000000002</v>
+        <v>2.9321479999999998</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -65809,7 +65597,7 @@
         <v>2.8908E-2</v>
       </c>
       <c r="AI104">
-        <v>3.1549079999999998</v>
+        <v>3.1549080000000003</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -65913,7 +65701,7 @@
         <v>2.73</v>
       </c>
       <c r="AH105">
-        <v>1.9272000000000001E-2</v>
+        <v>1.9271999999999997E-2</v>
       </c>
       <c r="AI105">
         <v>3.2452719999999999</v>
@@ -66127,7 +65915,7 @@
         <v>0</v>
       </c>
       <c r="AH107">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AI107">
         <v>11.594892</v>
@@ -66237,7 +66025,7 @@
         <v>1.3140000000000001E-2</v>
       </c>
       <c r="AI108">
-        <v>7.8071400000000004</v>
+        <v>7.8071399999999995</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -66448,7 +66236,7 @@
         <v>0.33600000000000002</v>
       </c>
       <c r="AH110">
-        <v>0.18045600000000001</v>
+        <v>0.18045599999999998</v>
       </c>
       <c r="AI110">
         <v>0.82045599999999996</v>
@@ -66555,7 +66343,7 @@
         <v>0</v>
       </c>
       <c r="AH111">
-        <v>9.6360000000000005E-3</v>
+        <v>9.6359999999999987E-3</v>
       </c>
       <c r="AI111">
         <v>12.589636</v>
@@ -66662,7 +66450,7 @@
         <v>0</v>
       </c>
       <c r="AH112">
-        <v>1.4892000000000001E-2</v>
+        <v>1.4891999999999999E-2</v>
       </c>
       <c r="AI112">
         <v>12.874891999999999</v>
@@ -66876,10 +66664,10 @@
         <v>1.008</v>
       </c>
       <c r="AH114">
-        <v>4.9931999999999997E-2</v>
+        <v>4.9932000000000004E-2</v>
       </c>
       <c r="AI114">
-        <v>6.3699320000000004</v>
+        <v>6.3699319999999995</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -66986,7 +66774,7 @@
         <v>4.5552000000000002E-2</v>
       </c>
       <c r="AI115">
-        <v>3.3335520000000001</v>
+        <v>3.3335519999999996</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -67093,7 +66881,7 @@
         <v>4.6427999999999997E-2</v>
       </c>
       <c r="AI116">
-        <v>3.6544279999999998</v>
+        <v>3.6544280000000002</v>
       </c>
     </row>
   </sheetData>

--- a/source data/BO_iteration.xlsx
+++ b/source data/BO_iteration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dangerlin/Documents/GitHub/SDL-for-low-temperature-ZIB-electrolyte-optimiztion/source data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2A2D9B-1ECA-E14C-8A8A-F4698469C4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2CBFCA3-2C05-524C-8A08-856F69233142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="60160" windowHeight="33840" activeTab="5" xr2:uid="{C0319422-2C05-7840-8738-65B20D86A76B}"/>
   </bookViews>
@@ -127,12 +127,6 @@
     <t xml:space="preserve">Data of single objective optimization </t>
   </si>
   <si>
-    <t>Potential_Mean</t>
-  </si>
-  <si>
-    <t>Potential_STD</t>
-  </si>
-  <si>
     <t>OER_Mean</t>
   </si>
   <si>
@@ -143,18 +137,6 @@
   </si>
   <si>
     <t>HER_STD</t>
-  </si>
-  <si>
-    <t>Potential_1</t>
-  </si>
-  <si>
-    <t>Potential_2</t>
-  </si>
-  <si>
-    <t>Potential_3</t>
-  </si>
-  <si>
-    <t>Potential_4</t>
   </si>
   <si>
     <t>OER_1</t>
@@ -209,171 +191,6 @@
   </si>
   <si>
     <t xml:space="preserve">Data of multiple objective optimization </t>
-  </si>
-  <si>
-    <r>
-      <t>Liquid_1: ZnCl</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(15 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_2: Zn(BF</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(10 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_3: satureated Zn(ClO</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(4.29 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_4: saturated Zn(OTf)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve"> (4 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_5: saturated Zn(Gluconate)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve"> (0.219 m)</t>
-    </r>
   </si>
   <si>
     <t>2.10E-05</t>
@@ -479,126 +296,6 @@
   </si>
   <si>
     <t>Multi-obj opt_HE3</t>
-  </si>
-  <si>
-    <r>
-      <t>Liquid_1: ZnCl</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(15 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_2: Zn(ClO</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(4 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_3: Zn(OTf)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve"> (3.5 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_4: saturated Zn(Gluconate)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve"> (0.219 m)</t>
-    </r>
   </si>
   <si>
     <t>0.5677721915351116</t>
@@ -833,7 +530,364 @@
   </si>
   <si>
     <r>
-      <t>Liquid_1: saturated ZnCl</t>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>Conductivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (mS cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>–1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>) was used as the single objective.
+Liquid_1: saturated ZnCl</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(32.657 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_2: satureated ZnSO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(3.575 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_3: saturated Zn(OAc)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (1.913 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_4: saturated Zn(Gluconate)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (0.219 m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>Conductivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (mS cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>–1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>) was used as the single objective.
+Liquid_1: saturated ZnCl</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(32.657 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_2: saturated ZnBr</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(20.915 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_3: satureated ZnSO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(3.575 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_4: saturated Zn(OAc)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (1.913 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_5: saturated Zn(Gluconate)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (0.219 m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>Conductivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (mS cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>–1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>) and electrochemical stability window (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>ESW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>, V) were used as objectives.
+Liquid_1: saturated ZnCl</t>
     </r>
     <r>
       <rPr>
@@ -963,7 +1017,61 @@
   </si>
   <si>
     <r>
-      <t>Liquid_1: saturated ZnCl</t>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>Conductivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (mS cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>–1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>) and electrochemical stability window (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>ESW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>, V) were used as objectives.
+Liquid_1: ZnCl</t>
     </r>
     <r>
       <rPr>
@@ -980,7 +1088,7 @@
         <color theme="1"/>
         <rFont val="ArialMT"/>
       </rPr>
-      <t>(32.657 m)</t>
+      <t>(15 m)</t>
     </r>
     <r>
       <rPr>
@@ -990,7 +1098,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
-Liquid_2: satureated ZnSO</t>
+Liquid_2: Zn(BF</t>
     </r>
     <r>
       <rPr>
@@ -999,7 +1107,25 @@
         <color theme="1"/>
         <rFont val="ArialMT"/>
       </rPr>
-      <t xml:space="preserve">4 </t>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
     </r>
     <r>
       <rPr>
@@ -1007,7 +1133,7 @@
         <color theme="1"/>
         <rFont val="ArialMT"/>
       </rPr>
-      <t>(3.575 m)</t>
+      <t>(10 m)</t>
     </r>
     <r>
       <rPr>
@@ -1017,7 +1143,51 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
-Liquid_3: saturated Zn(OAc)</t>
+Liquid_3: satureated Zn(ClO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(4.29 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_4: saturated Zn(OTf)</t>
     </r>
     <r>
       <rPr>
@@ -1034,7 +1204,181 @@
         <color theme="1"/>
         <rFont val="ArialMT"/>
       </rPr>
-      <t xml:space="preserve"> (1.913 m)</t>
+      <t xml:space="preserve"> (4 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_5: saturated Zn(Gluconate)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (0.219 m)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>Conductivity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (mS cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>–1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>) and electrochemical stability window (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>ESW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t>, V) were used as objectives.
+Liquid_1: ZnCl</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(15 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_2: Zn(ClO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>(4 m)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Liquid_3: Zn(OTf)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ArialMT"/>
+      </rPr>
+      <t xml:space="preserve"> (3.5 m)</t>
     </r>
     <r>
       <rPr>
@@ -1065,141 +1409,29 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Liquid_1: saturated ZnCl</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(32.657 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_2: saturated ZnBr</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(20.915 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_3: satureated ZnSO</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve">4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>(3.575 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_4: saturated Zn(OAc)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve"> (1.913 m)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Liquid_5: saturated Zn(Gluconate)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="ArialMT"/>
-      </rPr>
-      <t xml:space="preserve"> (0.219 m)</t>
-    </r>
+    <t>ESW_Mean</t>
+  </si>
+  <si>
+    <t>ESW_STD</t>
+  </si>
+  <si>
+    <t>ESW_1</t>
+  </si>
+  <si>
+    <t>ESW_2</t>
+  </si>
+  <si>
+    <t>ESW_3</t>
+  </si>
+  <si>
+    <t>ESW_4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1213,6 +1445,19 @@
       <name val="ArialMT"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ArialMT"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ArialMT"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="ArialMT"/>
@@ -1238,7 +1483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1249,10 +1494,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1587,13 +1835,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1CE7DE4-EA2A-F645-8F47-792DAD65B977}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1"/>
     <col min="2" max="2" width="20.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46" style="1" customWidth="1"/>
     <col min="5" max="16384" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
@@ -1611,21 +1859,21 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="76">
+    <row r="2" spans="1:4" ht="112">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="95">
+        <v>160</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="131">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1635,51 +1883,54 @@
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="95">
+      <c r="D3" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="131">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="95">
+        <v>48</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="131">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="76">
+        <v>48</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="112">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>91</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1751,8 +2002,8 @@
       <c r="B2">
         <v>42.918450947499998</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>92</v>
+      <c r="C2" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="D2">
         <v>42.050275999999997</v>
@@ -1801,8 +2052,8 @@
       <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>93</v>
+      <c r="B3" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="C3">
         <v>0.24782085045246899</v>
@@ -1834,19 +2085,19 @@
       <c r="L3">
         <v>61</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="4">
         <v>2.8738159999999997</v>
       </c>
       <c r="N3">
         <v>0.65780000000000005</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="4">
         <v>0.40555599999999997</v>
       </c>
       <c r="P3">
         <v>5.9567999999999996E-2</v>
       </c>
-      <c r="Q3" s="5">
+      <c r="Q3" s="4">
         <v>3.9967399999999995</v>
       </c>
     </row>
@@ -1857,8 +2108,8 @@
       <c r="B4">
         <v>39.517174095000001</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>94</v>
+      <c r="C4" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="D4">
         <v>39.16172675</v>
@@ -1910,8 +2161,8 @@
       <c r="B5">
         <v>74.083560152499999</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>95</v>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="D5">
         <v>73.497387380000006</v>
@@ -1952,7 +2203,7 @@
       <c r="P5">
         <v>3.066E-2</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="4">
         <v>6.7876839999999996</v>
       </c>
     </row>
@@ -1963,8 +2214,8 @@
       <c r="B6">
         <v>52.898363297499998</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>96</v>
+      <c r="C6" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="D6">
         <v>52.881947140000001</v>
@@ -1993,10 +2244,10 @@
       <c r="L6">
         <v>91</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="4">
         <v>1.4369079999999999</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="4">
         <v>0.72930000000000006</v>
       </c>
       <c r="O6">
@@ -2016,8 +2267,8 @@
       <c r="B7">
         <v>39.953147244999997</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>97</v>
+      <c r="C7" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="D7">
         <v>38.174922680000002</v>
@@ -2046,7 +2297,7 @@
       <c r="L7">
         <v>90</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="4">
         <v>15.283475999999999</v>
       </c>
       <c r="N7">
@@ -2058,7 +2309,7 @@
       <c r="P7">
         <v>9.6359999999999987E-3</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="4">
         <v>15.717471999999999</v>
       </c>
     </row>
@@ -2069,8 +2320,8 @@
       <c r="B8">
         <v>57.21813925</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>98</v>
+      <c r="C8" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="D8">
         <v>56.76311862</v>
@@ -2111,7 +2362,7 @@
       <c r="P8">
         <v>2.3651999999999999E-2</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8" s="4">
         <v>2.9645879999999996</v>
       </c>
     </row>
@@ -2119,11 +2370,11 @@
       <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>100</v>
+      <c r="B9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="D9">
         <v>60.740653760000001</v>
@@ -2155,7 +2406,7 @@
       <c r="M9">
         <v>3.6575839999999999</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="4">
         <v>1.0009999999999999</v>
       </c>
       <c r="O9">
@@ -2164,7 +2415,7 @@
       <c r="P9">
         <v>1.0512000000000001E-2</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="4">
         <v>4.7685719999999998</v>
       </c>
     </row>
@@ -2172,8 +2423,8 @@
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>101</v>
+      <c r="B10" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="C10">
         <v>0.526246489632614</v>
@@ -2228,8 +2479,8 @@
       <c r="B11">
         <v>48.656278100000002</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>102</v>
+      <c r="C11" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="D11">
         <v>49.002003170000002</v>
@@ -2311,7 +2562,7 @@
       <c r="L12">
         <v>102</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="4">
         <v>12.279031999999999</v>
       </c>
       <c r="N12">
@@ -2334,8 +2585,8 @@
       <c r="B13">
         <v>52.933969677500002</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>103</v>
+      <c r="C13" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="D13">
         <v>52.706491149999998</v>
@@ -2387,8 +2638,8 @@
       <c r="B14">
         <v>39.682550677499997</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>104</v>
+      <c r="C14" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="D14">
         <v>38.268316319999997</v>
@@ -2473,7 +2724,7 @@
       <c r="M15">
         <v>20.116712</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" s="4">
         <v>0.57199999999999995</v>
       </c>
       <c r="O15">
@@ -2493,8 +2744,8 @@
       <c r="B16">
         <v>54.45862511</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>105</v>
+      <c r="C16" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="D16">
         <v>52.004763179999998</v>
@@ -2546,8 +2797,8 @@
       <c r="B17">
         <v>45.916521227499999</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>106</v>
+      <c r="C17" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="D17">
         <v>46.545090799999997</v>
@@ -2576,16 +2827,16 @@
       <c r="L17">
         <v>130</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="4">
         <v>1.3062799999999997</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" s="4">
         <v>0.28599999999999998</v>
       </c>
       <c r="O17">
         <v>0.160692</v>
       </c>
-      <c r="P17" s="5">
+      <c r="P17" s="4">
         <v>6.0444000000000005E-2</v>
       </c>
       <c r="Q17">
@@ -2596,11 +2847,11 @@
       <c r="A18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>108</v>
+      <c r="B18" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="D18">
         <v>38.504118099999999</v>
@@ -2652,8 +2903,8 @@
       <c r="B19">
         <v>39.98774126</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>109</v>
+      <c r="C19" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="D19">
         <v>44.528613980000003</v>
@@ -2705,8 +2956,8 @@
       <c r="B20">
         <v>38.087868784999998</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>110</v>
+      <c r="C20" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="D20">
         <v>37.051213250000004</v>
@@ -2755,11 +3006,11 @@
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>112</v>
+      <c r="B21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="D21">
         <v>44.894928849999999</v>
@@ -2800,7 +3051,7 @@
       <c r="P21">
         <v>5.5188000000000001E-2</v>
       </c>
-      <c r="Q21" s="5">
+      <c r="Q21" s="4">
         <v>5.4815280000000008</v>
       </c>
     </row>
@@ -2811,8 +3062,8 @@
       <c r="B22">
         <v>59.166765507500003</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>113</v>
+      <c r="C22" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="D22">
         <v>57.888635649999998</v>
@@ -2841,7 +3092,7 @@
       <c r="L22">
         <v>89</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="4">
         <v>9.6664720000000006</v>
       </c>
       <c r="N22">
@@ -2864,8 +3115,8 @@
       <c r="B23">
         <v>30.025825112500002</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>114</v>
+      <c r="C23" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="D23">
         <v>30.91275641</v>
@@ -2906,7 +3157,7 @@
       <c r="P23">
         <v>5.1684000000000001E-2</v>
       </c>
-      <c r="Q23" s="5">
+      <c r="Q23" s="4">
         <v>1.7668519999999999</v>
       </c>
     </row>
@@ -2970,8 +3221,8 @@
       <c r="B25">
         <v>44.418483864999999</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>115</v>
+      <c r="C25" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="D25">
         <v>43.953496659999999</v>
@@ -3023,8 +3274,8 @@
       <c r="B26">
         <v>51.919963320000001</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>116</v>
+      <c r="C26" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="D26">
         <v>51.646000600000001</v>
@@ -3076,8 +3327,8 @@
       <c r="B27">
         <v>50.467251564999998</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>117</v>
+      <c r="C27" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="D27">
         <v>49.303560660000002</v>
@@ -3109,7 +3360,7 @@
       <c r="M27">
         <v>5.3557479999999993</v>
       </c>
-      <c r="N27" s="5">
+      <c r="N27" s="4">
         <v>1.1439999999999999</v>
       </c>
       <c r="O27">
@@ -3118,7 +3369,7 @@
       <c r="P27">
         <v>1.5768000000000001E-2</v>
       </c>
-      <c r="Q27" s="5">
+      <c r="Q27" s="4">
         <v>6.5996879999999987</v>
       </c>
     </row>
@@ -3129,8 +3380,8 @@
       <c r="B28">
         <v>47.054673972499998</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>118</v>
+      <c r="C28" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="D28">
         <v>46.224606780000002</v>
@@ -3179,11 +3430,11 @@
       <c r="A29" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>120</v>
+      <c r="B29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="D29">
         <v>28.79088243</v>
@@ -3235,8 +3486,8 @@
       <c r="B30">
         <v>64.1891300825</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>121</v>
+      <c r="C30" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="D30">
         <v>64.044459579999995</v>
@@ -3277,7 +3528,7 @@
       <c r="P30">
         <v>7.1831999999999993E-2</v>
       </c>
-      <c r="Q30" s="5">
+      <c r="Q30" s="4">
         <v>4.4765479999999984</v>
       </c>
     </row>
@@ -3288,8 +3539,8 @@
       <c r="B31">
         <v>36.5237768</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>122</v>
+      <c r="C31" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="D31">
         <v>35.710041259999997</v>
@@ -3341,8 +3592,8 @@
       <c r="B32">
         <v>54.608795227500003</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>123</v>
+      <c r="C32" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="D32">
         <v>55.335758200000001</v>
@@ -3383,7 +3634,7 @@
       <c r="P32">
         <v>2.7156E-2</v>
       </c>
-      <c r="Q32" s="5">
+      <c r="Q32" s="4">
         <v>3.2279640000000005</v>
       </c>
     </row>
@@ -3486,7 +3737,7 @@
       <c r="O34">
         <v>6.8867999999999999E-2</v>
       </c>
-      <c r="P34" s="5">
+      <c r="P34" s="4">
         <v>3.5915999999999997E-2</v>
       </c>
       <c r="Q34">
@@ -3542,7 +3793,7 @@
       <c r="P35">
         <v>2.9783999999999998E-2</v>
       </c>
-      <c r="Q35" s="5">
+      <c r="Q35" s="4">
         <v>10.688351999999998</v>
       </c>
     </row>
@@ -3550,11 +3801,11 @@
       <c r="A36" t="s">
         <v>19</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>125</v>
+      <c r="B36" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="D36">
         <v>47.829798220000001</v>
@@ -3589,13 +3840,13 @@
       <c r="N36">
         <v>8.5800000000000015E-2</v>
       </c>
-      <c r="O36" s="5">
+      <c r="O36" s="4">
         <v>0.17599600000000001</v>
       </c>
-      <c r="P36" s="5">
+      <c r="P36" s="4">
         <v>0.12088800000000001</v>
       </c>
-      <c r="Q36" s="5">
+      <c r="Q36" s="4">
         <v>1.9502200000000001</v>
       </c>
     </row>
@@ -3603,11 +3854,11 @@
       <c r="A37" t="s">
         <v>19</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>127</v>
+      <c r="B37" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="D37">
         <v>29.869636610000001</v>
@@ -3636,7 +3887,7 @@
       <c r="L37">
         <v>19</v>
       </c>
-      <c r="M37" s="5">
+      <c r="M37" s="4">
         <v>4.8332360000000003</v>
       </c>
       <c r="N37">
@@ -3645,10 +3896,10 @@
       <c r="O37">
         <v>0.57389999999999997</v>
       </c>
-      <c r="P37" s="5">
+      <c r="P37" s="4">
         <v>1.8395999999999999E-2</v>
       </c>
-      <c r="Q37" s="5">
+      <c r="Q37" s="4">
         <v>6.8269320000000002</v>
       </c>
     </row>
@@ -3656,11 +3907,11 @@
       <c r="A38" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>129</v>
+      <c r="B38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="D38">
         <v>48.302143129999997</v>
@@ -3698,7 +3949,7 @@
       <c r="O38">
         <v>0.18364800000000001</v>
       </c>
-      <c r="P38" s="5">
+      <c r="P38" s="4">
         <v>5.6939999999999998E-2</v>
       </c>
       <c r="Q38">
@@ -3712,8 +3963,8 @@
       <c r="B39">
         <v>43.912943492499998</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>130</v>
+      <c r="C39" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="D39">
         <v>43.807258959999999</v>
@@ -3762,11 +4013,11 @@
       <c r="A40" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>132</v>
+      <c r="B40" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="D40">
         <v>34.971083950000001</v>
@@ -3801,13 +4052,13 @@
       <c r="N40">
         <v>1.2869999999999999</v>
       </c>
-      <c r="O40" s="5">
+      <c r="O40" s="4">
         <v>0.29842799999999997</v>
       </c>
       <c r="P40">
         <v>5.5188000000000001E-2</v>
       </c>
-      <c r="Q40" s="5">
+      <c r="Q40" s="4">
         <v>8.4332719999999988</v>
       </c>
     </row>
@@ -3815,11 +4066,11 @@
       <c r="A41" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>134</v>
+      <c r="B41" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="D41">
         <v>17.629161109999998</v>
@@ -3848,7 +4099,7 @@
       <c r="L41">
         <v>13</v>
       </c>
-      <c r="M41" s="5">
+      <c r="M41" s="4">
         <v>15.936615999999999</v>
       </c>
       <c r="N41">
@@ -3860,7 +4111,7 @@
       <c r="P41">
         <v>7.0080000000000003E-3</v>
       </c>
-      <c r="Q41" s="5">
+      <c r="Q41" s="4">
         <v>17.154619999999998</v>
       </c>
     </row>
@@ -3871,8 +4122,8 @@
       <c r="B42">
         <v>42.693942667500004</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>135</v>
+      <c r="C42" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="D42">
         <v>41.585500430000003</v>
@@ -3904,7 +4155,7 @@
       <c r="M42">
         <v>4.3107239999999996</v>
       </c>
-      <c r="N42" s="5">
+      <c r="N42" s="4">
         <v>1.0009999999999999</v>
       </c>
       <c r="O42">
@@ -3924,8 +4175,8 @@
       <c r="B43">
         <v>59.239201352499997</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>136</v>
+      <c r="C43" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="D43">
         <v>59.21154035</v>
@@ -3966,7 +4217,7 @@
       <c r="P43">
         <v>2.7156E-2</v>
       </c>
-      <c r="Q43" s="5">
+      <c r="Q43" s="4">
         <v>4.330487999999999</v>
       </c>
     </row>
@@ -3974,11 +4225,11 @@
       <c r="A44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>138</v>
+      <c r="B44" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="D44">
         <v>37.165418899999999</v>
@@ -4030,8 +4281,8 @@
       <c r="B45">
         <v>42.565158369999999</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>139</v>
+      <c r="C45" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="D45">
         <v>43.152021740000002</v>
@@ -4083,8 +4334,8 @@
       <c r="B46">
         <v>50.865378542499997</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>140</v>
+      <c r="C46" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="D46">
         <v>49.076958099999999</v>
@@ -4125,7 +4376,7 @@
       <c r="P46">
         <v>7.7964000000000006E-2</v>
       </c>
-      <c r="Q46" s="5">
+      <c r="Q46" s="4">
         <v>4.1103799999999993</v>
       </c>
     </row>
@@ -4136,8 +4387,8 @@
       <c r="B47">
         <v>51.105464947500003</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>141</v>
+      <c r="C47" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="D47">
         <v>49.192516959999999</v>
@@ -4166,7 +4417,7 @@
       <c r="L47">
         <v>87</v>
       </c>
-      <c r="M47" s="5">
+      <c r="M47" s="4">
         <v>12.279031999999999</v>
       </c>
       <c r="N47">
@@ -4178,7 +4429,7 @@
       <c r="P47">
         <v>3.3287999999999998E-2</v>
       </c>
-      <c r="Q47" s="5">
+      <c r="Q47" s="4">
         <v>12.655899999999999</v>
       </c>
     </row>
@@ -4186,11 +4437,11 @@
       <c r="A48" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>143</v>
+      <c r="B48" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="D48">
         <v>42.311381820000001</v>
@@ -4219,7 +4470,7 @@
       <c r="L48">
         <v>67</v>
       </c>
-      <c r="M48" s="5">
+      <c r="M48" s="4">
         <v>1.3062799999999997</v>
       </c>
       <c r="N48">
@@ -4228,10 +4479,10 @@
       <c r="O48">
         <v>0.13008400000000001</v>
       </c>
-      <c r="P48" s="5">
+      <c r="P48" s="4">
         <v>4.2923999999999997E-2</v>
       </c>
-      <c r="Q48" s="5">
+      <c r="Q48" s="4">
         <v>3.0093880000000004</v>
       </c>
     </row>
@@ -4239,11 +4490,11 @@
       <c r="A49" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>145</v>
+      <c r="B49" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="D49">
         <v>39.021679239999997</v>
@@ -4281,10 +4532,10 @@
       <c r="O49">
         <v>0.20660400000000001</v>
       </c>
-      <c r="P49" s="5">
+      <c r="P49" s="4">
         <v>6.0444000000000005E-2</v>
       </c>
-      <c r="Q49" s="5">
+      <c r="Q49" s="4">
         <v>9.4071520000000017</v>
       </c>
     </row>
@@ -4295,8 +4546,8 @@
       <c r="B50">
         <v>42.947345802500003</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>146</v>
+      <c r="C50" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="D50">
         <v>43.43559741</v>
@@ -4334,7 +4585,7 @@
       <c r="O50">
         <v>5.3564000000000001E-2</v>
       </c>
-      <c r="P50" s="5">
+      <c r="P50" s="4">
         <v>0.10074</v>
       </c>
       <c r="Q50">
@@ -4348,8 +4599,8 @@
       <c r="B51">
         <v>36.774583759999999</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>147</v>
+      <c r="C51" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="D51">
         <v>36.427164300000001</v>
@@ -4381,7 +4632,7 @@
       <c r="M51">
         <v>3.1350719999999996</v>
       </c>
-      <c r="N51" s="5">
+      <c r="N51" s="4">
         <v>0.14299999999999999</v>
       </c>
       <c r="O51">
@@ -4451,11 +4702,11 @@
       <c r="A53" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>149</v>
+      <c r="B53" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="D53">
         <v>58.376072559999997</v>
@@ -4507,8 +4758,8 @@
       <c r="B54">
         <v>60.302358515000002</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>150</v>
+      <c r="C54" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="D54">
         <v>59.678462619999998</v>
@@ -4537,19 +4788,19 @@
       <c r="L54">
         <v>133</v>
       </c>
-      <c r="M54" s="5">
+      <c r="M54" s="4">
         <v>4.8332360000000003</v>
       </c>
       <c r="N54">
         <v>0.12870000000000001</v>
       </c>
-      <c r="O54" s="5">
+      <c r="O54" s="4">
         <v>0.35199200000000003</v>
       </c>
-      <c r="P54" s="5">
+      <c r="P54" s="4">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="Q54" s="5">
+      <c r="Q54" s="4">
         <v>5.3358280000000002</v>
       </c>
     </row>
@@ -4560,8 +4811,8 @@
       <c r="B55">
         <v>61.182410417500002</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>151</v>
+      <c r="C55" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="D55">
         <v>61.002644850000003</v>
@@ -4602,7 +4853,7 @@
       <c r="P55">
         <v>1.4016000000000001E-2</v>
       </c>
-      <c r="Q55" s="5">
+      <c r="Q55" s="4">
         <v>4.8443159999999992</v>
       </c>
     </row>
@@ -4613,8 +4864,8 @@
       <c r="B56">
         <v>50.737554317499999</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>152</v>
+      <c r="C56" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="D56">
         <v>50.460411039999997</v>
@@ -4646,7 +4897,7 @@
       <c r="M56">
         <v>3.1350719999999996</v>
       </c>
-      <c r="N56" s="5">
+      <c r="N56" s="4">
         <v>1.0009999999999999</v>
       </c>
       <c r="O56">
@@ -4655,7 +4906,7 @@
       <c r="P56">
         <v>5.8692000000000001E-2</v>
       </c>
-      <c r="Q56" s="5">
+      <c r="Q56" s="4">
         <v>4.3018919999999996</v>
       </c>
     </row>
@@ -4716,11 +4967,11 @@
       <c r="A58" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>154</v>
+      <c r="B58" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="D58">
         <v>49.31990132</v>
@@ -4761,7 +5012,7 @@
       <c r="P58">
         <v>9.4607999999999998E-2</v>
       </c>
-      <c r="Q58" s="5">
+      <c r="Q58" s="4">
         <v>4.4580720000000005</v>
       </c>
     </row>
@@ -4769,11 +5020,11 @@
       <c r="A59" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>156</v>
+      <c r="B59" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="D59">
         <v>42.700642500000001</v>
@@ -4855,7 +5106,7 @@
       <c r="L60">
         <v>5</v>
       </c>
-      <c r="M60" s="5">
+      <c r="M60" s="4">
         <v>13.454683999999999</v>
       </c>
       <c r="N60">
@@ -4867,7 +5118,7 @@
       <c r="P60">
         <v>5.2560000000000003E-3</v>
       </c>
-      <c r="Q60" s="5">
+      <c r="Q60" s="4">
         <v>15.231891999999998</v>
       </c>
     </row>
@@ -4875,11 +5126,11 @@
       <c r="A61" t="s">
         <v>19</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>158</v>
+      <c r="B61" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="D61">
         <v>25.110166209999999</v>
@@ -4908,7 +5159,7 @@
       <c r="L61">
         <v>16</v>
       </c>
-      <c r="M61" s="5">
+      <c r="M61" s="4">
         <v>0.65313999999999983</v>
       </c>
       <c r="N61">
@@ -4917,10 +5168,10 @@
       <c r="O61">
         <v>0.90293600000000007</v>
       </c>
-      <c r="P61" s="5">
+      <c r="P61" s="4">
         <v>2.8908E-2</v>
       </c>
-      <c r="Q61" s="5">
+      <c r="Q61" s="4">
         <v>2.7003840000000001</v>
       </c>
     </row>
@@ -4928,11 +5179,11 @@
       <c r="A62" t="s">
         <v>19</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>160</v>
+      <c r="B62" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="D62">
         <v>40.560747689999999</v>
@@ -4961,7 +5212,7 @@
       <c r="L62">
         <v>93</v>
       </c>
-      <c r="M62" s="5">
+      <c r="M62" s="4">
         <v>3.5269559999999998</v>
       </c>
       <c r="N62">
@@ -4984,8 +5235,8 @@
       <c r="B63">
         <v>45.376144932499997</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>161</v>
+      <c r="C63" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="D63">
         <v>45.720019999999998</v>
@@ -5026,7 +5277,7 @@
       <c r="P63">
         <v>8.4971999999999992E-2</v>
       </c>
-      <c r="Q63" s="5">
+      <c r="Q63" s="4">
         <v>4.5086479999999991</v>
       </c>
     </row>
@@ -5037,8 +5288,8 @@
       <c r="B64">
         <v>46.582691692499999</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>162</v>
+      <c r="C64" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="D64">
         <v>46.320895219999997</v>
@@ -5090,8 +5341,8 @@
       <c r="B65">
         <v>56.5917818275</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>163</v>
+      <c r="C65" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="D65">
         <v>63.589058049999998</v>
@@ -5140,11 +5391,11 @@
       <c r="A66" t="s">
         <v>20</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>165</v>
+      <c r="B66" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="D66">
         <v>43.569656350000002</v>
@@ -5182,10 +5433,10 @@
       <c r="O66">
         <v>0.28312400000000004</v>
       </c>
-      <c r="P66" s="5">
+      <c r="P66" s="4">
         <v>3.6791999999999998E-2</v>
       </c>
-      <c r="Q66" s="5">
+      <c r="Q66" s="4">
         <v>10.021576000000001</v>
       </c>
     </row>
@@ -5196,8 +5447,8 @@
       <c r="B67">
         <v>51.510058727500002</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>166</v>
+      <c r="C67" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="D67">
         <v>52.000143639999997</v>
@@ -5226,7 +5477,7 @@
       <c r="L67">
         <v>109</v>
       </c>
-      <c r="M67" s="5">
+      <c r="M67" s="4">
         <v>7.0539119999999995</v>
       </c>
       <c r="N67">
@@ -12766,22 +13017,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" t="s">
-        <v>32</v>
       </c>
       <c r="J1" t="s">
         <v>3</v>
@@ -12796,40 +13047,40 @@
         <v>6</v>
       </c>
       <c r="N1" t="s">
+        <v>168</v>
+      </c>
+      <c r="O1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P1" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>171</v>
+      </c>
+      <c r="R1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" t="s">
+      <c r="U1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" t="s">
+      <c r="V1" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="W1" t="s">
         <v>36</v>
       </c>
-      <c r="R1" t="s">
+      <c r="X1" t="s">
         <v>37</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Y1" t="s">
         <v>38</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>44</v>
       </c>
       <c r="Z1" t="s">
         <v>7</v>
@@ -18668,8 +18919,8 @@
       <c r="L53">
         <v>57.49086114</v>
       </c>
-      <c r="M53" s="5" t="s">
-        <v>45</v>
+      <c r="M53" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="N53">
         <v>1.7250869550000001</v>
@@ -18882,8 +19133,8 @@
       <c r="H55">
         <v>-4.0384228000000001E-2</v>
       </c>
-      <c r="I55" s="5" t="s">
-        <v>46</v>
+      <c r="I55" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="J55">
         <v>50.433476059999997</v>
@@ -19673,8 +19924,8 @@
       <c r="H62">
         <v>-3.4185321999999997E-2</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>47</v>
+      <c r="I62" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="J62">
         <v>38.486427890000002</v>
@@ -20012,8 +20263,8 @@
       <c r="H65">
         <v>-4.0408083999999997E-2</v>
       </c>
-      <c r="I65" s="5" t="s">
-        <v>48</v>
+      <c r="I65" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="J65">
         <v>51.276335279999998</v>
@@ -20351,8 +20602,8 @@
       <c r="H68">
         <v>-4.0454401000000001E-2</v>
       </c>
-      <c r="I68" s="5" t="s">
-        <v>49</v>
+      <c r="I68" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="J68">
         <v>53.549883610000002</v>
@@ -22046,8 +22297,8 @@
       <c r="H83">
         <v>-4.0377544000000001E-2</v>
       </c>
-      <c r="I83" s="5" t="s">
-        <v>46</v>
+      <c r="I83" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="J83">
         <v>28.099021740000001</v>
@@ -27357,8 +27608,8 @@
       <c r="H130">
         <v>-2.1923268999999999E-2</v>
       </c>
-      <c r="I130" s="5" t="s">
-        <v>47</v>
+      <c r="I130" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="J130">
         <v>29.21663736</v>
@@ -27690,8 +27941,8 @@
       <c r="F133">
         <v>1.7152603280000001</v>
       </c>
-      <c r="G133" s="5" t="s">
-        <v>50</v>
+      <c r="G133" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="H133">
         <v>1.0324234E-2</v>
@@ -29611,8 +29862,8 @@
       <c r="F150">
         <v>1.573885132</v>
       </c>
-      <c r="G150" s="5" t="s">
-        <v>51</v>
+      <c r="G150" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="H150">
         <v>-6.4703202000000001E-2</v>
@@ -31086,8 +31337,8 @@
       <c r="H163">
         <v>9.892507E-3</v>
       </c>
-      <c r="I163" s="5" t="s">
-        <v>52</v>
+      <c r="I163" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="J163">
         <v>33.353342820000002</v>
@@ -35489,22 +35740,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" t="s">
-        <v>32</v>
       </c>
       <c r="J1" t="s">
         <v>3</v>
@@ -35519,40 +35770,40 @@
         <v>6</v>
       </c>
       <c r="N1" t="s">
+        <v>168</v>
+      </c>
+      <c r="O1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P1" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>171</v>
+      </c>
+      <c r="R1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" t="s">
+      <c r="U1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" t="s">
+      <c r="V1" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="W1" t="s">
         <v>36</v>
       </c>
-      <c r="R1" t="s">
+      <c r="X1" t="s">
         <v>37</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Y1" t="s">
         <v>38</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>44</v>
       </c>
       <c r="Z1" t="s">
         <v>7</v>
@@ -35842,8 +36093,8 @@
       <c r="H4">
         <v>1.087435E-2</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>56</v>
+      <c r="I4" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="J4">
         <v>62.870183310000002</v>
@@ -36294,8 +36545,8 @@
       <c r="H8">
         <v>1.0836983999999999E-2</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>57</v>
+      <c r="I8" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="J8">
         <v>62.023866499999997</v>
@@ -37989,8 +38240,8 @@
       <c r="H23">
         <v>1.0814389000000001E-2</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>58</v>
+      <c r="I23" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="J23">
         <v>49.630594649999999</v>
@@ -39119,8 +39370,8 @@
       <c r="H33">
         <v>1.0850706E-2</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>59</v>
+      <c r="I33" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="J33">
         <v>49.722037149999998</v>
@@ -39232,8 +39483,8 @@
       <c r="H34">
         <v>1.0849037000000001E-2</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>60</v>
+      <c r="I34" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="J34">
         <v>64.516713190000004</v>
@@ -39345,8 +39596,8 @@
       <c r="H35">
         <v>1.0851753E-2</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>61</v>
+      <c r="I35" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="J35">
         <v>62.764786770000001</v>
@@ -39458,8 +39709,8 @@
       <c r="H36">
         <v>1.0848524E-2</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>62</v>
+      <c r="I36" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="J36">
         <v>30.876989689999998</v>
@@ -39684,8 +39935,8 @@
       <c r="H38">
         <v>-4.0071408000000003E-2</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>63</v>
+      <c r="I38" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="J38">
         <v>89.661542299999994</v>
@@ -39797,8 +40048,8 @@
       <c r="H39">
         <v>-4.0071565000000003E-2</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>64</v>
+      <c r="I39" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="J39">
         <v>73.460761700000006</v>
@@ -40023,8 +40274,8 @@
       <c r="H41">
         <v>1.0848340999999999E-2</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>65</v>
+      <c r="I41" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="J41">
         <v>35.794268099999996</v>
@@ -42622,8 +42873,8 @@
       <c r="H64">
         <v>-3.9438149999999998E-2</v>
       </c>
-      <c r="I64" s="5" t="s">
-        <v>49</v>
+      <c r="I64" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="J64">
         <v>93.256614909999996</v>
@@ -43074,8 +43325,8 @@
       <c r="H68">
         <v>1.0828310000000001E-2</v>
       </c>
-      <c r="I68" s="5" t="s">
-        <v>66</v>
+      <c r="I68" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="J68">
         <v>64.764628490000007</v>
@@ -43526,8 +43777,8 @@
       <c r="H72">
         <v>1.0807615E-2</v>
       </c>
-      <c r="I72" s="5" t="s">
-        <v>67</v>
+      <c r="I72" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="J72">
         <v>62.231978050000002</v>
@@ -44091,8 +44342,8 @@
       <c r="H77">
         <v>-1.8143459000000001E-2</v>
       </c>
-      <c r="I77" s="5" t="s">
-        <v>68</v>
+      <c r="I77" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="J77">
         <v>102.5074609</v>
@@ -44543,8 +44794,8 @@
       <c r="H81">
         <v>9.8958980000000002E-3</v>
       </c>
-      <c r="I81" s="5" t="s">
-        <v>69</v>
+      <c r="I81" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="J81">
         <v>84.053351730000003</v>
@@ -45334,8 +45585,8 @@
       <c r="H88">
         <v>9.9551569999999992E-3</v>
       </c>
-      <c r="I88" s="5" t="s">
-        <v>70</v>
+      <c r="I88" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="J88">
         <v>82.115083170000005</v>
@@ -46012,8 +46263,8 @@
       <c r="H94">
         <v>9.9031589999999999E-3</v>
       </c>
-      <c r="I94" s="5" t="s">
-        <v>71</v>
+      <c r="I94" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="J94">
         <v>69.282708139999997</v>
@@ -46464,8 +46715,8 @@
       <c r="H98">
         <v>9.8514069999999995E-3</v>
       </c>
-      <c r="I98" s="5" t="s">
-        <v>68</v>
+      <c r="I98" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="J98">
         <v>38.094268419999999</v>
@@ -49628,8 +49879,8 @@
       <c r="H126">
         <v>9.9630729999999994E-3</v>
       </c>
-      <c r="I126" s="5" t="s">
-        <v>72</v>
+      <c r="I126" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="J126">
         <v>93.887455130000006</v>
@@ -49967,8 +50218,8 @@
       <c r="H129">
         <v>-4.0456842E-2</v>
       </c>
-      <c r="I129" s="5" t="s">
-        <v>73</v>
+      <c r="I129" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="J129">
         <v>47.3647858</v>
@@ -50645,8 +50896,8 @@
       <c r="H135">
         <v>9.8765980000000003E-3</v>
       </c>
-      <c r="I135" s="5" t="s">
-        <v>74</v>
+      <c r="I135" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="J135">
         <v>59.037385530000002</v>
@@ -50871,8 +51122,8 @@
       <c r="H137">
         <v>9.8577339999999999E-3</v>
       </c>
-      <c r="I137" s="5" t="s">
-        <v>75</v>
+      <c r="I137" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="J137">
         <v>67.363400920000004</v>
@@ -51097,8 +51348,8 @@
       <c r="H139">
         <v>9.857055E-3</v>
       </c>
-      <c r="I139" s="5" t="s">
-        <v>76</v>
+      <c r="I139" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="J139">
         <v>45.253920860000001</v>
@@ -51888,8 +52139,8 @@
       <c r="H146">
         <v>9.8914199999999997E-3</v>
       </c>
-      <c r="I146" s="5" t="s">
-        <v>77</v>
+      <c r="I146" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="J146">
         <v>77.215643479999997</v>
@@ -52340,8 +52591,8 @@
       <c r="H150">
         <v>9.9690379999999995E-3</v>
       </c>
-      <c r="I150" s="5" t="s">
-        <v>78</v>
+      <c r="I150" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="J150">
         <v>69.942284720000004</v>
@@ -52566,8 +52817,8 @@
       <c r="H152">
         <v>9.8869679999999995E-3</v>
       </c>
-      <c r="I152" s="5" t="s">
-        <v>79</v>
+      <c r="I152" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="J152">
         <v>36.253004519999998</v>
@@ -52792,8 +53043,8 @@
       <c r="H154">
         <v>9.8636330000000001E-3</v>
       </c>
-      <c r="I154" s="5" t="s">
-        <v>80</v>
+      <c r="I154" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="J154">
         <v>54.552453409999998</v>
@@ -54148,8 +54399,8 @@
       <c r="H166">
         <v>9.9869090000000004E-3</v>
       </c>
-      <c r="I166" s="5" t="s">
-        <v>81</v>
+      <c r="I166" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="J166">
         <v>59.913109370000001</v>
@@ -54483,22 +54734,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" t="s">
-        <v>32</v>
       </c>
       <c r="J1" t="s">
         <v>3</v>
@@ -54513,40 +54764,40 @@
         <v>6</v>
       </c>
       <c r="N1" t="s">
+        <v>168</v>
+      </c>
+      <c r="O1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P1" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>171</v>
+      </c>
+      <c r="R1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" t="s">
+      <c r="U1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" t="s">
+      <c r="V1" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="W1" t="s">
         <v>36</v>
       </c>
-      <c r="R1" t="s">
+      <c r="X1" t="s">
         <v>37</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Y1" t="s">
         <v>38</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>44</v>
       </c>
       <c r="Z1" t="s">
         <v>7</v>
@@ -54925,8 +55176,8 @@
       <c r="H5">
         <v>1.0816101999999999E-2</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>83</v>
+      <c r="I5" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="J5">
         <v>31.84129167</v>
@@ -55353,8 +55604,8 @@
       <c r="H9">
         <v>1.0834508E-2</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>84</v>
+      <c r="I9" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="J9">
         <v>29.933633369999999</v>
@@ -57386,8 +57637,8 @@
       <c r="H28">
         <v>-8.6923309999999993E-3</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>71</v>
+      <c r="I28" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="J28">
         <v>112.4926214</v>
@@ -57707,8 +57958,8 @@
       <c r="H31">
         <v>1.0849354E-2</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>85</v>
+      <c r="I31" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="J31">
         <v>36.381240949999999</v>
@@ -59205,8 +59456,8 @@
       <c r="H45">
         <v>9.892484E-3</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>76</v>
+      <c r="I45" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="J45">
         <v>77.095910140000001</v>
@@ -59847,8 +60098,8 @@
       <c r="H51">
         <v>9.8998360000000004E-3</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>86</v>
+      <c r="I51" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="J51">
         <v>50.624082270000002</v>
@@ -61131,8 +61382,8 @@
       <c r="H63">
         <v>9.9029860000000008E-3</v>
       </c>
-      <c r="I63" s="5" t="s">
-        <v>87</v>
+      <c r="I63" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="J63">
         <v>88.211839420000004</v>
@@ -63592,8 +63843,8 @@
       <c r="H86">
         <v>9.8935140000000008E-3</v>
       </c>
-      <c r="I86" s="5" t="s">
-        <v>88</v>
+      <c r="I86" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="J86">
         <v>30.40697655</v>
@@ -65304,8 +65555,8 @@
       <c r="H102">
         <v>-4.0421502999999998E-2</v>
       </c>
-      <c r="I102" s="5" t="s">
-        <v>89</v>
+      <c r="I102" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="J102">
         <v>49.708414179999998</v>
